--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\bois\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\bois\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578EBAA7-0E11-42C3-BDCF-6F2F88C3BB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CD674D-8219-4D60-911E-DB2EF4C92697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="465">
   <si>
     <t>path</t>
   </si>
@@ -1419,6 +1419,18 @@
   </si>
   <si>
     <t>50g</t>
+  </si>
+  <si>
+    <t>12850013</t>
+  </si>
+  <si>
+    <t>25x40-2,40m</t>
+  </si>
+  <si>
+    <t>Lattes S.P 25x40 traitées 2.40m</t>
+  </si>
+  <si>
+    <t>71175236</t>
   </si>
 </sst>
 </file>
@@ -1464,7 +1476,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1483,6 +1495,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1496,7 +1514,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1538,19 +1556,13 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1568,17 +1580,27 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1593,9 +1615,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1938,14 +1957,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065E4AF0-A4F8-4CE3-9E23-EDCEACB756BD}">
-  <dimension ref="A1:G450"/>
+  <dimension ref="A1:G451"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="21" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.77734375" style="5" customWidth="1"/>
   </cols>
@@ -1963,7 +1982,7 @@
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
@@ -1981,14 +2000,14 @@
       <c r="C2" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="25">
         <v>15.44</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="12">
-        <v>118.965</v>
+      <c r="F2" s="26">
+        <v>117.38500000000023</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -2001,13 +2020,13 @@
       <c r="C3" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="25">
         <v>18.73</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2021,14 +2040,14 @@
       <c r="C4" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="25">
         <v>8.81</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="12">
-        <v>228.49899999999914</v>
+      <c r="F4" s="26">
+        <v>343.69899999999916</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -2041,14 +2060,14 @@
       <c r="C5" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D5" s="11">
-        <v>9.98</v>
-      </c>
-      <c r="E5" s="21" t="s">
+      <c r="D5" s="25">
+        <v>10.78</v>
+      </c>
+      <c r="E5" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="12">
-        <v>260.6399999999997</v>
+      <c r="F5" s="26">
+        <v>385.91999999999973</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -2061,14 +2080,14 @@
       <c r="C6" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D6" s="11">
-        <v>12.84</v>
-      </c>
-      <c r="E6" s="21" t="s">
+      <c r="D6" s="25">
+        <v>12.41</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="12">
-        <v>319.67999999999972</v>
+      <c r="F6" s="26">
+        <v>443.51999999999975</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -2081,14 +2100,14 @@
       <c r="C7" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="25">
         <v>15.74</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="12">
-        <v>120.95800000000065</v>
+      <c r="F7" s="26">
+        <v>119.51800000000065</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -2096,13 +2115,13 @@
       <c r="B8" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="25">
         <v>14.71</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="26">
         <v>45</v>
       </c>
     </row>
@@ -2111,14 +2130,14 @@
       <c r="B9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="25">
         <v>21.56</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="12">
-        <v>8.9999999999999964</v>
+      <c r="F9" s="26">
+        <v>-3.5527136788005009E-15</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -2126,13 +2145,13 @@
       <c r="B10" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="25">
         <v>44.06</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="26">
         <v>11.519999999999982</v>
       </c>
     </row>
@@ -2141,13 +2160,13 @@
       <c r="B11" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="25">
         <v>91.48</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2156,13 +2175,13 @@
       <c r="B12" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="25">
         <v>2.31</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2176,13 +2195,13 @@
       <c r="C13" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="25">
         <v>7.79</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="26">
         <v>14.900000000000224</v>
       </c>
     </row>
@@ -2196,14 +2215,14 @@
       <c r="C14" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="25">
         <v>10.83</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="12">
-        <v>33.549999999999834</v>
+      <c r="F14" s="26">
+        <v>32.024999999999835</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2216,14 +2235,14 @@
       <c r="C15" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="25">
         <v>13.94</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="12">
-        <v>30.500000000000217</v>
+      <c r="F15" s="26">
+        <v>12.150000000000212</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -2236,13 +2255,13 @@
       <c r="C16" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="25">
         <v>0</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E16" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2256,14 +2275,14 @@
       <c r="C17" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="25">
         <v>20.09</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="12">
-        <v>3.0549999999981581</v>
+      <c r="F17" s="26">
+        <v>4.9999999981578114E-3</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2276,13 +2295,13 @@
       <c r="C18" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="25">
         <v>16.75</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2296,14 +2315,14 @@
       <c r="C19" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="25">
         <v>19.990000000000002</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E19" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="12">
-        <v>143.34799999999339</v>
+      <c r="F19" s="26">
+        <v>140.29799999999338</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2316,13 +2335,13 @@
       <c r="C20" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="25">
         <v>28.560000000000002</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="26">
         <v>167.15000000000467</v>
       </c>
     </row>
@@ -2336,14 +2355,14 @@
       <c r="C21" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="25">
         <v>28.34</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="12">
-        <v>152.49700000000186</v>
+      <c r="F21" s="26">
+        <v>150.97200000000186</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2356,13 +2375,13 @@
       <c r="C22" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="25">
         <v>54.51</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="26">
         <v>-4.9999999999914557E-3</v>
       </c>
     </row>
@@ -2376,13 +2395,13 @@
       <c r="C23" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="25">
         <v>39.340000000000003</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2396,13 +2415,13 @@
       <c r="C24" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="25">
         <v>9.4500000000000011</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="26">
         <v>35.736999999999895</v>
       </c>
     </row>
@@ -2416,13 +2435,13 @@
       <c r="C25" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="25">
         <v>10.39</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="E25" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2436,13 +2455,13 @@
       <c r="C26" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="25">
         <v>8.98</v>
       </c>
-      <c r="E26" s="21" t="s">
+      <c r="E26" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="26">
         <v>74.247999999999593</v>
       </c>
     </row>
@@ -2456,14 +2475,14 @@
       <c r="C27" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="25">
         <v>10.81</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E27" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="12">
-        <v>148.4970000000001</v>
+      <c r="F27" s="26">
+        <v>145.5270000000001</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2476,13 +2495,13 @@
       <c r="C28" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="25">
         <v>8.8000000000000007</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="E28" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2496,13 +2515,13 @@
       <c r="C29" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="25">
         <v>16.080000000000002</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="26">
         <v>178.6339999999939</v>
       </c>
     </row>
@@ -2516,13 +2535,13 @@
       <c r="C30" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="25">
         <v>15.71</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="E30" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2536,13 +2555,13 @@
       <c r="C31" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="25">
         <v>31.3</v>
       </c>
-      <c r="E31" s="21" t="s">
+      <c r="E31" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2556,13 +2575,13 @@
       <c r="C32" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="25">
         <v>31.3</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2576,14 +2595,14 @@
       <c r="C33" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="25">
         <v>12.98</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F33" s="12">
-        <v>155.54700000000017</v>
+      <c r="F33" s="26">
+        <v>152.56700000000018</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2596,14 +2615,14 @@
       <c r="C34" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="D34" s="11">
-        <v>16.66</v>
-      </c>
-      <c r="E34" s="21" t="s">
+      <c r="D34" s="25">
+        <v>18.11</v>
+      </c>
+      <c r="E34" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="F34" s="12">
-        <v>56.380999999993712</v>
+      <c r="F34" s="26">
+        <v>169.2409999999937</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2616,13 +2635,13 @@
       <c r="C35" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="25">
         <v>18.97</v>
       </c>
-      <c r="E35" s="21" t="s">
+      <c r="E35" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2636,13 +2655,13 @@
       <c r="C36" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="25">
         <v>24.560000000000002</v>
       </c>
-      <c r="E36" s="21" t="s">
+      <c r="E36" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2656,13 +2675,13 @@
       <c r="C37" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="25">
         <v>56.24</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2676,13 +2695,13 @@
       <c r="C38" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="25">
         <v>91.48</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2696,13 +2715,13 @@
       <c r="C39" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="25">
         <v>30.060000000000002</v>
       </c>
-      <c r="E39" s="21" t="s">
+      <c r="E39" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="26">
         <v>87.61900000000422</v>
       </c>
     </row>
@@ -2711,13 +2730,13 @@
       <c r="B40" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="25">
         <v>34.82</v>
       </c>
-      <c r="E40" s="21" t="s">
+      <c r="E40" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F40" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2726,13 +2745,13 @@
       <c r="B41" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="25">
         <v>16.64</v>
       </c>
-      <c r="E41" s="21" t="s">
+      <c r="E41" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="F41" s="12">
+      <c r="F41" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2741,13 +2760,13 @@
       <c r="B42" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="25">
         <v>24.72</v>
       </c>
-      <c r="E42" s="21" t="s">
+      <c r="E42" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="26">
         <v>2.34</v>
       </c>
     </row>
@@ -2756,13 +2775,13 @@
       <c r="B43" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="25">
         <v>25.16</v>
       </c>
-      <c r="E43" s="21" t="s">
+      <c r="E43" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F43" s="12">
+      <c r="F43" s="26">
         <v>4.3964831775156199E-14</v>
       </c>
     </row>
@@ -2771,13 +2790,13 @@
       <c r="B44" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="25">
         <v>28.8</v>
       </c>
-      <c r="E44" s="21" t="s">
+      <c r="E44" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="12">
+      <c r="F44" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2786,13 +2805,13 @@
       <c r="B45" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="25">
         <v>52.6</v>
       </c>
-      <c r="E45" s="21" t="s">
+      <c r="E45" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="F45" s="12">
+      <c r="F45" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2801,13 +2820,13 @@
       <c r="B46" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="25">
         <v>33.380000000000003</v>
       </c>
-      <c r="E46" s="21" t="s">
+      <c r="E46" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2816,13 +2835,13 @@
       <c r="B47" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="25">
         <v>40.730000000000004</v>
       </c>
-      <c r="E47" s="21" t="s">
+      <c r="E47" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="12">
+      <c r="F47" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2831,13 +2850,13 @@
       <c r="B48" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="25">
         <v>85.05</v>
       </c>
-      <c r="E48" s="21" t="s">
+      <c r="E48" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F48" s="12">
+      <c r="F48" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2846,13 +2865,13 @@
       <c r="B49" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="25">
         <v>97.73</v>
       </c>
-      <c r="E49" s="21" t="s">
+      <c r="E49" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F49" s="12">
+      <c r="F49" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2866,14 +2885,14 @@
       <c r="C50" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="D50" s="11">
+      <c r="D50" s="25">
         <v>30.95</v>
       </c>
-      <c r="E50" s="21" t="s">
+      <c r="E50" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F50" s="12">
-        <v>6.2399999999999842</v>
+      <c r="F50" s="26">
+        <v>4.6799999999999837</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -2886,13 +2905,13 @@
       <c r="C51" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D51" s="11">
+      <c r="D51" s="25">
         <v>25.310000000000002</v>
       </c>
-      <c r="E51" s="21" t="s">
+      <c r="E51" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="12">
+      <c r="F51" s="26">
         <v>10.921000000000276</v>
       </c>
     </row>
@@ -2906,14 +2925,14 @@
       <c r="C52" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="25">
         <v>26.55</v>
       </c>
-      <c r="E52" s="21" t="s">
+      <c r="E52" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="12">
-        <v>76.439999999997639</v>
+      <c r="F52" s="26">
+        <v>81.549999999997638</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2926,13 +2945,13 @@
       <c r="C53" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="25">
         <v>37.869999999999997</v>
       </c>
-      <c r="E53" s="21" t="s">
+      <c r="E53" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F53" s="12">
+      <c r="F53" s="26">
         <v>-1.0000000018073329E-3</v>
       </c>
     </row>
@@ -2946,14 +2965,14 @@
       <c r="C54" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="25">
         <v>22.59</v>
       </c>
-      <c r="E54" s="21" t="s">
+      <c r="E54" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="F54" s="12">
-        <v>150.96999999999943</v>
+      <c r="F54" s="26">
+        <v>143.72999999999942</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2966,14 +2985,14 @@
       <c r="C55" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="25">
         <v>33.380000000000003</v>
       </c>
-      <c r="E55" s="21" t="s">
+      <c r="E55" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F55" s="12">
-        <v>140.40000000001157</v>
+      <c r="F55" s="26">
+        <v>105.33000000001158</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2981,13 +3000,13 @@
       <c r="B56" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="25">
         <v>71.77</v>
       </c>
-      <c r="E56" s="21" t="s">
+      <c r="E56" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F56" s="12">
+      <c r="F56" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2996,13 +3015,13 @@
       <c r="B57" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="25">
         <v>68.930000000000007</v>
       </c>
-      <c r="E57" s="21" t="s">
+      <c r="E57" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F57" s="12">
+      <c r="F57" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3016,13 +3035,13 @@
       <c r="C58" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="25">
         <v>47.94</v>
       </c>
-      <c r="E58" s="21" t="s">
+      <c r="E58" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F58" s="12">
+      <c r="F58" s="26">
         <v>62.399999999999942</v>
       </c>
     </row>
@@ -3036,13 +3055,13 @@
       <c r="C59" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D59" s="11">
+      <c r="D59" s="25">
         <v>25.18</v>
       </c>
-      <c r="E59" s="21" t="s">
+      <c r="E59" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="F59" s="12">
+      <c r="F59" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3056,13 +3075,13 @@
       <c r="C60" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="25">
         <v>39.07</v>
       </c>
-      <c r="E60" s="21" t="s">
+      <c r="E60" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="F60" s="12">
+      <c r="F60" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3076,13 +3095,13 @@
       <c r="C61" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="25">
         <v>42.52</v>
       </c>
-      <c r="E61" s="21" t="s">
+      <c r="E61" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F61" s="12">
+      <c r="F61" s="26">
         <v>-4.9999999997818456E-3</v>
       </c>
     </row>
@@ -3096,13 +3115,13 @@
       <c r="C62" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D62" s="11">
+      <c r="D62" s="25">
         <v>39.910000000000004</v>
       </c>
-      <c r="E62" s="21" t="s">
+      <c r="E62" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="F62" s="12">
+      <c r="F62" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3111,13 +3130,13 @@
       <c r="B63" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="25">
         <v>33.730000000000004</v>
       </c>
-      <c r="E63" s="21" t="s">
+      <c r="E63" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="F63" s="12">
+      <c r="F63" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3131,17 +3150,17 @@
       <c r="C64" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D64" s="11">
+      <c r="D64" s="25">
         <v>38.94</v>
       </c>
-      <c r="E64" s="21" t="s">
+      <c r="E64" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="F64" s="12">
+      <c r="F64" s="26">
         <v>12.200000000000017</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>312</v>
       </c>
@@ -3151,92 +3170,92 @@
       <c r="C65" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="D65" s="11">
+      <c r="D65" s="25">
         <v>46.37</v>
       </c>
-      <c r="E65" s="21" t="s">
+      <c r="E65" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="F65" s="12">
+      <c r="F65" s="26">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="15">
+      <c r="D66" s="25">
         <v>59.300000000000004</v>
       </c>
-      <c r="E66" s="22" t="s">
+      <c r="E66" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F66" s="17">
+      <c r="F66" s="26">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D67" s="15">
+      <c r="D67" s="25">
         <v>88.92</v>
       </c>
-      <c r="E67" s="22" t="s">
+      <c r="E67" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="F67" s="17">
+      <c r="F67" s="26">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D68" s="15">
+      <c r="D68" s="25">
         <v>118.54</v>
       </c>
-      <c r="E68" s="22" t="s">
+      <c r="E68" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F68" s="17">
+      <c r="F68" s="26">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="D69" s="15">
+      <c r="D69" s="25">
         <v>185.26</v>
       </c>
-      <c r="E69" s="22" t="s">
+      <c r="E69" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F69" s="17">
+      <c r="F69" s="26">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="D70" s="15">
+      <c r="D70" s="25">
         <v>222.33</v>
       </c>
-      <c r="E70" s="22" t="s">
+      <c r="E70" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="17">
+      <c r="F70" s="26">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="13" t="s">
         <v>143</v>
@@ -3244,97 +3263,103 @@
       <c r="C71" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="D71" s="11">
+      <c r="D71" s="27">
         <v>0.69000000000000006</v>
       </c>
-      <c r="E71" s="21" t="s">
+      <c r="E71" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="F71" s="12">
+      <c r="F71" s="33">
         <v>576.00000000000136</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G71" s="31"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
-      <c r="B72" s="18" t="s">
+      <c r="B72" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D72" s="11">
+      <c r="D72" s="27">
         <v>0.54</v>
       </c>
-      <c r="E72" s="21" t="s">
+      <c r="E72" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="F72" s="12">
+      <c r="F72" s="33">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G72" s="31"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
-      <c r="B73" s="18" t="s">
+      <c r="B73" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="27">
         <v>0.35000000000000003</v>
       </c>
-      <c r="E73" s="21" t="s">
+      <c r="E73" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="F73" s="12">
+      <c r="F73" s="33">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G73" s="31"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
-      <c r="B74" s="18" t="s">
+      <c r="B74" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D74" s="11">
+      <c r="D74" s="27">
         <v>0.28000000000000003</v>
       </c>
-      <c r="E74" s="21" t="s">
+      <c r="E74" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="F74" s="12">
+      <c r="F74" s="33">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G74" s="31"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
-      <c r="B75" s="18" t="s">
+      <c r="B75" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D75" s="11">
+      <c r="D75" s="27">
         <v>0.64</v>
       </c>
-      <c r="E75" s="21" t="s">
+      <c r="E75" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="F75" s="12">
+      <c r="F75" s="33">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G75" s="31"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B76" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C76" s="19" t="s">
+      <c r="C76" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="D76" s="11">
+      <c r="D76" s="27">
         <v>1.33</v>
       </c>
-      <c r="E76" s="21" t="s">
+      <c r="E76" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="F76" s="12">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F76" s="33">
+        <v>179</v>
+      </c>
+      <c r="G76" s="31"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>303</v>
       </c>
@@ -3344,37 +3369,39 @@
       <c r="C77" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D77" s="11">
+      <c r="D77" s="27">
         <v>1.49</v>
       </c>
-      <c r="E77" s="21" t="s">
+      <c r="E77" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="F77" s="12">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F77" s="33">
+        <v>151</v>
+      </c>
+      <c r="G77" s="31"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B78" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="C78" s="19" t="s">
+      <c r="C78" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="D78" s="11">
+      <c r="D78" s="27">
         <v>1.6300000000000001</v>
       </c>
-      <c r="E78" s="21" t="s">
+      <c r="E78" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="F78" s="12">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F78" s="33">
+        <v>302</v>
+      </c>
+      <c r="G78" s="31"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>303</v>
       </c>
@@ -3384,37 +3411,39 @@
       <c r="C79" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="D79" s="11">
+      <c r="D79" s="27">
         <v>1.82</v>
       </c>
-      <c r="E79" s="21" t="s">
+      <c r="E79" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="F79" s="12">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F79" s="33">
+        <v>101</v>
+      </c>
+      <c r="G79" s="31"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B80" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C80" s="19" t="s">
+      <c r="C80" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="D80" s="11">
+      <c r="D80" s="27">
         <v>1.96</v>
       </c>
-      <c r="E80" s="21" t="s">
+      <c r="E80" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="F80" s="12">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F80" s="33">
+        <v>59</v>
+      </c>
+      <c r="G80" s="31"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>303</v>
       </c>
@@ -3424,37 +3453,39 @@
       <c r="C81" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="D81" s="11">
+      <c r="D81" s="27">
         <v>2.13</v>
       </c>
-      <c r="E81" s="21" t="s">
+      <c r="E81" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="F81" s="12">
+      <c r="F81" s="33">
         <v>156</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G81" s="31"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B82" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="C82" s="19" t="s">
+      <c r="C82" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="D82" s="11">
+      <c r="D82" s="27">
         <v>2.29</v>
       </c>
-      <c r="E82" s="21" t="s">
+      <c r="E82" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="F82" s="12">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F82" s="33">
+        <v>138</v>
+      </c>
+      <c r="G82" s="31"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>303</v>
       </c>
@@ -3464,904 +3495,950 @@
       <c r="C83" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D83" s="27">
         <v>2.4700000000000002</v>
       </c>
-      <c r="E83" s="21" t="s">
+      <c r="E83" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="F83" s="12">
+      <c r="F83" s="33">
         <v>2</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G83" s="31"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B84" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C84" s="19" t="s">
+      <c r="C84" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="D84" s="11">
+      <c r="D84" s="27">
         <v>2.61</v>
       </c>
-      <c r="E84" s="21" t="s">
+      <c r="E84" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="F84" s="12">
+      <c r="F84" s="33">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G84" s="31"/>
+    </row>
+    <row r="85" spans="1:7" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D85" s="11">
-        <v>1.98</v>
-      </c>
-      <c r="E85" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="F85" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+        <v>463</v>
+      </c>
+      <c r="C85" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="D85" s="32">
+        <v>1.33</v>
+      </c>
+      <c r="E85" s="30" t="s">
+        <v>461</v>
+      </c>
+      <c r="F85" s="33">
+        <v>167</v>
+      </c>
+      <c r="G85" s="31"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D86" s="11">
-        <v>2.38</v>
-      </c>
-      <c r="E86" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="F86" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+        <v>367</v>
+      </c>
+      <c r="D86" s="27">
+        <v>1.59</v>
+      </c>
+      <c r="E86" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="F86" s="33">
+        <v>-3</v>
+      </c>
+      <c r="G86" s="31"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B87" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D87" s="27">
+        <v>1.98</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="F87" s="33">
+        <v>0</v>
+      </c>
+      <c r="G87" s="31"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B88" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D87" s="11">
+      <c r="D88" s="27">
+        <v>2.38</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="F88" s="33">
+        <v>-10</v>
+      </c>
+      <c r="G88" s="31"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="5"/>
+      <c r="B89" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D89" s="27">
         <v>2.7600000000000002</v>
       </c>
-      <c r="E87" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="F87" s="12">
+      <c r="E89" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="F89" s="33">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="5"/>
-      <c r="B88" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="D88" s="11">
-        <v>1.31</v>
-      </c>
-      <c r="E88" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="F88" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="B89" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D89" s="11">
-        <v>3.12</v>
-      </c>
-      <c r="E89" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="F89" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G89" s="31"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D90" s="11">
-        <v>3.5100000000000002</v>
-      </c>
-      <c r="E90" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="F90" s="12">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+      <c r="D90" s="27">
+        <v>1.31</v>
+      </c>
+      <c r="E90" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="F90" s="33">
+        <v>-11</v>
+      </c>
+      <c r="G90" s="31"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D91" s="11">
-        <v>3.91</v>
-      </c>
-      <c r="E91" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="F91" s="12">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+        <v>361</v>
+      </c>
+      <c r="D91" s="27">
+        <v>3.12</v>
+      </c>
+      <c r="E91" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="F91" s="33">
+        <v>50</v>
+      </c>
+      <c r="G91" s="31"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D92" s="11">
-        <v>4.3100000000000005</v>
-      </c>
-      <c r="E92" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="F92" s="12">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+        <v>363</v>
+      </c>
+      <c r="D92" s="27">
+        <v>3.5100000000000002</v>
+      </c>
+      <c r="E92" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="F92" s="33">
+        <v>7</v>
+      </c>
+      <c r="G92" s="31"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D93" s="11">
-        <v>4.68</v>
-      </c>
-      <c r="E93" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="F93" s="12">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+        <v>365</v>
+      </c>
+      <c r="D93" s="27">
+        <v>3.91</v>
+      </c>
+      <c r="E93" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="F93" s="33">
+        <v>112</v>
+      </c>
+      <c r="G93" s="31"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D94" s="11">
-        <v>5.07</v>
-      </c>
-      <c r="E94" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="F94" s="12">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+        <v>370</v>
+      </c>
+      <c r="D94" s="27">
+        <v>4.3100000000000005</v>
+      </c>
+      <c r="E94" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F94" s="33">
+        <v>74</v>
+      </c>
+      <c r="G94" s="31"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="D95" s="11">
-        <v>5.47</v>
-      </c>
-      <c r="E95" s="21" t="s">
-        <v>223</v>
-      </c>
-      <c r="F95" s="12">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+        <v>371</v>
+      </c>
+      <c r="D95" s="27">
+        <v>4.68</v>
+      </c>
+      <c r="E95" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="F95" s="33">
+        <v>75</v>
+      </c>
+      <c r="G95" s="31"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B96" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D96" s="27">
+        <v>5.07</v>
+      </c>
+      <c r="E96" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="F96" s="33">
+        <v>124</v>
+      </c>
+      <c r="G96" s="31"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B97" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C97" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D96" s="11">
+      <c r="D97" s="27">
+        <v>5.47</v>
+      </c>
+      <c r="E97" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="F97" s="33">
+        <v>28</v>
+      </c>
+      <c r="G97" s="31"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="5"/>
+      <c r="B98" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D98" s="27">
         <v>5.87</v>
       </c>
-      <c r="E96" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="F96" s="12">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="5"/>
-      <c r="B97" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="D97" s="11">
-        <v>1.69</v>
-      </c>
-      <c r="E97" s="21" t="s">
+      <c r="E98" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="F97" s="12">
+      <c r="F98" s="33">
         <v>91</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="B98" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D98" s="11">
-        <v>3.98</v>
-      </c>
-      <c r="E98" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="F98" s="12">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G98" s="31"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="D99" s="11">
-        <v>5.12</v>
-      </c>
-      <c r="E99" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="F99" s="12">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+        <v>376</v>
+      </c>
+      <c r="D99" s="27">
+        <v>1.69</v>
+      </c>
+      <c r="E99" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="F99" s="33">
+        <v>77</v>
+      </c>
+      <c r="G99" s="31"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="D100" s="11">
-        <v>5.94</v>
-      </c>
-      <c r="E100" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="F100" s="12">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+        <v>378</v>
+      </c>
+      <c r="D100" s="27">
+        <v>3.98</v>
+      </c>
+      <c r="E100" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="F100" s="33">
+        <v>60</v>
+      </c>
+      <c r="G100" s="31"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B101" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D101" s="27">
+        <v>5.12</v>
+      </c>
+      <c r="E101" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="F101" s="33">
+        <v>52</v>
+      </c>
+      <c r="G101" s="31"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B102" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C102" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="D101" s="11">
+      <c r="D102" s="27">
+        <v>5.94</v>
+      </c>
+      <c r="E102" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="F102" s="33">
+        <v>58</v>
+      </c>
+      <c r="G102" s="31"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="5"/>
+      <c r="B103" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D103" s="27">
         <v>6.92</v>
       </c>
-      <c r="E101" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="F101" s="12">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="5"/>
-      <c r="B102" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="D102" s="11">
-        <v>2.13</v>
-      </c>
-      <c r="E102" s="21" t="s">
+      <c r="E103" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="F102" s="12">
+      <c r="F103" s="33">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B103" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="D103" s="11">
-        <v>5.1100000000000003</v>
-      </c>
-      <c r="E103" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="F103" s="12">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G103" s="31"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>302</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="D104" s="11">
-        <v>5.76</v>
-      </c>
-      <c r="E104" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="F104" s="12">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+        <v>377</v>
+      </c>
+      <c r="D104" s="27">
+        <v>2.13</v>
+      </c>
+      <c r="E104" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F104" s="33">
+        <v>21</v>
+      </c>
+      <c r="G104" s="31"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>302</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="D105" s="11">
-        <v>6.3900000000000006</v>
-      </c>
-      <c r="E105" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="F105" s="12">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+      <c r="D105" s="27">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="E105" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="F105" s="33">
+        <v>130</v>
+      </c>
+      <c r="G105" s="31"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>302</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="D106" s="11">
-        <v>7.03</v>
-      </c>
-      <c r="E106" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="F106" s="12">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+        <v>393</v>
+      </c>
+      <c r="D106" s="27">
+        <v>5.76</v>
+      </c>
+      <c r="E106" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="F106" s="33">
+        <v>66</v>
+      </c>
+      <c r="G106" s="31"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>302</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D107" s="11">
-        <v>7.68</v>
-      </c>
-      <c r="E107" s="21" t="s">
-        <v>235</v>
-      </c>
-      <c r="F107" s="12">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+        <v>394</v>
+      </c>
+      <c r="D107" s="27">
+        <v>6.3900000000000006</v>
+      </c>
+      <c r="E107" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="F107" s="33">
+        <v>47</v>
+      </c>
+      <c r="G107" s="31"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>302</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="D108" s="11">
-        <v>8.31</v>
-      </c>
-      <c r="E108" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="F108" s="12">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+        <v>395</v>
+      </c>
+      <c r="D108" s="27">
+        <v>7.03</v>
+      </c>
+      <c r="E108" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="F108" s="33">
+        <v>104</v>
+      </c>
+      <c r="G108" s="31"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>302</v>
       </c>
       <c r="B109" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D109" s="11">
-        <v>8.9500000000000011</v>
-      </c>
-      <c r="E109" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="F109" s="12">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+        <v>396</v>
+      </c>
+      <c r="D109" s="27">
+        <v>7.68</v>
+      </c>
+      <c r="E109" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="F109" s="33">
+        <v>169</v>
+      </c>
+      <c r="G109" s="31"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>302</v>
       </c>
       <c r="B110" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D110" s="27">
+        <v>8.31</v>
+      </c>
+      <c r="E110" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="F110" s="33">
+        <v>23</v>
+      </c>
+      <c r="G110" s="31"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B111" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C111" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D110" s="11">
+      <c r="D111" s="27">
+        <v>8.9500000000000011</v>
+      </c>
+      <c r="E111" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="F111" s="33">
+        <v>8</v>
+      </c>
+      <c r="G111" s="31"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="5"/>
+      <c r="B112" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="D112" s="27">
         <v>9.61</v>
       </c>
-      <c r="E110" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="F110" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="5"/>
-      <c r="B111" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="D111" s="11">
-        <v>4.2700000000000005</v>
-      </c>
-      <c r="E111" s="21" t="s">
+      <c r="E112" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="F111" s="12">
+      <c r="F112" s="33">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="B112" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="D112" s="11">
-        <v>10.220000000000001</v>
-      </c>
-      <c r="E112" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="F112" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G112" s="31"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D113" s="11">
-        <v>11.5</v>
-      </c>
-      <c r="E113" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="F113" s="12">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+        <v>384</v>
+      </c>
+      <c r="D113" s="27">
+        <v>4.2700000000000005</v>
+      </c>
+      <c r="E113" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="F113" s="33">
+        <v>10</v>
+      </c>
+      <c r="G113" s="31"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="D114" s="11">
-        <v>12.780000000000001</v>
-      </c>
-      <c r="E114" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="F114" s="12">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+        <v>385</v>
+      </c>
+      <c r="D114" s="27">
+        <v>10.220000000000001</v>
+      </c>
+      <c r="E114" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="F114" s="33">
+        <v>18</v>
+      </c>
+      <c r="G114" s="31"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="D115" s="11">
-        <v>14.07</v>
-      </c>
-      <c r="E115" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="F115" s="12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+        <v>386</v>
+      </c>
+      <c r="D115" s="27">
+        <v>11.5</v>
+      </c>
+      <c r="E115" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="F115" s="33">
+        <v>16</v>
+      </c>
+      <c r="G115" s="31"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="D116" s="11">
-        <v>15.34</v>
-      </c>
-      <c r="E116" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="F116" s="12">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+        <v>387</v>
+      </c>
+      <c r="D116" s="27">
+        <v>12.780000000000001</v>
+      </c>
+      <c r="E116" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="F116" s="33">
+        <v>2</v>
+      </c>
+      <c r="G116" s="31"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D117" s="11">
-        <v>16.61</v>
-      </c>
-      <c r="E117" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="F117" s="12">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+        <v>388</v>
+      </c>
+      <c r="D117" s="27">
+        <v>14.07</v>
+      </c>
+      <c r="E117" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="F117" s="33">
+        <v>16</v>
+      </c>
+      <c r="G117" s="31"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D118" s="11">
-        <v>17.88</v>
-      </c>
-      <c r="E118" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="F118" s="12">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+        <v>389</v>
+      </c>
+      <c r="D118" s="27">
+        <v>15.34</v>
+      </c>
+      <c r="E118" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="F118" s="33">
+        <v>32</v>
+      </c>
+      <c r="G118" s="31"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B119" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D119" s="27">
+        <v>16.61</v>
+      </c>
+      <c r="E119" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="F119" s="33">
+        <v>25</v>
+      </c>
+      <c r="G119" s="31"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B120" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C120" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="D119" s="11">
+      <c r="D120" s="27">
+        <v>17.88</v>
+      </c>
+      <c r="E120" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="F120" s="33">
+        <v>11</v>
+      </c>
+      <c r="G120" s="31"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" s="5"/>
+      <c r="B121" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D121" s="27">
         <v>19.12</v>
       </c>
-      <c r="E119" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="F119" s="12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="5"/>
-      <c r="B120" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="D120" s="11">
-        <v>8.02</v>
-      </c>
-      <c r="E120" s="21" t="s">
+      <c r="E121" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="F120" s="12">
+      <c r="F121" s="33">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="B121" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D121" s="11">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="E121" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="F121" s="12">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G121" s="31"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D122" s="11">
-        <v>22.64</v>
-      </c>
-      <c r="E122" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="F122" s="12">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+        <v>392</v>
+      </c>
+      <c r="D122" s="27">
+        <v>8.02</v>
+      </c>
+      <c r="E122" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="F122" s="33">
+        <v>18</v>
+      </c>
+      <c r="G122" s="31"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D123" s="11">
-        <v>27.150000000000002</v>
-      </c>
-      <c r="E123" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="F123" s="12">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+        <v>399</v>
+      </c>
+      <c r="D123" s="27">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E123" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="F123" s="33">
+        <v>26</v>
+      </c>
+      <c r="G123" s="31"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D124" s="11">
-        <v>31.69</v>
-      </c>
-      <c r="E124" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="F124" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+      <c r="D124" s="27">
+        <v>22.64</v>
+      </c>
+      <c r="E124" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="F124" s="33">
+        <v>23</v>
+      </c>
+      <c r="G124" s="31"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="D125" s="11">
-        <v>33.94</v>
-      </c>
-      <c r="E125" s="21" t="s">
-        <v>253</v>
-      </c>
-      <c r="F125" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+        <v>401</v>
+      </c>
+      <c r="D125" s="27">
+        <v>27.150000000000002</v>
+      </c>
+      <c r="E125" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="F125" s="33">
+        <v>15</v>
+      </c>
+      <c r="G125" s="31"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B126" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D126" s="27">
+        <v>31.69</v>
+      </c>
+      <c r="E126" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="F126" s="33">
+        <v>0</v>
+      </c>
+      <c r="G126" s="31"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B127" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C127" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="D126" s="11">
+      <c r="D127" s="27">
+        <v>33.94</v>
+      </c>
+      <c r="E127" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="F127" s="33">
+        <v>0</v>
+      </c>
+      <c r="G127" s="31"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="5"/>
+      <c r="B128" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="D128" s="27">
         <v>36.22</v>
       </c>
-      <c r="E126" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="F126" s="12">
+      <c r="E128" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="F128" s="28">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="5"/>
-      <c r="B127" s="16" t="s">
-        <v>278</v>
-      </c>
-      <c r="D127" s="11">
-        <v>2.15</v>
-      </c>
-      <c r="E127" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="F127" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B128" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="D128" s="11">
-        <v>5.12</v>
-      </c>
-      <c r="E128" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="F128" s="12">
-        <v>0</v>
-      </c>
+      <c r="G128" s="30"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D129" s="11">
-        <v>4.07</v>
-      </c>
-      <c r="E129" s="21" t="s">
-        <v>257</v>
-      </c>
-      <c r="F129" s="12">
-        <v>379</v>
+        <v>404</v>
+      </c>
+      <c r="D129" s="34">
+        <v>5.12</v>
+      </c>
+      <c r="E129" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="F129" s="35">
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
@@ -4369,19 +4446,19 @@
         <v>309</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="D130" s="11">
-        <v>4.53</v>
-      </c>
-      <c r="E130" s="21" t="s">
-        <v>258</v>
-      </c>
-      <c r="F130" s="12">
-        <v>69</v>
+        <v>405</v>
+      </c>
+      <c r="D130" s="34">
+        <v>4.07</v>
+      </c>
+      <c r="E130" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="F130" s="35">
+        <v>302</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
@@ -4389,19 +4466,19 @@
         <v>309</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D131" s="11">
-        <v>6.7</v>
-      </c>
-      <c r="E131" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="F131" s="12">
-        <v>224</v>
+        <v>406</v>
+      </c>
+      <c r="D131" s="34">
+        <v>4.53</v>
+      </c>
+      <c r="E131" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="F131" s="35">
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
@@ -4409,19 +4486,19 @@
         <v>309</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D132" s="11">
-        <v>8.31</v>
-      </c>
-      <c r="E132" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="F132" s="12">
-        <v>0</v>
+        <v>407</v>
+      </c>
+      <c r="D132" s="34">
+        <v>6.7</v>
+      </c>
+      <c r="E132" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="F132" s="35">
+        <v>221</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
@@ -4429,19 +4506,19 @@
         <v>309</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D133" s="11">
-        <v>7.8900000000000006</v>
-      </c>
-      <c r="E133" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="F133" s="12">
-        <v>390</v>
+        <v>408</v>
+      </c>
+      <c r="D133" s="34">
+        <v>8.31</v>
+      </c>
+      <c r="E133" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="F133" s="35">
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
@@ -4449,54 +4526,54 @@
         <v>309</v>
       </c>
       <c r="B134" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D134" s="34">
+        <v>7.8900000000000006</v>
+      </c>
+      <c r="E134" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="F134" s="35">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B135" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C135" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="D134" s="11">
+      <c r="D135" s="34">
         <v>9.61</v>
       </c>
-      <c r="E134" s="21" t="s">
+      <c r="E135" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="F134" s="12">
+      <c r="F135" s="35">
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="5"/>
-      <c r="B135" s="16" t="s">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="5"/>
+      <c r="B136" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="D135" s="11">
+      <c r="D136" s="34">
         <v>3.5500000000000003</v>
       </c>
-      <c r="E135" s="21" t="s">
+      <c r="E136" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="F135" s="12">
+      <c r="F136" s="35">
         <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B136" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="D136" s="11">
-        <v>6.22</v>
-      </c>
-      <c r="E136" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="F136" s="12">
-        <v>387</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
@@ -4504,19 +4581,19 @@
         <v>309</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="D137" s="11">
-        <v>6.91</v>
-      </c>
-      <c r="E137" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="F137" s="12">
-        <v>246</v>
+        <v>411</v>
+      </c>
+      <c r="D137" s="34">
+        <v>6.22</v>
+      </c>
+      <c r="E137" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="F137" s="35">
+        <v>351</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
@@ -4524,19 +4601,19 @@
         <v>309</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="D138" s="11">
-        <v>10.91</v>
-      </c>
-      <c r="E138" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="F138" s="12">
-        <v>0</v>
+        <v>418</v>
+      </c>
+      <c r="D138" s="34">
+        <v>6.91</v>
+      </c>
+      <c r="E138" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="F138" s="35">
+        <v>162</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
@@ -4544,19 +4621,19 @@
         <v>309</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D139" s="11">
-        <v>10.370000000000001</v>
-      </c>
-      <c r="E139" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="F139" s="12">
-        <v>223</v>
+        <v>419</v>
+      </c>
+      <c r="D139" s="34">
+        <v>10.91</v>
+      </c>
+      <c r="E139" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="F139" s="35">
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
@@ -4564,19 +4641,19 @@
         <v>309</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D140" s="11">
-        <v>13.88</v>
-      </c>
-      <c r="E140" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="F140" s="12">
-        <v>173</v>
+        <v>420</v>
+      </c>
+      <c r="D140" s="34">
+        <v>10.370000000000001</v>
+      </c>
+      <c r="E140" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="F140" s="35">
+        <v>223</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
@@ -4584,19 +4661,19 @@
         <v>309</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D141" s="11">
-        <v>9.23</v>
-      </c>
-      <c r="E141" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="F141" s="12">
-        <v>0</v>
+        <v>421</v>
+      </c>
+      <c r="D141" s="34">
+        <v>13.88</v>
+      </c>
+      <c r="E141" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="F141" s="35">
+        <v>143</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
@@ -4604,53 +4681,53 @@
         <v>309</v>
       </c>
       <c r="B142" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D142" s="34">
+        <v>9.23</v>
+      </c>
+      <c r="E142" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="F142" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B143" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="C143" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D142" s="11">
+      <c r="D143" s="34">
         <v>11.14</v>
       </c>
-      <c r="E142" s="21" t="s">
+      <c r="E143" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="F142" s="12">
+      <c r="F143" s="35">
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="5"/>
-      <c r="B143" s="16" t="s">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="5"/>
+      <c r="B144" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="D143" s="11">
+      <c r="D144" s="34">
         <v>3.17</v>
       </c>
-      <c r="E143" s="21" t="s">
+      <c r="E144" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="F143" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B144" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="D144" s="11">
-        <v>7.2</v>
-      </c>
-      <c r="E144" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="F144" s="12">
+      <c r="F144" s="35">
         <v>0</v>
       </c>
     </row>
@@ -4659,18 +4736,18 @@
         <v>309</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="D145" s="11">
-        <v>18.11</v>
-      </c>
-      <c r="E145" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="F145" s="12">
+        <v>412</v>
+      </c>
+      <c r="D145" s="34">
+        <v>7.2</v>
+      </c>
+      <c r="E145" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="F145" s="35">
         <v>0</v>
       </c>
     </row>
@@ -4679,19 +4756,19 @@
         <v>309</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="D146" s="11">
-        <v>11.94</v>
-      </c>
-      <c r="E146" s="21" t="s">
-        <v>274</v>
-      </c>
-      <c r="F146" s="12">
-        <v>99</v>
+        <v>413</v>
+      </c>
+      <c r="D146" s="34">
+        <v>18.11</v>
+      </c>
+      <c r="E146" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="F146" s="35">
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
@@ -4699,19 +4776,19 @@
         <v>309</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D147" s="11">
-        <v>15.16</v>
-      </c>
-      <c r="E147" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="F147" s="12">
-        <v>47</v>
+        <v>414</v>
+      </c>
+      <c r="D147" s="34">
+        <v>11.94</v>
+      </c>
+      <c r="E147" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="F147" s="35">
+        <v>99</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
@@ -4719,19 +4796,19 @@
         <v>309</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="D148" s="11">
-        <v>13.52</v>
-      </c>
-      <c r="E148" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="F148" s="12">
-        <v>108</v>
+        <v>415</v>
+      </c>
+      <c r="D148" s="34">
+        <v>15.16</v>
+      </c>
+      <c r="E148" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="F148" s="35">
+        <v>47</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
@@ -4739,255 +4816,267 @@
         <v>309</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D149" s="11">
-        <v>24.89</v>
-      </c>
-      <c r="E149" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="F149" s="12">
-        <v>0</v>
+        <v>416</v>
+      </c>
+      <c r="D149" s="34">
+        <v>13.52</v>
+      </c>
+      <c r="E149" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="F149" s="35">
+        <v>106</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="B150" s="28" t="s">
-        <v>424</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="D150" s="26">
-        <v>7.8</v>
-      </c>
-      <c r="E150" s="21">
-        <v>71175236</v>
-      </c>
-      <c r="F150" s="24">
-        <v>5</v>
+        <v>309</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D150" s="34">
+        <v>24.89</v>
+      </c>
+      <c r="E150" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="F150" s="35">
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="B151" s="13" t="s">
-        <v>425</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="D151" s="25">
-        <v>18.150000000000002</v>
-      </c>
-      <c r="E151" s="29" t="s">
-        <v>426</v>
-      </c>
-      <c r="F151" s="27">
-        <v>3</v>
+        <v>445</v>
+      </c>
+      <c r="B151" s="23" t="s">
+        <v>424</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="D151" s="12">
+        <v>7.8</v>
+      </c>
+      <c r="E151" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="F151" s="22">
+        <v>4</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="B152" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="D152" s="30">
-        <v>23.8</v>
-      </c>
-      <c r="E152" s="21" t="s">
-        <v>427</v>
-      </c>
-      <c r="F152" s="31">
+        <v>446</v>
+      </c>
+      <c r="B152" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D152" s="11">
+        <v>18.150000000000002</v>
+      </c>
+      <c r="E152" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="F152" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="D153" s="32">
-        <v>18.22</v>
-      </c>
-      <c r="E153" s="21" t="s">
-        <v>429</v>
-      </c>
-      <c r="F153" s="33">
-        <v>24</v>
+        <v>459</v>
+      </c>
+      <c r="D153" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="E153" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="F153" s="12">
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="B154" s="9" t="s">
-        <v>431</v>
+        <v>448</v>
+      </c>
+      <c r="B154" s="24" t="s">
+        <v>430</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="D154" s="35">
-        <v>9.82</v>
-      </c>
-      <c r="E154" s="34" t="s">
-        <v>438</v>
-      </c>
-      <c r="F154" s="36">
-        <v>2</v>
+        <v>457</v>
+      </c>
+      <c r="D154" s="11">
+        <v>18.22</v>
+      </c>
+      <c r="E154" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="F154" s="12">
+        <v>16</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C155" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D155" s="35">
+      <c r="D155" s="36">
         <v>9.82</v>
       </c>
-      <c r="E155" s="34" t="s">
-        <v>439</v>
-      </c>
-      <c r="F155" s="36">
-        <v>0</v>
+      <c r="E155" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="F155" s="37">
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="5" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C156" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D156" s="35">
+      <c r="D156" s="36">
         <v>9.82</v>
       </c>
-      <c r="E156" s="34" t="s">
-        <v>440</v>
-      </c>
-      <c r="F156" s="36">
-        <v>1</v>
+      <c r="E156" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="F156" s="37">
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D157" s="35">
+      <c r="D157" s="36">
         <v>9.82</v>
       </c>
-      <c r="E157" s="34" t="s">
-        <v>441</v>
-      </c>
-      <c r="F157" s="36">
-        <v>2</v>
+      <c r="E157" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="F157" s="37">
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B158" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D158" s="35">
+      <c r="D158" s="36">
         <v>9.82</v>
       </c>
-      <c r="E158" s="34" t="s">
-        <v>442</v>
-      </c>
-      <c r="F158" s="36">
-        <v>0</v>
+      <c r="E158" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="F158" s="37">
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B159" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C159" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D159" s="35">
+      <c r="D159" s="36">
         <v>9.82</v>
       </c>
-      <c r="E159" s="34" t="s">
-        <v>443</v>
-      </c>
-      <c r="F159" s="36">
-        <v>1</v>
+      <c r="E159" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="F159" s="37">
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="B160" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="D160" s="36">
+        <v>9.82</v>
+      </c>
+      <c r="E160" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="F160" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="B160" s="9" t="s">
+      <c r="B161" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="C160" s="5" t="s">
+      <c r="C161" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="D160" s="35">
+      <c r="D161" s="36">
         <v>6.3</v>
       </c>
-      <c r="E160" s="34" t="s">
+      <c r="E161" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="F160" s="36">
+      <c r="F161" s="37">
         <v>4</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A161" s="5"/>
-      <c r="B161" s="5"/>
-      <c r="C161" s="5"/>
-      <c r="D161" s="5"/>
-      <c r="E161" s="21"/>
-      <c r="F161" s="5"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
       <c r="D162" s="5"/>
-      <c r="E162" s="21"/>
+      <c r="E162" s="19"/>
       <c r="F162" s="5"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
@@ -4995,7 +5084,7 @@
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
       <c r="D163" s="5"/>
-      <c r="E163" s="21"/>
+      <c r="E163" s="19"/>
       <c r="F163" s="5"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
@@ -5003,7 +5092,7 @@
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
       <c r="D164" s="5"/>
-      <c r="E164" s="21"/>
+      <c r="E164" s="19"/>
       <c r="F164" s="5"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
@@ -5011,7 +5100,7 @@
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
       <c r="D165" s="5"/>
-      <c r="E165" s="21"/>
+      <c r="E165" s="19"/>
       <c r="F165" s="5"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
@@ -5019,7 +5108,7 @@
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
       <c r="D166" s="5"/>
-      <c r="E166" s="21"/>
+      <c r="E166" s="19"/>
       <c r="F166" s="5"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
@@ -5027,7 +5116,7 @@
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
       <c r="D167" s="5"/>
-      <c r="E167" s="21"/>
+      <c r="E167" s="19"/>
       <c r="F167" s="5"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
@@ -5035,7 +5124,7 @@
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
       <c r="D168" s="5"/>
-      <c r="E168" s="21"/>
+      <c r="E168" s="19"/>
       <c r="F168" s="5"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
@@ -5043,7 +5132,7 @@
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
       <c r="D169" s="5"/>
-      <c r="E169" s="21"/>
+      <c r="E169" s="19"/>
       <c r="F169" s="5"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
@@ -5051,7 +5140,7 @@
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
       <c r="D170" s="5"/>
-      <c r="E170" s="21"/>
+      <c r="E170" s="19"/>
       <c r="F170" s="5"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
@@ -5059,7 +5148,7 @@
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
       <c r="D171" s="5"/>
-      <c r="E171" s="21"/>
+      <c r="E171" s="19"/>
       <c r="F171" s="5"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
@@ -5067,7 +5156,7 @@
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
       <c r="D172" s="5"/>
-      <c r="E172" s="21"/>
+      <c r="E172" s="19"/>
       <c r="F172" s="5"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
@@ -5075,7 +5164,7 @@
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
       <c r="D173" s="5"/>
-      <c r="E173" s="21"/>
+      <c r="E173" s="19"/>
       <c r="F173" s="5"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
@@ -5083,7 +5172,7 @@
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
       <c r="D174" s="5"/>
-      <c r="E174" s="21"/>
+      <c r="E174" s="19"/>
       <c r="F174" s="5"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
@@ -5091,7 +5180,7 @@
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
       <c r="D175" s="5"/>
-      <c r="E175" s="21"/>
+      <c r="E175" s="19"/>
       <c r="F175" s="5"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
@@ -5099,7 +5188,7 @@
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
       <c r="D176" s="5"/>
-      <c r="E176" s="21"/>
+      <c r="E176" s="19"/>
       <c r="F176" s="5"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
@@ -5107,7 +5196,7 @@
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
       <c r="D177" s="5"/>
-      <c r="E177" s="21"/>
+      <c r="E177" s="19"/>
       <c r="F177" s="5"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
@@ -5115,7 +5204,7 @@
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
       <c r="D178" s="5"/>
-      <c r="E178" s="21"/>
+      <c r="E178" s="19"/>
       <c r="F178" s="5"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
@@ -5123,7 +5212,7 @@
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
       <c r="D179" s="5"/>
-      <c r="E179" s="21"/>
+      <c r="E179" s="19"/>
       <c r="F179" s="5"/>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
@@ -5131,7 +5220,7 @@
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
       <c r="D180" s="5"/>
-      <c r="E180" s="21"/>
+      <c r="E180" s="19"/>
       <c r="F180" s="5"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
@@ -5139,7 +5228,7 @@
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
       <c r="D181" s="5"/>
-      <c r="E181" s="21"/>
+      <c r="E181" s="19"/>
       <c r="F181" s="5"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
@@ -5147,7 +5236,7 @@
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
       <c r="D182" s="5"/>
-      <c r="E182" s="21"/>
+      <c r="E182" s="19"/>
       <c r="F182" s="5"/>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
@@ -5155,7 +5244,7 @@
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
       <c r="D183" s="5"/>
-      <c r="E183" s="21"/>
+      <c r="E183" s="19"/>
       <c r="F183" s="5"/>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
@@ -5163,7 +5252,7 @@
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
       <c r="D184" s="5"/>
-      <c r="E184" s="21"/>
+      <c r="E184" s="19"/>
       <c r="F184" s="5"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
@@ -5171,7 +5260,7 @@
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
       <c r="D185" s="5"/>
-      <c r="E185" s="21"/>
+      <c r="E185" s="19"/>
       <c r="F185" s="5"/>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
@@ -5179,7 +5268,7 @@
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
       <c r="D186" s="5"/>
-      <c r="E186" s="21"/>
+      <c r="E186" s="19"/>
       <c r="F186" s="5"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
@@ -5187,7 +5276,7 @@
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
       <c r="D187" s="5"/>
-      <c r="E187" s="21"/>
+      <c r="E187" s="19"/>
       <c r="F187" s="5"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
@@ -5195,7 +5284,7 @@
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
       <c r="D188" s="5"/>
-      <c r="E188" s="21"/>
+      <c r="E188" s="19"/>
       <c r="F188" s="5"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
@@ -5203,7 +5292,7 @@
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
       <c r="D189" s="5"/>
-      <c r="E189" s="21"/>
+      <c r="E189" s="19"/>
       <c r="F189" s="5"/>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
@@ -5211,7 +5300,7 @@
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
       <c r="D190" s="5"/>
-      <c r="E190" s="21"/>
+      <c r="E190" s="19"/>
       <c r="F190" s="5"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
@@ -5219,7 +5308,7 @@
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
       <c r="D191" s="5"/>
-      <c r="E191" s="21"/>
+      <c r="E191" s="19"/>
       <c r="F191" s="5"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
@@ -5227,7 +5316,7 @@
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
       <c r="D192" s="5"/>
-      <c r="E192" s="21"/>
+      <c r="E192" s="19"/>
       <c r="F192" s="5"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
@@ -5235,7 +5324,7 @@
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
       <c r="D193" s="5"/>
-      <c r="E193" s="21"/>
+      <c r="E193" s="19"/>
       <c r="F193" s="5"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
@@ -5243,7 +5332,7 @@
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
       <c r="D194" s="5"/>
-      <c r="E194" s="21"/>
+      <c r="E194" s="19"/>
       <c r="F194" s="5"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
@@ -5251,7 +5340,7 @@
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
       <c r="D195" s="5"/>
-      <c r="E195" s="21"/>
+      <c r="E195" s="19"/>
       <c r="F195" s="5"/>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
@@ -5259,7 +5348,7 @@
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
       <c r="D196" s="5"/>
-      <c r="E196" s="21"/>
+      <c r="E196" s="19"/>
       <c r="F196" s="5"/>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
@@ -5267,7 +5356,7 @@
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
       <c r="D197" s="5"/>
-      <c r="E197" s="21"/>
+      <c r="E197" s="19"/>
       <c r="F197" s="5"/>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
@@ -5275,7 +5364,7 @@
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
       <c r="D198" s="5"/>
-      <c r="E198" s="21"/>
+      <c r="E198" s="19"/>
       <c r="F198" s="5"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
@@ -5283,7 +5372,7 @@
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
       <c r="D199" s="5"/>
-      <c r="E199" s="21"/>
+      <c r="E199" s="19"/>
       <c r="F199" s="5"/>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
@@ -5291,7 +5380,7 @@
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
       <c r="D200" s="5"/>
-      <c r="E200" s="21"/>
+      <c r="E200" s="19"/>
       <c r="F200" s="5"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
@@ -5299,7 +5388,7 @@
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
       <c r="D201" s="5"/>
-      <c r="E201" s="21"/>
+      <c r="E201" s="19"/>
       <c r="F201" s="5"/>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
@@ -5307,7 +5396,7 @@
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
       <c r="D202" s="5"/>
-      <c r="E202" s="21"/>
+      <c r="E202" s="19"/>
       <c r="F202" s="5"/>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
@@ -5315,7 +5404,7 @@
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
       <c r="D203" s="5"/>
-      <c r="E203" s="21"/>
+      <c r="E203" s="19"/>
       <c r="F203" s="5"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
@@ -5323,7 +5412,7 @@
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
       <c r="D204" s="5"/>
-      <c r="E204" s="21"/>
+      <c r="E204" s="19"/>
       <c r="F204" s="5"/>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
@@ -5331,7 +5420,7 @@
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
       <c r="D205" s="5"/>
-      <c r="E205" s="21"/>
+      <c r="E205" s="19"/>
       <c r="F205" s="5"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
@@ -5339,7 +5428,7 @@
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
       <c r="D206" s="5"/>
-      <c r="E206" s="21"/>
+      <c r="E206" s="19"/>
       <c r="F206" s="5"/>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
@@ -5347,7 +5436,7 @@
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
       <c r="D207" s="5"/>
-      <c r="E207" s="21"/>
+      <c r="E207" s="19"/>
       <c r="F207" s="5"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
@@ -5355,7 +5444,7 @@
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
       <c r="D208" s="5"/>
-      <c r="E208" s="21"/>
+      <c r="E208" s="19"/>
       <c r="F208" s="5"/>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
@@ -5363,7 +5452,7 @@
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
       <c r="D209" s="5"/>
-      <c r="E209" s="21"/>
+      <c r="E209" s="19"/>
       <c r="F209" s="5"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
@@ -5371,7 +5460,7 @@
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
       <c r="D210" s="5"/>
-      <c r="E210" s="21"/>
+      <c r="E210" s="19"/>
       <c r="F210" s="5"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
@@ -5379,7 +5468,7 @@
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
       <c r="D211" s="5"/>
-      <c r="E211" s="21"/>
+      <c r="E211" s="19"/>
       <c r="F211" s="5"/>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
@@ -5387,7 +5476,7 @@
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
       <c r="D212" s="5"/>
-      <c r="E212" s="21"/>
+      <c r="E212" s="19"/>
       <c r="F212" s="5"/>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
@@ -5395,7 +5484,7 @@
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
       <c r="D213" s="5"/>
-      <c r="E213" s="21"/>
+      <c r="E213" s="19"/>
       <c r="F213" s="5"/>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
@@ -5403,7 +5492,7 @@
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
       <c r="D214" s="5"/>
-      <c r="E214" s="21"/>
+      <c r="E214" s="19"/>
       <c r="F214" s="5"/>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
@@ -5411,7 +5500,7 @@
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
       <c r="D215" s="5"/>
-      <c r="E215" s="21"/>
+      <c r="E215" s="19"/>
       <c r="F215" s="5"/>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
@@ -5419,7 +5508,7 @@
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
       <c r="D216" s="5"/>
-      <c r="E216" s="21"/>
+      <c r="E216" s="19"/>
       <c r="F216" s="5"/>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
@@ -5427,7 +5516,7 @@
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
       <c r="D217" s="5"/>
-      <c r="E217" s="21"/>
+      <c r="E217" s="19"/>
       <c r="F217" s="5"/>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
@@ -5435,7 +5524,7 @@
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
       <c r="D218" s="5"/>
-      <c r="E218" s="21"/>
+      <c r="E218" s="19"/>
       <c r="F218" s="5"/>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
@@ -5443,7 +5532,7 @@
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
       <c r="D219" s="5"/>
-      <c r="E219" s="21"/>
+      <c r="E219" s="19"/>
       <c r="F219" s="5"/>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
@@ -5451,7 +5540,7 @@
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
       <c r="D220" s="5"/>
-      <c r="E220" s="21"/>
+      <c r="E220" s="19"/>
       <c r="F220" s="5"/>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
@@ -5459,7 +5548,7 @@
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
       <c r="D221" s="5"/>
-      <c r="E221" s="21"/>
+      <c r="E221" s="19"/>
       <c r="F221" s="5"/>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
@@ -5467,7 +5556,7 @@
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
       <c r="D222" s="5"/>
-      <c r="E222" s="21"/>
+      <c r="E222" s="19"/>
       <c r="F222" s="5"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
@@ -5475,7 +5564,7 @@
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
       <c r="D223" s="5"/>
-      <c r="E223" s="21"/>
+      <c r="E223" s="19"/>
       <c r="F223" s="5"/>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
@@ -5483,7 +5572,7 @@
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
       <c r="D224" s="5"/>
-      <c r="E224" s="21"/>
+      <c r="E224" s="19"/>
       <c r="F224" s="5"/>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
@@ -5491,7 +5580,7 @@
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
       <c r="D225" s="5"/>
-      <c r="E225" s="21"/>
+      <c r="E225" s="19"/>
       <c r="F225" s="5"/>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
@@ -5499,7 +5588,7 @@
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
       <c r="D226" s="5"/>
-      <c r="E226" s="21"/>
+      <c r="E226" s="19"/>
       <c r="F226" s="5"/>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
@@ -5507,7 +5596,7 @@
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
       <c r="D227" s="5"/>
-      <c r="E227" s="21"/>
+      <c r="E227" s="19"/>
       <c r="F227" s="5"/>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
@@ -5515,7 +5604,7 @@
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
       <c r="D228" s="5"/>
-      <c r="E228" s="21"/>
+      <c r="E228" s="19"/>
       <c r="F228" s="5"/>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
@@ -5523,7 +5612,7 @@
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
       <c r="D229" s="5"/>
-      <c r="E229" s="21"/>
+      <c r="E229" s="19"/>
       <c r="F229" s="5"/>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
@@ -5531,7 +5620,7 @@
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
       <c r="D230" s="5"/>
-      <c r="E230" s="21"/>
+      <c r="E230" s="19"/>
       <c r="F230" s="5"/>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
@@ -5539,7 +5628,7 @@
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
       <c r="D231" s="5"/>
-      <c r="E231" s="21"/>
+      <c r="E231" s="19"/>
       <c r="F231" s="5"/>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
@@ -5547,7 +5636,7 @@
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
       <c r="D232" s="5"/>
-      <c r="E232" s="21"/>
+      <c r="E232" s="19"/>
       <c r="F232" s="5"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
@@ -5555,7 +5644,7 @@
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
       <c r="D233" s="5"/>
-      <c r="E233" s="21"/>
+      <c r="E233" s="19"/>
       <c r="F233" s="5"/>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
@@ -5563,7 +5652,7 @@
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
       <c r="D234" s="5"/>
-      <c r="E234" s="21"/>
+      <c r="E234" s="19"/>
       <c r="F234" s="5"/>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
@@ -5571,7 +5660,7 @@
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
       <c r="D235" s="5"/>
-      <c r="E235" s="21"/>
+      <c r="E235" s="19"/>
       <c r="F235" s="5"/>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
@@ -5579,7 +5668,7 @@
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
       <c r="D236" s="5"/>
-      <c r="E236" s="21"/>
+      <c r="E236" s="19"/>
       <c r="F236" s="5"/>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
@@ -5587,7 +5676,7 @@
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
       <c r="D237" s="5"/>
-      <c r="E237" s="21"/>
+      <c r="E237" s="19"/>
       <c r="F237" s="5"/>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
@@ -5595,7 +5684,7 @@
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
       <c r="D238" s="5"/>
-      <c r="E238" s="21"/>
+      <c r="E238" s="19"/>
       <c r="F238" s="5"/>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
@@ -5603,7 +5692,7 @@
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
       <c r="D239" s="5"/>
-      <c r="E239" s="21"/>
+      <c r="E239" s="19"/>
       <c r="F239" s="5"/>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
@@ -5611,7 +5700,7 @@
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
       <c r="D240" s="5"/>
-      <c r="E240" s="21"/>
+      <c r="E240" s="19"/>
       <c r="F240" s="5"/>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
@@ -5619,7 +5708,7 @@
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
       <c r="D241" s="5"/>
-      <c r="E241" s="21"/>
+      <c r="E241" s="19"/>
       <c r="F241" s="5"/>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
@@ -5627,7 +5716,7 @@
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
       <c r="D242" s="5"/>
-      <c r="E242" s="21"/>
+      <c r="E242" s="19"/>
       <c r="F242" s="5"/>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
@@ -5635,7 +5724,7 @@
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
       <c r="D243" s="5"/>
-      <c r="E243" s="21"/>
+      <c r="E243" s="19"/>
       <c r="F243" s="5"/>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
@@ -5643,7 +5732,7 @@
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
       <c r="D244" s="5"/>
-      <c r="E244" s="21"/>
+      <c r="E244" s="19"/>
       <c r="F244" s="5"/>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
@@ -5651,7 +5740,7 @@
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
       <c r="D245" s="5"/>
-      <c r="E245" s="21"/>
+      <c r="E245" s="19"/>
       <c r="F245" s="5"/>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
@@ -5659,7 +5748,7 @@
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
       <c r="D246" s="5"/>
-      <c r="E246" s="21"/>
+      <c r="E246" s="19"/>
       <c r="F246" s="5"/>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
@@ -5667,7 +5756,7 @@
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
       <c r="D247" s="5"/>
-      <c r="E247" s="21"/>
+      <c r="E247" s="19"/>
       <c r="F247" s="5"/>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
@@ -5675,7 +5764,7 @@
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
       <c r="D248" s="5"/>
-      <c r="E248" s="21"/>
+      <c r="E248" s="19"/>
       <c r="F248" s="5"/>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
@@ -5683,7 +5772,7 @@
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
       <c r="D249" s="5"/>
-      <c r="E249" s="21"/>
+      <c r="E249" s="19"/>
       <c r="F249" s="5"/>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
@@ -5691,7 +5780,7 @@
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
       <c r="D250" s="5"/>
-      <c r="E250" s="21"/>
+      <c r="E250" s="19"/>
       <c r="F250" s="5"/>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
@@ -5699,7 +5788,7 @@
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
       <c r="D251" s="5"/>
-      <c r="E251" s="21"/>
+      <c r="E251" s="19"/>
       <c r="F251" s="5"/>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
@@ -5707,7 +5796,7 @@
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
       <c r="D252" s="5"/>
-      <c r="E252" s="21"/>
+      <c r="E252" s="19"/>
       <c r="F252" s="5"/>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
@@ -5715,7 +5804,7 @@
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
       <c r="D253" s="5"/>
-      <c r="E253" s="21"/>
+      <c r="E253" s="19"/>
       <c r="F253" s="5"/>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
@@ -5723,7 +5812,7 @@
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
       <c r="D254" s="5"/>
-      <c r="E254" s="21"/>
+      <c r="E254" s="19"/>
       <c r="F254" s="5"/>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
@@ -5731,7 +5820,7 @@
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
       <c r="D255" s="5"/>
-      <c r="E255" s="21"/>
+      <c r="E255" s="19"/>
       <c r="F255" s="5"/>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
@@ -5739,7 +5828,7 @@
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
       <c r="D256" s="5"/>
-      <c r="E256" s="21"/>
+      <c r="E256" s="19"/>
       <c r="F256" s="5"/>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
@@ -5747,7 +5836,7 @@
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
       <c r="D257" s="5"/>
-      <c r="E257" s="21"/>
+      <c r="E257" s="19"/>
       <c r="F257" s="5"/>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
@@ -5755,7 +5844,7 @@
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
       <c r="D258" s="5"/>
-      <c r="E258" s="21"/>
+      <c r="E258" s="19"/>
       <c r="F258" s="5"/>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
@@ -5763,7 +5852,7 @@
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
       <c r="D259" s="5"/>
-      <c r="E259" s="21"/>
+      <c r="E259" s="19"/>
       <c r="F259" s="5"/>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
@@ -5771,7 +5860,7 @@
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
       <c r="D260" s="5"/>
-      <c r="E260" s="21"/>
+      <c r="E260" s="19"/>
       <c r="F260" s="5"/>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
@@ -5779,7 +5868,7 @@
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
       <c r="D261" s="5"/>
-      <c r="E261" s="21"/>
+      <c r="E261" s="19"/>
       <c r="F261" s="5"/>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
@@ -5787,7 +5876,7 @@
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
       <c r="D262" s="5"/>
-      <c r="E262" s="21"/>
+      <c r="E262" s="19"/>
       <c r="F262" s="5"/>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
@@ -5795,7 +5884,7 @@
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
       <c r="D263" s="5"/>
-      <c r="E263" s="21"/>
+      <c r="E263" s="19"/>
       <c r="F263" s="5"/>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
@@ -5803,7 +5892,7 @@
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
       <c r="D264" s="5"/>
-      <c r="E264" s="21"/>
+      <c r="E264" s="19"/>
       <c r="F264" s="5"/>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
@@ -5811,7 +5900,7 @@
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
       <c r="D265" s="5"/>
-      <c r="E265" s="21"/>
+      <c r="E265" s="19"/>
       <c r="F265" s="5"/>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
@@ -5819,7 +5908,7 @@
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
       <c r="D266" s="5"/>
-      <c r="E266" s="21"/>
+      <c r="E266" s="19"/>
       <c r="F266" s="5"/>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
@@ -5827,7 +5916,7 @@
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
       <c r="D267" s="5"/>
-      <c r="E267" s="21"/>
+      <c r="E267" s="19"/>
       <c r="F267" s="5"/>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
@@ -5835,7 +5924,7 @@
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
       <c r="D268" s="5"/>
-      <c r="E268" s="21"/>
+      <c r="E268" s="19"/>
       <c r="F268" s="5"/>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
@@ -5843,7 +5932,7 @@
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
       <c r="D269" s="5"/>
-      <c r="E269" s="21"/>
+      <c r="E269" s="19"/>
       <c r="F269" s="5"/>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
@@ -5851,7 +5940,7 @@
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
       <c r="D270" s="5"/>
-      <c r="E270" s="21"/>
+      <c r="E270" s="19"/>
       <c r="F270" s="5"/>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
@@ -5859,7 +5948,7 @@
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
       <c r="D271" s="5"/>
-      <c r="E271" s="21"/>
+      <c r="E271" s="19"/>
       <c r="F271" s="5"/>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
@@ -5867,7 +5956,7 @@
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
       <c r="D272" s="5"/>
-      <c r="E272" s="21"/>
+      <c r="E272" s="19"/>
       <c r="F272" s="5"/>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
@@ -5875,7 +5964,7 @@
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
       <c r="D273" s="5"/>
-      <c r="E273" s="21"/>
+      <c r="E273" s="19"/>
       <c r="F273" s="5"/>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
@@ -5883,7 +5972,7 @@
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
       <c r="D274" s="5"/>
-      <c r="E274" s="21"/>
+      <c r="E274" s="19"/>
       <c r="F274" s="5"/>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
@@ -5891,7 +5980,7 @@
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
       <c r="D275" s="5"/>
-      <c r="E275" s="21"/>
+      <c r="E275" s="19"/>
       <c r="F275" s="5"/>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
@@ -5899,7 +5988,7 @@
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
       <c r="D276" s="5"/>
-      <c r="E276" s="21"/>
+      <c r="E276" s="19"/>
       <c r="F276" s="5"/>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
@@ -5907,7 +5996,7 @@
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
       <c r="D277" s="5"/>
-      <c r="E277" s="21"/>
+      <c r="E277" s="19"/>
       <c r="F277" s="5"/>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
@@ -5915,7 +6004,7 @@
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
       <c r="D278" s="5"/>
-      <c r="E278" s="21"/>
+      <c r="E278" s="19"/>
       <c r="F278" s="5"/>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
@@ -5923,7 +6012,7 @@
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
       <c r="D279" s="5"/>
-      <c r="E279" s="21"/>
+      <c r="E279" s="19"/>
       <c r="F279" s="5"/>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
@@ -5931,7 +6020,7 @@
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
       <c r="D280" s="5"/>
-      <c r="E280" s="21"/>
+      <c r="E280" s="19"/>
       <c r="F280" s="5"/>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
@@ -5939,7 +6028,7 @@
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
       <c r="D281" s="5"/>
-      <c r="E281" s="21"/>
+      <c r="E281" s="19"/>
       <c r="F281" s="5"/>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
@@ -5947,7 +6036,7 @@
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
       <c r="D282" s="5"/>
-      <c r="E282" s="21"/>
+      <c r="E282" s="19"/>
       <c r="F282" s="5"/>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
@@ -5955,7 +6044,7 @@
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
       <c r="D283" s="5"/>
-      <c r="E283" s="21"/>
+      <c r="E283" s="19"/>
       <c r="F283" s="5"/>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
@@ -5963,7 +6052,7 @@
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
       <c r="D284" s="5"/>
-      <c r="E284" s="21"/>
+      <c r="E284" s="19"/>
       <c r="F284" s="5"/>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
@@ -5971,7 +6060,7 @@
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
       <c r="D285" s="5"/>
-      <c r="E285" s="21"/>
+      <c r="E285" s="19"/>
       <c r="F285" s="5"/>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
@@ -5979,7 +6068,7 @@
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
       <c r="D286" s="5"/>
-      <c r="E286" s="21"/>
+      <c r="E286" s="19"/>
       <c r="F286" s="5"/>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
@@ -5987,7 +6076,7 @@
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
       <c r="D287" s="5"/>
-      <c r="E287" s="21"/>
+      <c r="E287" s="19"/>
       <c r="F287" s="5"/>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
@@ -5995,7 +6084,7 @@
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
       <c r="D288" s="5"/>
-      <c r="E288" s="21"/>
+      <c r="E288" s="19"/>
       <c r="F288" s="5"/>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
@@ -6003,7 +6092,7 @@
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
       <c r="D289" s="5"/>
-      <c r="E289" s="21"/>
+      <c r="E289" s="19"/>
       <c r="F289" s="5"/>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
@@ -6011,7 +6100,7 @@
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
       <c r="D290" s="5"/>
-      <c r="E290" s="21"/>
+      <c r="E290" s="19"/>
       <c r="F290" s="5"/>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
@@ -6019,7 +6108,7 @@
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
       <c r="D291" s="5"/>
-      <c r="E291" s="21"/>
+      <c r="E291" s="19"/>
       <c r="F291" s="5"/>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
@@ -6027,7 +6116,7 @@
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
       <c r="D292" s="5"/>
-      <c r="E292" s="21"/>
+      <c r="E292" s="19"/>
       <c r="F292" s="5"/>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
@@ -6035,7 +6124,7 @@
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
       <c r="D293" s="5"/>
-      <c r="E293" s="21"/>
+      <c r="E293" s="19"/>
       <c r="F293" s="5"/>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
@@ -6043,7 +6132,7 @@
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
       <c r="D294" s="5"/>
-      <c r="E294" s="21"/>
+      <c r="E294" s="19"/>
       <c r="F294" s="5"/>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
@@ -6051,7 +6140,7 @@
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
       <c r="D295" s="5"/>
-      <c r="E295" s="21"/>
+      <c r="E295" s="19"/>
       <c r="F295" s="5"/>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
@@ -6059,7 +6148,7 @@
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
       <c r="D296" s="5"/>
-      <c r="E296" s="21"/>
+      <c r="E296" s="19"/>
       <c r="F296" s="5"/>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
@@ -6067,7 +6156,7 @@
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
       <c r="D297" s="5"/>
-      <c r="E297" s="21"/>
+      <c r="E297" s="19"/>
       <c r="F297" s="5"/>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
@@ -6075,7 +6164,7 @@
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
       <c r="D298" s="5"/>
-      <c r="E298" s="21"/>
+      <c r="E298" s="19"/>
       <c r="F298" s="5"/>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
@@ -6083,7 +6172,7 @@
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
       <c r="D299" s="5"/>
-      <c r="E299" s="21"/>
+      <c r="E299" s="19"/>
       <c r="F299" s="5"/>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
@@ -6091,7 +6180,7 @@
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
       <c r="D300" s="5"/>
-      <c r="E300" s="21"/>
+      <c r="E300" s="19"/>
       <c r="F300" s="5"/>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
@@ -6099,7 +6188,7 @@
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
       <c r="D301" s="5"/>
-      <c r="E301" s="21"/>
+      <c r="E301" s="19"/>
       <c r="F301" s="5"/>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
@@ -6107,7 +6196,7 @@
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
       <c r="D302" s="5"/>
-      <c r="E302" s="21"/>
+      <c r="E302" s="19"/>
       <c r="F302" s="5"/>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
@@ -6115,7 +6204,7 @@
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
       <c r="D303" s="5"/>
-      <c r="E303" s="21"/>
+      <c r="E303" s="19"/>
       <c r="F303" s="5"/>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
@@ -6123,7 +6212,7 @@
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
       <c r="D304" s="5"/>
-      <c r="E304" s="21"/>
+      <c r="E304" s="19"/>
       <c r="F304" s="5"/>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
@@ -6131,7 +6220,7 @@
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
       <c r="D305" s="5"/>
-      <c r="E305" s="21"/>
+      <c r="E305" s="19"/>
       <c r="F305" s="5"/>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
@@ -6139,7 +6228,7 @@
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
       <c r="D306" s="5"/>
-      <c r="E306" s="21"/>
+      <c r="E306" s="19"/>
       <c r="F306" s="5"/>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
@@ -6147,7 +6236,7 @@
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
       <c r="D307" s="5"/>
-      <c r="E307" s="21"/>
+      <c r="E307" s="19"/>
       <c r="F307" s="5"/>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
@@ -6155,7 +6244,7 @@
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
       <c r="D308" s="5"/>
-      <c r="E308" s="21"/>
+      <c r="E308" s="19"/>
       <c r="F308" s="5"/>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
@@ -6163,7 +6252,7 @@
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
       <c r="D309" s="5"/>
-      <c r="E309" s="21"/>
+      <c r="E309" s="19"/>
       <c r="F309" s="5"/>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
@@ -6171,7 +6260,7 @@
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
       <c r="D310" s="5"/>
-      <c r="E310" s="21"/>
+      <c r="E310" s="19"/>
       <c r="F310" s="5"/>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
@@ -6179,7 +6268,7 @@
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
       <c r="D311" s="5"/>
-      <c r="E311" s="21"/>
+      <c r="E311" s="19"/>
       <c r="F311" s="5"/>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
@@ -6187,7 +6276,7 @@
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
       <c r="D312" s="5"/>
-      <c r="E312" s="21"/>
+      <c r="E312" s="19"/>
       <c r="F312" s="5"/>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.3">
@@ -6195,7 +6284,7 @@
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
       <c r="D313" s="5"/>
-      <c r="E313" s="21"/>
+      <c r="E313" s="19"/>
       <c r="F313" s="5"/>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
@@ -6203,7 +6292,7 @@
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
       <c r="D314" s="5"/>
-      <c r="E314" s="21"/>
+      <c r="E314" s="19"/>
       <c r="F314" s="5"/>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
@@ -6211,7 +6300,7 @@
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
       <c r="D315" s="5"/>
-      <c r="E315" s="21"/>
+      <c r="E315" s="19"/>
       <c r="F315" s="5"/>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
@@ -6219,7 +6308,7 @@
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
       <c r="D316" s="5"/>
-      <c r="E316" s="21"/>
+      <c r="E316" s="19"/>
       <c r="F316" s="5"/>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
@@ -6227,7 +6316,7 @@
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
       <c r="D317" s="5"/>
-      <c r="E317" s="21"/>
+      <c r="E317" s="19"/>
       <c r="F317" s="5"/>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
@@ -6235,7 +6324,7 @@
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
       <c r="D318" s="5"/>
-      <c r="E318" s="21"/>
+      <c r="E318" s="19"/>
       <c r="F318" s="5"/>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
@@ -6243,7 +6332,7 @@
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
       <c r="D319" s="5"/>
-      <c r="E319" s="21"/>
+      <c r="E319" s="19"/>
       <c r="F319" s="5"/>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
@@ -6251,7 +6340,7 @@
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
       <c r="D320" s="5"/>
-      <c r="E320" s="21"/>
+      <c r="E320" s="19"/>
       <c r="F320" s="5"/>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
@@ -6259,7 +6348,7 @@
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
       <c r="D321" s="5"/>
-      <c r="E321" s="21"/>
+      <c r="E321" s="19"/>
       <c r="F321" s="5"/>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
@@ -6267,7 +6356,7 @@
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
       <c r="D322" s="5"/>
-      <c r="E322" s="21"/>
+      <c r="E322" s="19"/>
       <c r="F322" s="5"/>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
@@ -6275,7 +6364,7 @@
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
       <c r="D323" s="5"/>
-      <c r="E323" s="21"/>
+      <c r="E323" s="19"/>
       <c r="F323" s="5"/>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
@@ -6283,7 +6372,7 @@
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
       <c r="D324" s="5"/>
-      <c r="E324" s="21"/>
+      <c r="E324" s="19"/>
       <c r="F324" s="5"/>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
@@ -6291,7 +6380,7 @@
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
       <c r="D325" s="5"/>
-      <c r="E325" s="21"/>
+      <c r="E325" s="19"/>
       <c r="F325" s="5"/>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
@@ -6299,7 +6388,7 @@
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
       <c r="D326" s="5"/>
-      <c r="E326" s="21"/>
+      <c r="E326" s="19"/>
       <c r="F326" s="5"/>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
@@ -6307,7 +6396,7 @@
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
       <c r="D327" s="5"/>
-      <c r="E327" s="21"/>
+      <c r="E327" s="19"/>
       <c r="F327" s="5"/>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
@@ -6315,7 +6404,7 @@
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
       <c r="D328" s="5"/>
-      <c r="E328" s="21"/>
+      <c r="E328" s="19"/>
       <c r="F328" s="5"/>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
@@ -6323,7 +6412,7 @@
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
       <c r="D329" s="5"/>
-      <c r="E329" s="21"/>
+      <c r="E329" s="19"/>
       <c r="F329" s="5"/>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
@@ -6331,7 +6420,7 @@
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
       <c r="D330" s="5"/>
-      <c r="E330" s="21"/>
+      <c r="E330" s="19"/>
       <c r="F330" s="5"/>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
@@ -6339,7 +6428,7 @@
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
       <c r="D331" s="5"/>
-      <c r="E331" s="21"/>
+      <c r="E331" s="19"/>
       <c r="F331" s="5"/>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
@@ -6347,7 +6436,7 @@
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
       <c r="D332" s="5"/>
-      <c r="E332" s="21"/>
+      <c r="E332" s="19"/>
       <c r="F332" s="5"/>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
@@ -6355,7 +6444,7 @@
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
       <c r="D333" s="5"/>
-      <c r="E333" s="21"/>
+      <c r="E333" s="19"/>
       <c r="F333" s="5"/>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
@@ -6363,7 +6452,7 @@
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
       <c r="D334" s="5"/>
-      <c r="E334" s="21"/>
+      <c r="E334" s="19"/>
       <c r="F334" s="5"/>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
@@ -6371,7 +6460,7 @@
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
       <c r="D335" s="5"/>
-      <c r="E335" s="21"/>
+      <c r="E335" s="19"/>
       <c r="F335" s="5"/>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.3">
@@ -6379,7 +6468,7 @@
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
       <c r="D336" s="5"/>
-      <c r="E336" s="21"/>
+      <c r="E336" s="19"/>
       <c r="F336" s="5"/>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.3">
@@ -6387,7 +6476,7 @@
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
       <c r="D337" s="5"/>
-      <c r="E337" s="21"/>
+      <c r="E337" s="19"/>
       <c r="F337" s="5"/>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.3">
@@ -6395,7 +6484,7 @@
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
       <c r="D338" s="5"/>
-      <c r="E338" s="21"/>
+      <c r="E338" s="19"/>
       <c r="F338" s="5"/>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.3">
@@ -6403,7 +6492,7 @@
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
       <c r="D339" s="5"/>
-      <c r="E339" s="21"/>
+      <c r="E339" s="19"/>
       <c r="F339" s="5"/>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.3">
@@ -6411,7 +6500,7 @@
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
       <c r="D340" s="5"/>
-      <c r="E340" s="21"/>
+      <c r="E340" s="19"/>
       <c r="F340" s="5"/>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.3">
@@ -6419,7 +6508,7 @@
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
       <c r="D341" s="5"/>
-      <c r="E341" s="21"/>
+      <c r="E341" s="19"/>
       <c r="F341" s="5"/>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.3">
@@ -6427,7 +6516,7 @@
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
       <c r="D342" s="5"/>
-      <c r="E342" s="21"/>
+      <c r="E342" s="19"/>
       <c r="F342" s="5"/>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.3">
@@ -6435,7 +6524,7 @@
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
       <c r="D343" s="5"/>
-      <c r="E343" s="21"/>
+      <c r="E343" s="19"/>
       <c r="F343" s="5"/>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.3">
@@ -6443,7 +6532,7 @@
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
       <c r="D344" s="5"/>
-      <c r="E344" s="21"/>
+      <c r="E344" s="19"/>
       <c r="F344" s="5"/>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.3">
@@ -6451,7 +6540,7 @@
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
       <c r="D345" s="5"/>
-      <c r="E345" s="21"/>
+      <c r="E345" s="19"/>
       <c r="F345" s="5"/>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.3">
@@ -6459,7 +6548,7 @@
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
       <c r="D346" s="5"/>
-      <c r="E346" s="21"/>
+      <c r="E346" s="19"/>
       <c r="F346" s="5"/>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.3">
@@ -6467,7 +6556,7 @@
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
       <c r="D347" s="5"/>
-      <c r="E347" s="21"/>
+      <c r="E347" s="19"/>
       <c r="F347" s="5"/>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.3">
@@ -6475,7 +6564,7 @@
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
       <c r="D348" s="5"/>
-      <c r="E348" s="21"/>
+      <c r="E348" s="19"/>
       <c r="F348" s="5"/>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.3">
@@ -6483,7 +6572,7 @@
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
       <c r="D349" s="5"/>
-      <c r="E349" s="21"/>
+      <c r="E349" s="19"/>
       <c r="F349" s="5"/>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.3">
@@ -6491,7 +6580,7 @@
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
       <c r="D350" s="5"/>
-      <c r="E350" s="21"/>
+      <c r="E350" s="19"/>
       <c r="F350" s="5"/>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.3">
@@ -6499,7 +6588,7 @@
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
       <c r="D351" s="5"/>
-      <c r="E351" s="21"/>
+      <c r="E351" s="19"/>
       <c r="F351" s="5"/>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.3">
@@ -6507,7 +6596,7 @@
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
       <c r="D352" s="5"/>
-      <c r="E352" s="21"/>
+      <c r="E352" s="19"/>
       <c r="F352" s="5"/>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.3">
@@ -6515,7 +6604,7 @@
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
       <c r="D353" s="5"/>
-      <c r="E353" s="21"/>
+      <c r="E353" s="19"/>
       <c r="F353" s="5"/>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.3">
@@ -6523,7 +6612,7 @@
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
       <c r="D354" s="5"/>
-      <c r="E354" s="21"/>
+      <c r="E354" s="19"/>
       <c r="F354" s="5"/>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.3">
@@ -6531,7 +6620,7 @@
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
       <c r="D355" s="5"/>
-      <c r="E355" s="21"/>
+      <c r="E355" s="19"/>
       <c r="F355" s="5"/>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.3">
@@ -6539,7 +6628,7 @@
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
       <c r="D356" s="5"/>
-      <c r="E356" s="21"/>
+      <c r="E356" s="19"/>
       <c r="F356" s="5"/>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.3">
@@ -6547,7 +6636,7 @@
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
       <c r="D357" s="5"/>
-      <c r="E357" s="21"/>
+      <c r="E357" s="19"/>
       <c r="F357" s="5"/>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.3">
@@ -6555,7 +6644,7 @@
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
       <c r="D358" s="5"/>
-      <c r="E358" s="21"/>
+      <c r="E358" s="19"/>
       <c r="F358" s="5"/>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.3">
@@ -6563,7 +6652,7 @@
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
       <c r="D359" s="5"/>
-      <c r="E359" s="21"/>
+      <c r="E359" s="19"/>
       <c r="F359" s="5"/>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.3">
@@ -6571,7 +6660,7 @@
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
       <c r="D360" s="5"/>
-      <c r="E360" s="21"/>
+      <c r="E360" s="19"/>
       <c r="F360" s="5"/>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.3">
@@ -6579,7 +6668,7 @@
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
       <c r="D361" s="5"/>
-      <c r="E361" s="21"/>
+      <c r="E361" s="19"/>
       <c r="F361" s="5"/>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.3">
@@ -6587,7 +6676,7 @@
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
       <c r="D362" s="5"/>
-      <c r="E362" s="21"/>
+      <c r="E362" s="19"/>
       <c r="F362" s="5"/>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.3">
@@ -6595,7 +6684,7 @@
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
       <c r="D363" s="5"/>
-      <c r="E363" s="21"/>
+      <c r="E363" s="19"/>
       <c r="F363" s="5"/>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.3">
@@ -6603,7 +6692,7 @@
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
       <c r="D364" s="5"/>
-      <c r="E364" s="21"/>
+      <c r="E364" s="19"/>
       <c r="F364" s="5"/>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.3">
@@ -6611,7 +6700,7 @@
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
       <c r="D365" s="5"/>
-      <c r="E365" s="21"/>
+      <c r="E365" s="19"/>
       <c r="F365" s="5"/>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.3">
@@ -6619,7 +6708,7 @@
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
       <c r="D366" s="5"/>
-      <c r="E366" s="21"/>
+      <c r="E366" s="19"/>
       <c r="F366" s="5"/>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.3">
@@ -6627,7 +6716,7 @@
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
       <c r="D367" s="5"/>
-      <c r="E367" s="21"/>
+      <c r="E367" s="19"/>
       <c r="F367" s="5"/>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.3">
@@ -6635,7 +6724,7 @@
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
       <c r="D368" s="5"/>
-      <c r="E368" s="21"/>
+      <c r="E368" s="19"/>
       <c r="F368" s="5"/>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.3">
@@ -6643,7 +6732,7 @@
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
       <c r="D369" s="5"/>
-      <c r="E369" s="21"/>
+      <c r="E369" s="19"/>
       <c r="F369" s="5"/>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.3">
@@ -6651,7 +6740,7 @@
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
       <c r="D370" s="5"/>
-      <c r="E370" s="21"/>
+      <c r="E370" s="19"/>
       <c r="F370" s="5"/>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.3">
@@ -6659,7 +6748,7 @@
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
       <c r="D371" s="5"/>
-      <c r="E371" s="21"/>
+      <c r="E371" s="19"/>
       <c r="F371" s="5"/>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.3">
@@ -6667,7 +6756,7 @@
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
       <c r="D372" s="5"/>
-      <c r="E372" s="21"/>
+      <c r="E372" s="19"/>
       <c r="F372" s="5"/>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.3">
@@ -6675,7 +6764,7 @@
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
       <c r="D373" s="5"/>
-      <c r="E373" s="21"/>
+      <c r="E373" s="19"/>
       <c r="F373" s="5"/>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.3">
@@ -6683,7 +6772,7 @@
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
       <c r="D374" s="5"/>
-      <c r="E374" s="21"/>
+      <c r="E374" s="19"/>
       <c r="F374" s="5"/>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.3">
@@ -6691,7 +6780,7 @@
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
       <c r="D375" s="5"/>
-      <c r="E375" s="21"/>
+      <c r="E375" s="19"/>
       <c r="F375" s="5"/>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.3">
@@ -6699,7 +6788,7 @@
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
       <c r="D376" s="5"/>
-      <c r="E376" s="21"/>
+      <c r="E376" s="19"/>
       <c r="F376" s="5"/>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.3">
@@ -6707,7 +6796,7 @@
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
       <c r="D377" s="5"/>
-      <c r="E377" s="21"/>
+      <c r="E377" s="19"/>
       <c r="F377" s="5"/>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.3">
@@ -6715,7 +6804,7 @@
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
       <c r="D378" s="5"/>
-      <c r="E378" s="21"/>
+      <c r="E378" s="19"/>
       <c r="F378" s="5"/>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.3">
@@ -6723,7 +6812,7 @@
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
       <c r="D379" s="5"/>
-      <c r="E379" s="21"/>
+      <c r="E379" s="19"/>
       <c r="F379" s="5"/>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.3">
@@ -6731,7 +6820,7 @@
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
       <c r="D380" s="5"/>
-      <c r="E380" s="21"/>
+      <c r="E380" s="19"/>
       <c r="F380" s="5"/>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.3">
@@ -6739,7 +6828,7 @@
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
       <c r="D381" s="5"/>
-      <c r="E381" s="21"/>
+      <c r="E381" s="19"/>
       <c r="F381" s="5"/>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.3">
@@ -6747,7 +6836,7 @@
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
       <c r="D382" s="5"/>
-      <c r="E382" s="21"/>
+      <c r="E382" s="19"/>
       <c r="F382" s="5"/>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.3">
@@ -6755,7 +6844,7 @@
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
       <c r="D383" s="5"/>
-      <c r="E383" s="21"/>
+      <c r="E383" s="19"/>
       <c r="F383" s="5"/>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.3">
@@ -6763,7 +6852,7 @@
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
       <c r="D384" s="5"/>
-      <c r="E384" s="21"/>
+      <c r="E384" s="19"/>
       <c r="F384" s="5"/>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.3">
@@ -6771,7 +6860,7 @@
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
       <c r="D385" s="5"/>
-      <c r="E385" s="21"/>
+      <c r="E385" s="19"/>
       <c r="F385" s="5"/>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.3">
@@ -6779,7 +6868,7 @@
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
       <c r="D386" s="5"/>
-      <c r="E386" s="21"/>
+      <c r="E386" s="19"/>
       <c r="F386" s="5"/>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.3">
@@ -6787,7 +6876,7 @@
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
       <c r="D387" s="5"/>
-      <c r="E387" s="21"/>
+      <c r="E387" s="19"/>
       <c r="F387" s="5"/>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.3">
@@ -6795,7 +6884,7 @@
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
       <c r="D388" s="5"/>
-      <c r="E388" s="21"/>
+      <c r="E388" s="19"/>
       <c r="F388" s="5"/>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.3">
@@ -6803,7 +6892,7 @@
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
       <c r="D389" s="5"/>
-      <c r="E389" s="21"/>
+      <c r="E389" s="19"/>
       <c r="F389" s="5"/>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.3">
@@ -6811,7 +6900,7 @@
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
       <c r="D390" s="5"/>
-      <c r="E390" s="21"/>
+      <c r="E390" s="19"/>
       <c r="F390" s="5"/>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.3">
@@ -6819,7 +6908,7 @@
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
       <c r="D391" s="5"/>
-      <c r="E391" s="21"/>
+      <c r="E391" s="19"/>
       <c r="F391" s="5"/>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.3">
@@ -6827,7 +6916,7 @@
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
       <c r="D392" s="5"/>
-      <c r="E392" s="21"/>
+      <c r="E392" s="19"/>
       <c r="F392" s="5"/>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.3">
@@ -6835,7 +6924,7 @@
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
       <c r="D393" s="5"/>
-      <c r="E393" s="21"/>
+      <c r="E393" s="19"/>
       <c r="F393" s="5"/>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.3">
@@ -6843,7 +6932,7 @@
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
       <c r="D394" s="5"/>
-      <c r="E394" s="21"/>
+      <c r="E394" s="19"/>
       <c r="F394" s="5"/>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.3">
@@ -6851,7 +6940,7 @@
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
       <c r="D395" s="5"/>
-      <c r="E395" s="21"/>
+      <c r="E395" s="19"/>
       <c r="F395" s="5"/>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.3">
@@ -6859,7 +6948,7 @@
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
       <c r="D396" s="5"/>
-      <c r="E396" s="21"/>
+      <c r="E396" s="19"/>
       <c r="F396" s="5"/>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.3">
@@ -6867,7 +6956,7 @@
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
       <c r="D397" s="5"/>
-      <c r="E397" s="21"/>
+      <c r="E397" s="19"/>
       <c r="F397" s="5"/>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.3">
@@ -6875,7 +6964,7 @@
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
       <c r="D398" s="5"/>
-      <c r="E398" s="21"/>
+      <c r="E398" s="19"/>
       <c r="F398" s="5"/>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.3">
@@ -6883,7 +6972,7 @@
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
       <c r="D399" s="5"/>
-      <c r="E399" s="21"/>
+      <c r="E399" s="19"/>
       <c r="F399" s="5"/>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.3">
@@ -6891,7 +6980,7 @@
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
       <c r="D400" s="5"/>
-      <c r="E400" s="21"/>
+      <c r="E400" s="19"/>
       <c r="F400" s="5"/>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.3">
@@ -6899,7 +6988,7 @@
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
       <c r="D401" s="5"/>
-      <c r="E401" s="21"/>
+      <c r="E401" s="19"/>
       <c r="F401" s="5"/>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.3">
@@ -6907,7 +6996,7 @@
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
       <c r="D402" s="5"/>
-      <c r="E402" s="21"/>
+      <c r="E402" s="19"/>
       <c r="F402" s="5"/>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.3">
@@ -6915,7 +7004,7 @@
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
       <c r="D403" s="5"/>
-      <c r="E403" s="21"/>
+      <c r="E403" s="19"/>
       <c r="F403" s="5"/>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.3">
@@ -6923,7 +7012,7 @@
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
       <c r="D404" s="5"/>
-      <c r="E404" s="21"/>
+      <c r="E404" s="19"/>
       <c r="F404" s="5"/>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.3">
@@ -6931,7 +7020,7 @@
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
       <c r="D405" s="5"/>
-      <c r="E405" s="21"/>
+      <c r="E405" s="19"/>
       <c r="F405" s="5"/>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.3">
@@ -6939,7 +7028,7 @@
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
       <c r="D406" s="5"/>
-      <c r="E406" s="21"/>
+      <c r="E406" s="19"/>
       <c r="F406" s="5"/>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.3">
@@ -6947,7 +7036,7 @@
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
       <c r="D407" s="5"/>
-      <c r="E407" s="21"/>
+      <c r="E407" s="19"/>
       <c r="F407" s="5"/>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.3">
@@ -6955,7 +7044,7 @@
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
       <c r="D408" s="5"/>
-      <c r="E408" s="21"/>
+      <c r="E408" s="19"/>
       <c r="F408" s="5"/>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.3">
@@ -6963,7 +7052,7 @@
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
       <c r="D409" s="5"/>
-      <c r="E409" s="21"/>
+      <c r="E409" s="19"/>
       <c r="F409" s="5"/>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.3">
@@ -6971,7 +7060,7 @@
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
       <c r="D410" s="5"/>
-      <c r="E410" s="21"/>
+      <c r="E410" s="19"/>
       <c r="F410" s="5"/>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.3">
@@ -6979,7 +7068,7 @@
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
       <c r="D411" s="5"/>
-      <c r="E411" s="21"/>
+      <c r="E411" s="19"/>
       <c r="F411" s="5"/>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.3">
@@ -6987,7 +7076,7 @@
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
       <c r="D412" s="5"/>
-      <c r="E412" s="21"/>
+      <c r="E412" s="19"/>
       <c r="F412" s="5"/>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.3">
@@ -6995,7 +7084,7 @@
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
       <c r="D413" s="5"/>
-      <c r="E413" s="21"/>
+      <c r="E413" s="19"/>
       <c r="F413" s="5"/>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.3">
@@ -7003,7 +7092,7 @@
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
       <c r="D414" s="5"/>
-      <c r="E414" s="21"/>
+      <c r="E414" s="19"/>
       <c r="F414" s="5"/>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.3">
@@ -7011,7 +7100,7 @@
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
       <c r="D415" s="5"/>
-      <c r="E415" s="21"/>
+      <c r="E415" s="19"/>
       <c r="F415" s="5"/>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.3">
@@ -7019,7 +7108,7 @@
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
       <c r="D416" s="5"/>
-      <c r="E416" s="21"/>
+      <c r="E416" s="19"/>
       <c r="F416" s="5"/>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.3">
@@ -7027,7 +7116,7 @@
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
       <c r="D417" s="5"/>
-      <c r="E417" s="21"/>
+      <c r="E417" s="19"/>
       <c r="F417" s="5"/>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.3">
@@ -7035,7 +7124,7 @@
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
       <c r="D418" s="5"/>
-      <c r="E418" s="21"/>
+      <c r="E418" s="19"/>
       <c r="F418" s="5"/>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.3">
@@ -7043,7 +7132,7 @@
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
       <c r="D419" s="5"/>
-      <c r="E419" s="21"/>
+      <c r="E419" s="19"/>
       <c r="F419" s="5"/>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.3">
@@ -7051,7 +7140,7 @@
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
       <c r="D420" s="5"/>
-      <c r="E420" s="21"/>
+      <c r="E420" s="19"/>
       <c r="F420" s="5"/>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.3">
@@ -7059,7 +7148,7 @@
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
       <c r="D421" s="5"/>
-      <c r="E421" s="21"/>
+      <c r="E421" s="19"/>
       <c r="F421" s="5"/>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.3">
@@ -7067,7 +7156,7 @@
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
       <c r="D422" s="5"/>
-      <c r="E422" s="21"/>
+      <c r="E422" s="19"/>
       <c r="F422" s="5"/>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.3">
@@ -7075,7 +7164,7 @@
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
       <c r="D423" s="5"/>
-      <c r="E423" s="21"/>
+      <c r="E423" s="19"/>
       <c r="F423" s="5"/>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.3">
@@ -7083,7 +7172,7 @@
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
       <c r="D424" s="5"/>
-      <c r="E424" s="21"/>
+      <c r="E424" s="19"/>
       <c r="F424" s="5"/>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.3">
@@ -7091,7 +7180,7 @@
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
       <c r="D425" s="5"/>
-      <c r="E425" s="21"/>
+      <c r="E425" s="19"/>
       <c r="F425" s="5"/>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.3">
@@ -7099,7 +7188,7 @@
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
       <c r="D426" s="5"/>
-      <c r="E426" s="21"/>
+      <c r="E426" s="19"/>
       <c r="F426" s="5"/>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.3">
@@ -7107,7 +7196,7 @@
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
       <c r="D427" s="5"/>
-      <c r="E427" s="21"/>
+      <c r="E427" s="19"/>
       <c r="F427" s="5"/>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.3">
@@ -7115,7 +7204,7 @@
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
       <c r="D428" s="5"/>
-      <c r="E428" s="21"/>
+      <c r="E428" s="19"/>
       <c r="F428" s="5"/>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.3">
@@ -7123,7 +7212,7 @@
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
       <c r="D429" s="5"/>
-      <c r="E429" s="21"/>
+      <c r="E429" s="19"/>
       <c r="F429" s="5"/>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.3">
@@ -7131,7 +7220,7 @@
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
       <c r="D430" s="5"/>
-      <c r="E430" s="21"/>
+      <c r="E430" s="19"/>
       <c r="F430" s="5"/>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.3">
@@ -7139,7 +7228,7 @@
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
       <c r="D431" s="5"/>
-      <c r="E431" s="21"/>
+      <c r="E431" s="19"/>
       <c r="F431" s="5"/>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.3">
@@ -7147,7 +7236,7 @@
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
       <c r="D432" s="5"/>
-      <c r="E432" s="21"/>
+      <c r="E432" s="19"/>
       <c r="F432" s="5"/>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.3">
@@ -7155,7 +7244,7 @@
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
       <c r="D433" s="5"/>
-      <c r="E433" s="21"/>
+      <c r="E433" s="19"/>
       <c r="F433" s="5"/>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.3">
@@ -7163,7 +7252,7 @@
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
       <c r="D434" s="5"/>
-      <c r="E434" s="21"/>
+      <c r="E434" s="19"/>
       <c r="F434" s="5"/>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.3">
@@ -7171,7 +7260,7 @@
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
       <c r="D435" s="5"/>
-      <c r="E435" s="21"/>
+      <c r="E435" s="19"/>
       <c r="F435" s="5"/>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.3">
@@ -7179,7 +7268,7 @@
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
       <c r="D436" s="5"/>
-      <c r="E436" s="21"/>
+      <c r="E436" s="19"/>
       <c r="F436" s="5"/>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.3">
@@ -7187,7 +7276,7 @@
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
       <c r="D437" s="5"/>
-      <c r="E437" s="21"/>
+      <c r="E437" s="19"/>
       <c r="F437" s="5"/>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.3">
@@ -7195,7 +7284,7 @@
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
       <c r="D438" s="5"/>
-      <c r="E438" s="21"/>
+      <c r="E438" s="19"/>
       <c r="F438" s="5"/>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.3">
@@ -7203,7 +7292,7 @@
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
       <c r="D439" s="5"/>
-      <c r="E439" s="21"/>
+      <c r="E439" s="19"/>
       <c r="F439" s="5"/>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.3">
@@ -7211,7 +7300,7 @@
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
       <c r="D440" s="5"/>
-      <c r="E440" s="21"/>
+      <c r="E440" s="19"/>
       <c r="F440" s="5"/>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.3">
@@ -7219,7 +7308,7 @@
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
       <c r="D441" s="5"/>
-      <c r="E441" s="21"/>
+      <c r="E441" s="19"/>
       <c r="F441" s="5"/>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.3">
@@ -7227,7 +7316,7 @@
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
       <c r="D442" s="5"/>
-      <c r="E442" s="21"/>
+      <c r="E442" s="19"/>
       <c r="F442" s="5"/>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.3">
@@ -7235,7 +7324,7 @@
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
       <c r="D443" s="5"/>
-      <c r="E443" s="21"/>
+      <c r="E443" s="19"/>
       <c r="F443" s="5"/>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.3">
@@ -7243,7 +7332,7 @@
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
       <c r="D444" s="5"/>
-      <c r="E444" s="21"/>
+      <c r="E444" s="19"/>
       <c r="F444" s="5"/>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.3">
@@ -7251,7 +7340,7 @@
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
       <c r="D445" s="5"/>
-      <c r="E445" s="21"/>
+      <c r="E445" s="19"/>
       <c r="F445" s="5"/>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.3">
@@ -7259,7 +7348,7 @@
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
       <c r="D446" s="5"/>
-      <c r="E446" s="21"/>
+      <c r="E446" s="19"/>
       <c r="F446" s="5"/>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.3">
@@ -7267,17 +7356,25 @@
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
       <c r="D447" s="5"/>
-      <c r="E447" s="21"/>
+      <c r="E447" s="19"/>
       <c r="F447" s="5"/>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A448" s="2"/>
+      <c r="A448" s="5"/>
+      <c r="B448" s="5"/>
+      <c r="C448" s="5"/>
+      <c r="D448" s="5"/>
+      <c r="E448" s="19"/>
+      <c r="F448" s="5"/>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A449" s="2"/>
     </row>
     <row r="450" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A450" s="2"/>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A451" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\bois\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CD674D-8219-4D60-911E-DB2EF4C92697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A98CCFC-8FD7-4846-8953-66AB40EBEF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -1514,7 +1514,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1584,43 +1584,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -2000,13 +1963,13 @@
       <c r="C2" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="11">
         <v>15.44</v>
       </c>
       <c r="E2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="12">
         <v>117.38500000000023</v>
       </c>
     </row>
@@ -2020,13 +1983,13 @@
       <c r="C3" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="11">
         <v>18.73</v>
       </c>
       <c r="E3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2040,13 +2003,13 @@
       <c r="C4" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="11">
         <v>8.81</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="12">
         <v>343.69899999999916</v>
       </c>
     </row>
@@ -2060,13 +2023,13 @@
       <c r="C5" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="11">
         <v>10.78</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="12">
         <v>385.91999999999973</v>
       </c>
     </row>
@@ -2080,13 +2043,13 @@
       <c r="C6" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="11">
         <v>12.41</v>
       </c>
       <c r="E6" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="12">
         <v>443.51999999999975</v>
       </c>
     </row>
@@ -2100,13 +2063,13 @@
       <c r="C7" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="11">
         <v>15.74</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="12">
         <v>119.51800000000065</v>
       </c>
     </row>
@@ -2115,13 +2078,13 @@
       <c r="B8" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="11">
         <v>14.71</v>
       </c>
       <c r="E8" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="12">
         <v>45</v>
       </c>
     </row>
@@ -2130,13 +2093,13 @@
       <c r="B9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="11">
         <v>21.56</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="12">
         <v>-3.5527136788005009E-15</v>
       </c>
     </row>
@@ -2145,13 +2108,13 @@
       <c r="B10" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="11">
         <v>44.06</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="12">
         <v>11.519999999999982</v>
       </c>
     </row>
@@ -2160,13 +2123,13 @@
       <c r="B11" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="11">
         <v>91.48</v>
       </c>
       <c r="E11" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2175,13 +2138,13 @@
       <c r="B12" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="11">
         <v>2.31</v>
       </c>
       <c r="E12" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2195,13 +2158,13 @@
       <c r="C13" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="11">
         <v>7.79</v>
       </c>
       <c r="E13" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="12">
         <v>14.900000000000224</v>
       </c>
     </row>
@@ -2215,13 +2178,13 @@
       <c r="C14" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="11">
         <v>10.83</v>
       </c>
       <c r="E14" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="12">
         <v>32.024999999999835</v>
       </c>
     </row>
@@ -2235,13 +2198,13 @@
       <c r="C15" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="11">
         <v>13.94</v>
       </c>
       <c r="E15" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="12">
         <v>12.150000000000212</v>
       </c>
     </row>
@@ -2255,13 +2218,13 @@
       <c r="C16" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="11">
         <v>0</v>
       </c>
       <c r="E16" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2275,13 +2238,13 @@
       <c r="C17" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="11">
         <v>20.09</v>
       </c>
       <c r="E17" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="12">
         <v>4.9999999981578114E-3</v>
       </c>
     </row>
@@ -2295,13 +2258,13 @@
       <c r="C18" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="11">
         <v>16.75</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2315,13 +2278,13 @@
       <c r="C19" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="11">
         <v>19.990000000000002</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="12">
         <v>140.29799999999338</v>
       </c>
     </row>
@@ -2335,13 +2298,13 @@
       <c r="C20" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="11">
         <v>28.560000000000002</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="12">
         <v>167.15000000000467</v>
       </c>
     </row>
@@ -2355,13 +2318,13 @@
       <c r="C21" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="11">
         <v>28.34</v>
       </c>
       <c r="E21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="12">
         <v>150.97200000000186</v>
       </c>
     </row>
@@ -2375,13 +2338,13 @@
       <c r="C22" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="11">
         <v>54.51</v>
       </c>
       <c r="E22" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="12">
         <v>-4.9999999999914557E-3</v>
       </c>
     </row>
@@ -2395,13 +2358,13 @@
       <c r="C23" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D23" s="25">
+      <c r="D23" s="11">
         <v>39.340000000000003</v>
       </c>
       <c r="E23" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2415,13 +2378,13 @@
       <c r="C24" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="11">
         <v>9.4500000000000011</v>
       </c>
       <c r="E24" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="12">
         <v>35.736999999999895</v>
       </c>
     </row>
@@ -2435,13 +2398,13 @@
       <c r="C25" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="11">
         <v>10.39</v>
       </c>
       <c r="E25" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2455,13 +2418,13 @@
       <c r="C26" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="11">
         <v>8.98</v>
       </c>
       <c r="E26" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="26">
+      <c r="F26" s="12">
         <v>74.247999999999593</v>
       </c>
     </row>
@@ -2475,13 +2438,13 @@
       <c r="C27" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="11">
         <v>10.81</v>
       </c>
       <c r="E27" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="26">
+      <c r="F27" s="12">
         <v>145.5270000000001</v>
       </c>
     </row>
@@ -2495,13 +2458,13 @@
       <c r="C28" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="11">
         <v>8.8000000000000007</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="26">
+      <c r="F28" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2515,13 +2478,13 @@
       <c r="C29" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="11">
         <v>16.080000000000002</v>
       </c>
       <c r="E29" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="12">
         <v>178.6339999999939</v>
       </c>
     </row>
@@ -2535,13 +2498,13 @@
       <c r="C30" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="11">
         <v>15.71</v>
       </c>
       <c r="E30" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="26">
+      <c r="F30" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2555,13 +2518,13 @@
       <c r="C31" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="11">
         <v>31.3</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="F31" s="26">
+      <c r="F31" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2575,13 +2538,13 @@
       <c r="C32" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="11">
         <v>31.3</v>
       </c>
       <c r="E32" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="26">
+      <c r="F32" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2595,13 +2558,13 @@
       <c r="C33" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="D33" s="25">
+      <c r="D33" s="11">
         <v>12.98</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F33" s="26">
+      <c r="F33" s="12">
         <v>152.56700000000018</v>
       </c>
     </row>
@@ -2615,13 +2578,13 @@
       <c r="C34" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="11">
         <v>18.11</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="F34" s="26">
+      <c r="F34" s="12">
         <v>169.2409999999937</v>
       </c>
     </row>
@@ -2635,13 +2598,13 @@
       <c r="C35" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="11">
         <v>18.97</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F35" s="26">
+      <c r="F35" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2655,13 +2618,13 @@
       <c r="C36" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="D36" s="25">
+      <c r="D36" s="11">
         <v>24.560000000000002</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F36" s="26">
+      <c r="F36" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2675,13 +2638,13 @@
       <c r="C37" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="D37" s="25">
+      <c r="D37" s="11">
         <v>56.24</v>
       </c>
       <c r="E37" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="F37" s="26">
+      <c r="F37" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2695,13 +2658,13 @@
       <c r="C38" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D38" s="25">
+      <c r="D38" s="11">
         <v>91.48</v>
       </c>
       <c r="E38" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="26">
+      <c r="F38" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2715,13 +2678,13 @@
       <c r="C39" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="D39" s="25">
+      <c r="D39" s="11">
         <v>30.060000000000002</v>
       </c>
       <c r="E39" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="26">
+      <c r="F39" s="12">
         <v>87.61900000000422</v>
       </c>
     </row>
@@ -2730,13 +2693,13 @@
       <c r="B40" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D40" s="25">
+      <c r="D40" s="11">
         <v>34.82</v>
       </c>
       <c r="E40" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="26">
+      <c r="F40" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2745,13 +2708,13 @@
       <c r="B41" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D41" s="25">
+      <c r="D41" s="11">
         <v>16.64</v>
       </c>
       <c r="E41" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="F41" s="26">
+      <c r="F41" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2760,13 +2723,13 @@
       <c r="B42" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="25">
+      <c r="D42" s="11">
         <v>24.72</v>
       </c>
       <c r="E42" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="F42" s="26">
+      <c r="F42" s="12">
         <v>2.34</v>
       </c>
     </row>
@@ -2775,13 +2738,13 @@
       <c r="B43" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D43" s="25">
+      <c r="D43" s="11">
         <v>25.16</v>
       </c>
       <c r="E43" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F43" s="26">
+      <c r="F43" s="12">
         <v>4.3964831775156199E-14</v>
       </c>
     </row>
@@ -2790,13 +2753,13 @@
       <c r="B44" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D44" s="25">
+      <c r="D44" s="11">
         <v>28.8</v>
       </c>
       <c r="E44" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="26">
+      <c r="F44" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2805,13 +2768,13 @@
       <c r="B45" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D45" s="25">
+      <c r="D45" s="11">
         <v>52.6</v>
       </c>
       <c r="E45" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="F45" s="26">
+      <c r="F45" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2820,13 +2783,13 @@
       <c r="B46" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D46" s="25">
+      <c r="D46" s="11">
         <v>33.380000000000003</v>
       </c>
       <c r="E46" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="F46" s="26">
+      <c r="F46" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2835,13 +2798,13 @@
       <c r="B47" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="D47" s="25">
+      <c r="D47" s="11">
         <v>40.730000000000004</v>
       </c>
       <c r="E47" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="26">
+      <c r="F47" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2850,13 +2813,13 @@
       <c r="B48" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D48" s="25">
+      <c r="D48" s="11">
         <v>85.05</v>
       </c>
       <c r="E48" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F48" s="26">
+      <c r="F48" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2865,13 +2828,13 @@
       <c r="B49" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="25">
+      <c r="D49" s="11">
         <v>97.73</v>
       </c>
       <c r="E49" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F49" s="26">
+      <c r="F49" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2885,13 +2848,13 @@
       <c r="C50" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="D50" s="25">
+      <c r="D50" s="11">
         <v>30.95</v>
       </c>
       <c r="E50" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F50" s="26">
+      <c r="F50" s="12">
         <v>4.6799999999999837</v>
       </c>
     </row>
@@ -2905,13 +2868,13 @@
       <c r="C51" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D51" s="25">
+      <c r="D51" s="11">
         <v>25.310000000000002</v>
       </c>
       <c r="E51" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="26">
+      <c r="F51" s="12">
         <v>10.921000000000276</v>
       </c>
     </row>
@@ -2925,13 +2888,13 @@
       <c r="C52" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="D52" s="25">
+      <c r="D52" s="11">
         <v>26.55</v>
       </c>
       <c r="E52" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="26">
+      <c r="F52" s="12">
         <v>81.549999999997638</v>
       </c>
     </row>
@@ -2945,13 +2908,13 @@
       <c r="C53" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D53" s="25">
+      <c r="D53" s="11">
         <v>37.869999999999997</v>
       </c>
       <c r="E53" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F53" s="26">
+      <c r="F53" s="12">
         <v>-1.0000000018073329E-3</v>
       </c>
     </row>
@@ -2965,13 +2928,13 @@
       <c r="C54" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D54" s="25">
+      <c r="D54" s="11">
         <v>22.59</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="F54" s="26">
+      <c r="F54" s="12">
         <v>143.72999999999942</v>
       </c>
     </row>
@@ -2985,13 +2948,13 @@
       <c r="C55" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="D55" s="25">
+      <c r="D55" s="11">
         <v>33.380000000000003</v>
       </c>
       <c r="E55" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F55" s="26">
+      <c r="F55" s="12">
         <v>105.33000000001158</v>
       </c>
     </row>
@@ -3000,13 +2963,13 @@
       <c r="B56" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D56" s="25">
+      <c r="D56" s="11">
         <v>71.77</v>
       </c>
       <c r="E56" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F56" s="26">
+      <c r="F56" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3015,13 +2978,13 @@
       <c r="B57" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="25">
+      <c r="D57" s="11">
         <v>68.930000000000007</v>
       </c>
       <c r="E57" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F57" s="26">
+      <c r="F57" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3035,13 +2998,13 @@
       <c r="C58" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D58" s="25">
+      <c r="D58" s="11">
         <v>47.94</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F58" s="26">
+      <c r="F58" s="12">
         <v>62.399999999999942</v>
       </c>
     </row>
@@ -3055,13 +3018,13 @@
       <c r="C59" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D59" s="25">
+      <c r="D59" s="11">
         <v>25.18</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="F59" s="26">
+      <c r="F59" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3075,13 +3038,13 @@
       <c r="C60" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="D60" s="25">
+      <c r="D60" s="11">
         <v>39.07</v>
       </c>
       <c r="E60" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="F60" s="26">
+      <c r="F60" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3095,13 +3058,13 @@
       <c r="C61" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D61" s="25">
+      <c r="D61" s="11">
         <v>42.52</v>
       </c>
       <c r="E61" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F61" s="26">
+      <c r="F61" s="12">
         <v>-4.9999999997818456E-3</v>
       </c>
     </row>
@@ -3115,13 +3078,13 @@
       <c r="C62" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D62" s="25">
+      <c r="D62" s="11">
         <v>39.910000000000004</v>
       </c>
       <c r="E62" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="F62" s="26">
+      <c r="F62" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3130,13 +3093,13 @@
       <c r="B63" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="D63" s="25">
+      <c r="D63" s="11">
         <v>33.730000000000004</v>
       </c>
       <c r="E63" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="F63" s="26">
+      <c r="F63" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3150,13 +3113,13 @@
       <c r="C64" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D64" s="25">
+      <c r="D64" s="11">
         <v>38.94</v>
       </c>
       <c r="E64" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="F64" s="26">
+      <c r="F64" s="12">
         <v>12.200000000000017</v>
       </c>
     </row>
@@ -3170,13 +3133,13 @@
       <c r="C65" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="D65" s="25">
+      <c r="D65" s="11">
         <v>46.37</v>
       </c>
       <c r="E65" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="F65" s="26">
+      <c r="F65" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3185,13 +3148,13 @@
       <c r="B66" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="25">
+      <c r="D66" s="11">
         <v>59.300000000000004</v>
       </c>
       <c r="E66" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F66" s="26">
+      <c r="F66" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3200,13 +3163,13 @@
       <c r="B67" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D67" s="25">
+      <c r="D67" s="11">
         <v>88.92</v>
       </c>
       <c r="E67" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="F67" s="26">
+      <c r="F67" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3215,13 +3178,13 @@
       <c r="B68" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D68" s="25">
+      <c r="D68" s="11">
         <v>118.54</v>
       </c>
       <c r="E68" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F68" s="26">
+      <c r="F68" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3230,13 +3193,13 @@
       <c r="B69" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="D69" s="25">
+      <c r="D69" s="11">
         <v>185.26</v>
       </c>
       <c r="E69" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F69" s="26">
+      <c r="F69" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3245,13 +3208,13 @@
       <c r="B70" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="D70" s="25">
+      <c r="D70" s="11">
         <v>222.33</v>
       </c>
       <c r="E70" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="26">
+      <c r="F70" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3263,80 +3226,80 @@
       <c r="C71" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="D71" s="27">
+      <c r="D71" s="11">
         <v>0.69000000000000006</v>
       </c>
       <c r="E71" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="F71" s="33">
+      <c r="F71" s="12">
         <v>576.00000000000136</v>
       </c>
-      <c r="G71" s="31"/>
+      <c r="G71" s="10"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D72" s="27">
+      <c r="D72" s="11">
         <v>0.54</v>
       </c>
       <c r="E72" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="F72" s="33">
+      <c r="F72" s="12">
         <v>0</v>
       </c>
-      <c r="G72" s="31"/>
+      <c r="G72" s="10"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="D73" s="27">
+      <c r="D73" s="11">
         <v>0.35000000000000003</v>
       </c>
       <c r="E73" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="F73" s="33">
+      <c r="F73" s="12">
         <v>0</v>
       </c>
-      <c r="G73" s="31"/>
+      <c r="G73" s="10"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D74" s="27">
+      <c r="D74" s="11">
         <v>0.28000000000000003</v>
       </c>
       <c r="E74" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="F74" s="33">
+      <c r="F74" s="12">
         <v>0</v>
       </c>
-      <c r="G74" s="31"/>
+      <c r="G74" s="10"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D75" s="27">
+      <c r="D75" s="11">
         <v>0.64</v>
       </c>
       <c r="E75" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="F75" s="33">
+      <c r="F75" s="12">
         <v>0</v>
       </c>
-      <c r="G75" s="31"/>
+      <c r="G75" s="10"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
@@ -3348,16 +3311,16 @@
       <c r="C76" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="D76" s="27">
+      <c r="D76" s="11">
         <v>1.33</v>
       </c>
       <c r="E76" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="F76" s="33">
+      <c r="F76" s="12">
         <v>179</v>
       </c>
-      <c r="G76" s="31"/>
+      <c r="G76" s="10"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
@@ -3369,16 +3332,16 @@
       <c r="C77" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D77" s="27">
+      <c r="D77" s="11">
         <v>1.49</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="F77" s="33">
+      <c r="F77" s="12">
         <v>151</v>
       </c>
-      <c r="G77" s="31"/>
+      <c r="G77" s="10"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
@@ -3390,16 +3353,16 @@
       <c r="C78" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="D78" s="27">
+      <c r="D78" s="11">
         <v>1.6300000000000001</v>
       </c>
       <c r="E78" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="F78" s="33">
+      <c r="F78" s="12">
         <v>302</v>
       </c>
-      <c r="G78" s="31"/>
+      <c r="G78" s="10"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
@@ -3411,16 +3374,16 @@
       <c r="C79" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="D79" s="27">
+      <c r="D79" s="11">
         <v>1.82</v>
       </c>
       <c r="E79" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="F79" s="33">
+      <c r="F79" s="12">
         <v>101</v>
       </c>
-      <c r="G79" s="31"/>
+      <c r="G79" s="10"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
@@ -3432,16 +3395,16 @@
       <c r="C80" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="D80" s="27">
+      <c r="D80" s="11">
         <v>1.96</v>
       </c>
       <c r="E80" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="F80" s="33">
+      <c r="F80" s="12">
         <v>59</v>
       </c>
-      <c r="G80" s="31"/>
+      <c r="G80" s="10"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
@@ -3453,16 +3416,16 @@
       <c r="C81" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="D81" s="27">
+      <c r="D81" s="11">
         <v>2.13</v>
       </c>
       <c r="E81" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="F81" s="33">
+      <c r="F81" s="12">
         <v>156</v>
       </c>
-      <c r="G81" s="31"/>
+      <c r="G81" s="10"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
@@ -3474,16 +3437,16 @@
       <c r="C82" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="D82" s="27">
+      <c r="D82" s="11">
         <v>2.29</v>
       </c>
       <c r="E82" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="F82" s="33">
+      <c r="F82" s="12">
         <v>138</v>
       </c>
-      <c r="G82" s="31"/>
+      <c r="G82" s="10"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
@@ -3495,16 +3458,16 @@
       <c r="C83" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="D83" s="27">
+      <c r="D83" s="11">
         <v>2.4700000000000002</v>
       </c>
       <c r="E83" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="F83" s="33">
+      <c r="F83" s="12">
         <v>2</v>
       </c>
-      <c r="G83" s="31"/>
+      <c r="G83" s="10"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
@@ -3516,18 +3479,18 @@
       <c r="C84" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="D84" s="27">
+      <c r="D84" s="11">
         <v>2.61</v>
       </c>
       <c r="E84" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="F84" s="33">
+      <c r="F84" s="12">
         <v>0</v>
       </c>
-      <c r="G84" s="31"/>
-    </row>
-    <row r="85" spans="1:7" s="29" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G84" s="10"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>303</v>
       </c>
@@ -3537,16 +3500,16 @@
       <c r="C85" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="D85" s="32">
+      <c r="D85" s="11">
         <v>1.33</v>
       </c>
-      <c r="E85" s="30" t="s">
+      <c r="E85" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="F85" s="33">
+      <c r="F85" s="12">
         <v>167</v>
       </c>
-      <c r="G85" s="31"/>
+      <c r="G85" s="10"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
@@ -3558,16 +3521,16 @@
       <c r="C86" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="D86" s="27">
+      <c r="D86" s="11">
         <v>1.59</v>
       </c>
       <c r="E86" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="F86" s="33">
+      <c r="F86" s="12">
         <v>-3</v>
       </c>
-      <c r="G86" s="31"/>
+      <c r="G86" s="10"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
@@ -3579,16 +3542,16 @@
       <c r="C87" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="D87" s="27">
+      <c r="D87" s="11">
         <v>1.98</v>
       </c>
       <c r="E87" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="F87" s="33">
+      <c r="F87" s="12">
         <v>0</v>
       </c>
-      <c r="G87" s="31"/>
+      <c r="G87" s="10"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
@@ -3600,32 +3563,32 @@
       <c r="C88" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D88" s="27">
+      <c r="D88" s="11">
         <v>2.38</v>
       </c>
       <c r="E88" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="F88" s="33">
+      <c r="F88" s="12">
         <v>-10</v>
       </c>
-      <c r="G88" s="31"/>
+      <c r="G88" s="10"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="5"/>
       <c r="B89" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="D89" s="27">
+      <c r="D89" s="11">
         <v>2.7600000000000002</v>
       </c>
       <c r="E89" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="F89" s="33">
+      <c r="F89" s="12">
         <v>0</v>
       </c>
-      <c r="G89" s="31"/>
+      <c r="G89" s="10"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
@@ -3637,16 +3600,16 @@
       <c r="C90" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D90" s="27">
+      <c r="D90" s="11">
         <v>1.31</v>
       </c>
       <c r="E90" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="F90" s="33">
+      <c r="F90" s="12">
         <v>-11</v>
       </c>
-      <c r="G90" s="31"/>
+      <c r="G90" s="10"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
@@ -3658,16 +3621,16 @@
       <c r="C91" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D91" s="27">
+      <c r="D91" s="11">
         <v>3.12</v>
       </c>
       <c r="E91" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="F91" s="33">
+      <c r="F91" s="12">
         <v>50</v>
       </c>
-      <c r="G91" s="31"/>
+      <c r="G91" s="10"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
@@ -3679,16 +3642,16 @@
       <c r="C92" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="D92" s="27">
+      <c r="D92" s="11">
         <v>3.5100000000000002</v>
       </c>
       <c r="E92" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="F92" s="33">
+      <c r="F92" s="12">
         <v>7</v>
       </c>
-      <c r="G92" s="31"/>
+      <c r="G92" s="10"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
@@ -3700,16 +3663,16 @@
       <c r="C93" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="D93" s="27">
+      <c r="D93" s="11">
         <v>3.91</v>
       </c>
       <c r="E93" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="F93" s="33">
+      <c r="F93" s="12">
         <v>112</v>
       </c>
-      <c r="G93" s="31"/>
+      <c r="G93" s="10"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
@@ -3721,16 +3684,16 @@
       <c r="C94" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="D94" s="27">
+      <c r="D94" s="11">
         <v>4.3100000000000005</v>
       </c>
       <c r="E94" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="F94" s="33">
+      <c r="F94" s="12">
         <v>74</v>
       </c>
-      <c r="G94" s="31"/>
+      <c r="G94" s="10"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
@@ -3742,16 +3705,16 @@
       <c r="C95" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D95" s="27">
+      <c r="D95" s="11">
         <v>4.68</v>
       </c>
       <c r="E95" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="F95" s="33">
+      <c r="F95" s="12">
         <v>75</v>
       </c>
-      <c r="G95" s="31"/>
+      <c r="G95" s="10"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
@@ -3763,16 +3726,16 @@
       <c r="C96" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="D96" s="27">
+      <c r="D96" s="11">
         <v>5.07</v>
       </c>
       <c r="E96" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="F96" s="33">
+      <c r="F96" s="12">
         <v>124</v>
       </c>
-      <c r="G96" s="31"/>
+      <c r="G96" s="10"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
@@ -3784,32 +3747,32 @@
       <c r="C97" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D97" s="27">
+      <c r="D97" s="11">
         <v>5.47</v>
       </c>
       <c r="E97" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="F97" s="33">
+      <c r="F97" s="12">
         <v>28</v>
       </c>
-      <c r="G97" s="31"/>
+      <c r="G97" s="10"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="5"/>
       <c r="B98" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="D98" s="27">
+      <c r="D98" s="11">
         <v>5.87</v>
       </c>
       <c r="E98" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="F98" s="33">
+      <c r="F98" s="12">
         <v>91</v>
       </c>
-      <c r="G98" s="31"/>
+      <c r="G98" s="10"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
@@ -3821,16 +3784,16 @@
       <c r="C99" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="D99" s="27">
+      <c r="D99" s="11">
         <v>1.69</v>
       </c>
       <c r="E99" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="F99" s="33">
+      <c r="F99" s="12">
         <v>77</v>
       </c>
-      <c r="G99" s="31"/>
+      <c r="G99" s="10"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
@@ -3842,16 +3805,16 @@
       <c r="C100" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="D100" s="27">
+      <c r="D100" s="11">
         <v>3.98</v>
       </c>
       <c r="E100" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="F100" s="33">
+      <c r="F100" s="12">
         <v>60</v>
       </c>
-      <c r="G100" s="31"/>
+      <c r="G100" s="10"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
@@ -3863,16 +3826,16 @@
       <c r="C101" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="D101" s="27">
+      <c r="D101" s="11">
         <v>5.12</v>
       </c>
       <c r="E101" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="F101" s="33">
+      <c r="F101" s="12">
         <v>52</v>
       </c>
-      <c r="G101" s="31"/>
+      <c r="G101" s="10"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
@@ -3884,32 +3847,32 @@
       <c r="C102" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="D102" s="27">
+      <c r="D102" s="11">
         <v>5.94</v>
       </c>
       <c r="E102" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="F102" s="33">
+      <c r="F102" s="12">
         <v>58</v>
       </c>
-      <c r="G102" s="31"/>
+      <c r="G102" s="10"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="5"/>
       <c r="B103" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="D103" s="27">
+      <c r="D103" s="11">
         <v>6.92</v>
       </c>
       <c r="E103" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="F103" s="33">
+      <c r="F103" s="12">
         <v>0</v>
       </c>
-      <c r="G103" s="31"/>
+      <c r="G103" s="10"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
@@ -3921,16 +3884,16 @@
       <c r="C104" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="D104" s="27">
+      <c r="D104" s="11">
         <v>2.13</v>
       </c>
       <c r="E104" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="F104" s="33">
+      <c r="F104" s="12">
         <v>21</v>
       </c>
-      <c r="G104" s="31"/>
+      <c r="G104" s="10"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
@@ -3942,16 +3905,16 @@
       <c r="C105" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="D105" s="27">
+      <c r="D105" s="11">
         <v>5.1100000000000003</v>
       </c>
       <c r="E105" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="F105" s="33">
+      <c r="F105" s="12">
         <v>130</v>
       </c>
-      <c r="G105" s="31"/>
+      <c r="G105" s="10"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
@@ -3963,16 +3926,16 @@
       <c r="C106" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="D106" s="27">
+      <c r="D106" s="11">
         <v>5.76</v>
       </c>
       <c r="E106" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="F106" s="33">
+      <c r="F106" s="12">
         <v>66</v>
       </c>
-      <c r="G106" s="31"/>
+      <c r="G106" s="10"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
@@ -3984,16 +3947,16 @@
       <c r="C107" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="D107" s="27">
+      <c r="D107" s="11">
         <v>6.3900000000000006</v>
       </c>
       <c r="E107" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="F107" s="33">
+      <c r="F107" s="12">
         <v>47</v>
       </c>
-      <c r="G107" s="31"/>
+      <c r="G107" s="10"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
@@ -4005,16 +3968,16 @@
       <c r="C108" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="D108" s="27">
+      <c r="D108" s="11">
         <v>7.03</v>
       </c>
       <c r="E108" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="F108" s="33">
+      <c r="F108" s="12">
         <v>104</v>
       </c>
-      <c r="G108" s="31"/>
+      <c r="G108" s="10"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
@@ -4026,16 +3989,16 @@
       <c r="C109" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="D109" s="27">
+      <c r="D109" s="11">
         <v>7.68</v>
       </c>
       <c r="E109" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="F109" s="33">
+      <c r="F109" s="12">
         <v>169</v>
       </c>
-      <c r="G109" s="31"/>
+      <c r="G109" s="10"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
@@ -4047,16 +4010,16 @@
       <c r="C110" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="D110" s="27">
+      <c r="D110" s="11">
         <v>8.31</v>
       </c>
       <c r="E110" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="F110" s="33">
+      <c r="F110" s="12">
         <v>23</v>
       </c>
-      <c r="G110" s="31"/>
+      <c r="G110" s="10"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
@@ -4068,32 +4031,32 @@
       <c r="C111" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D111" s="27">
+      <c r="D111" s="11">
         <v>8.9500000000000011</v>
       </c>
       <c r="E111" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="F111" s="33">
+      <c r="F111" s="12">
         <v>8</v>
       </c>
-      <c r="G111" s="31"/>
+      <c r="G111" s="10"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="5"/>
       <c r="B112" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D112" s="27">
+      <c r="D112" s="11">
         <v>9.61</v>
       </c>
       <c r="E112" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="F112" s="33">
+      <c r="F112" s="12">
         <v>0</v>
       </c>
-      <c r="G112" s="31"/>
+      <c r="G112" s="10"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
@@ -4105,16 +4068,16 @@
       <c r="C113" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="D113" s="27">
+      <c r="D113" s="11">
         <v>4.2700000000000005</v>
       </c>
       <c r="E113" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="F113" s="33">
+      <c r="F113" s="12">
         <v>10</v>
       </c>
-      <c r="G113" s="31"/>
+      <c r="G113" s="10"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
@@ -4126,16 +4089,16 @@
       <c r="C114" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D114" s="27">
+      <c r="D114" s="11">
         <v>10.220000000000001</v>
       </c>
       <c r="E114" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="F114" s="33">
+      <c r="F114" s="12">
         <v>18</v>
       </c>
-      <c r="G114" s="31"/>
+      <c r="G114" s="10"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
@@ -4147,16 +4110,16 @@
       <c r="C115" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D115" s="27">
+      <c r="D115" s="11">
         <v>11.5</v>
       </c>
       <c r="E115" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="F115" s="33">
+      <c r="F115" s="12">
         <v>16</v>
       </c>
-      <c r="G115" s="31"/>
+      <c r="G115" s="10"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
@@ -4168,16 +4131,16 @@
       <c r="C116" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="D116" s="27">
+      <c r="D116" s="11">
         <v>12.780000000000001</v>
       </c>
       <c r="E116" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="F116" s="33">
+      <c r="F116" s="12">
         <v>2</v>
       </c>
-      <c r="G116" s="31"/>
+      <c r="G116" s="10"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
@@ -4189,16 +4152,16 @@
       <c r="C117" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="D117" s="27">
+      <c r="D117" s="11">
         <v>14.07</v>
       </c>
       <c r="E117" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F117" s="33">
+      <c r="F117" s="12">
         <v>16</v>
       </c>
-      <c r="G117" s="31"/>
+      <c r="G117" s="10"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
@@ -4210,16 +4173,16 @@
       <c r="C118" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="D118" s="27">
+      <c r="D118" s="11">
         <v>15.34</v>
       </c>
       <c r="E118" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="F118" s="33">
+      <c r="F118" s="12">
         <v>32</v>
       </c>
-      <c r="G118" s="31"/>
+      <c r="G118" s="10"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
@@ -4231,16 +4194,16 @@
       <c r="C119" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D119" s="27">
+      <c r="D119" s="11">
         <v>16.61</v>
       </c>
       <c r="E119" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="F119" s="33">
+      <c r="F119" s="12">
         <v>25</v>
       </c>
-      <c r="G119" s="31"/>
+      <c r="G119" s="10"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
@@ -4252,32 +4215,32 @@
       <c r="C120" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="D120" s="27">
+      <c r="D120" s="11">
         <v>17.88</v>
       </c>
       <c r="E120" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="F120" s="33">
+      <c r="F120" s="12">
         <v>11</v>
       </c>
-      <c r="G120" s="31"/>
+      <c r="G120" s="10"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="5"/>
       <c r="B121" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="D121" s="27">
+      <c r="D121" s="11">
         <v>19.12</v>
       </c>
       <c r="E121" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="F121" s="33">
+      <c r="F121" s="12">
         <v>0</v>
       </c>
-      <c r="G121" s="31"/>
+      <c r="G121" s="10"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
@@ -4289,16 +4252,16 @@
       <c r="C122" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D122" s="27">
+      <c r="D122" s="11">
         <v>8.02</v>
       </c>
       <c r="E122" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="F122" s="33">
+      <c r="F122" s="12">
         <v>18</v>
       </c>
-      <c r="G122" s="31"/>
+      <c r="G122" s="10"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
@@ -4310,16 +4273,16 @@
       <c r="C123" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="D123" s="27">
+      <c r="D123" s="11">
         <v>18.100000000000001</v>
       </c>
       <c r="E123" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="F123" s="33">
+      <c r="F123" s="12">
         <v>26</v>
       </c>
-      <c r="G123" s="31"/>
+      <c r="G123" s="10"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
@@ -4331,16 +4294,16 @@
       <c r="C124" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="D124" s="27">
+      <c r="D124" s="11">
         <v>22.64</v>
       </c>
       <c r="E124" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="F124" s="33">
+      <c r="F124" s="12">
         <v>23</v>
       </c>
-      <c r="G124" s="31"/>
+      <c r="G124" s="10"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
@@ -4352,16 +4315,16 @@
       <c r="C125" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="D125" s="27">
+      <c r="D125" s="11">
         <v>27.150000000000002</v>
       </c>
       <c r="E125" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="F125" s="33">
+      <c r="F125" s="12">
         <v>15</v>
       </c>
-      <c r="G125" s="31"/>
+      <c r="G125" s="10"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
@@ -4373,16 +4336,16 @@
       <c r="C126" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D126" s="27">
+      <c r="D126" s="11">
         <v>31.69</v>
       </c>
       <c r="E126" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="F126" s="33">
+      <c r="F126" s="12">
         <v>0</v>
       </c>
-      <c r="G126" s="31"/>
+      <c r="G126" s="10"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
@@ -4394,32 +4357,32 @@
       <c r="C127" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="D127" s="27">
+      <c r="D127" s="11">
         <v>33.94</v>
       </c>
       <c r="E127" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="F127" s="33">
+      <c r="F127" s="12">
         <v>0</v>
       </c>
-      <c r="G127" s="31"/>
+      <c r="G127" s="10"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="5"/>
       <c r="B128" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="D128" s="27">
+      <c r="D128" s="11">
         <v>36.22</v>
       </c>
       <c r="E128" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="F128" s="28">
+      <c r="F128" s="12">
         <v>0</v>
       </c>
-      <c r="G128" s="30"/>
+      <c r="G128" s="10"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
@@ -4431,13 +4394,13 @@
       <c r="C129" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="D129" s="34">
+      <c r="D129" s="11">
         <v>5.12</v>
       </c>
       <c r="E129" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="F129" s="35">
+      <c r="F129" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4451,13 +4414,13 @@
       <c r="C130" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="D130" s="34">
+      <c r="D130" s="11">
         <v>4.07</v>
       </c>
       <c r="E130" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="F130" s="35">
+      <c r="F130" s="12">
         <v>302</v>
       </c>
     </row>
@@ -4471,13 +4434,13 @@
       <c r="C131" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="D131" s="34">
+      <c r="D131" s="11">
         <v>4.53</v>
       </c>
       <c r="E131" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="F131" s="35">
+      <c r="F131" s="12">
         <v>9</v>
       </c>
     </row>
@@ -4491,13 +4454,13 @@
       <c r="C132" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D132" s="34">
+      <c r="D132" s="11">
         <v>6.7</v>
       </c>
       <c r="E132" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="F132" s="35">
+      <c r="F132" s="12">
         <v>221</v>
       </c>
     </row>
@@ -4511,13 +4474,13 @@
       <c r="C133" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D133" s="34">
+      <c r="D133" s="11">
         <v>8.31</v>
       </c>
       <c r="E133" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="F133" s="35">
+      <c r="F133" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4531,13 +4494,13 @@
       <c r="C134" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="D134" s="34">
+      <c r="D134" s="11">
         <v>7.8900000000000006</v>
       </c>
       <c r="E134" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="F134" s="35">
+      <c r="F134" s="12">
         <v>373</v>
       </c>
     </row>
@@ -4551,13 +4514,13 @@
       <c r="C135" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="D135" s="34">
+      <c r="D135" s="11">
         <v>9.61</v>
       </c>
       <c r="E135" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="F135" s="35">
+      <c r="F135" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4566,13 +4529,13 @@
       <c r="B136" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="D136" s="34">
+      <c r="D136" s="11">
         <v>3.5500000000000003</v>
       </c>
       <c r="E136" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="F136" s="35">
+      <c r="F136" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4586,13 +4549,13 @@
       <c r="C137" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="D137" s="34">
+      <c r="D137" s="11">
         <v>6.22</v>
       </c>
       <c r="E137" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="F137" s="35">
+      <c r="F137" s="12">
         <v>351</v>
       </c>
     </row>
@@ -4606,13 +4569,13 @@
       <c r="C138" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D138" s="34">
+      <c r="D138" s="11">
         <v>6.91</v>
       </c>
       <c r="E138" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="F138" s="35">
+      <c r="F138" s="12">
         <v>162</v>
       </c>
     </row>
@@ -4626,13 +4589,13 @@
       <c r="C139" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D139" s="34">
+      <c r="D139" s="11">
         <v>10.91</v>
       </c>
       <c r="E139" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="F139" s="35">
+      <c r="F139" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4646,13 +4609,13 @@
       <c r="C140" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="D140" s="34">
+      <c r="D140" s="11">
         <v>10.370000000000001</v>
       </c>
       <c r="E140" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="F140" s="35">
+      <c r="F140" s="12">
         <v>223</v>
       </c>
     </row>
@@ -4666,13 +4629,13 @@
       <c r="C141" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D141" s="34">
+      <c r="D141" s="11">
         <v>13.88</v>
       </c>
       <c r="E141" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="F141" s="35">
+      <c r="F141" s="12">
         <v>143</v>
       </c>
     </row>
@@ -4686,13 +4649,13 @@
       <c r="C142" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="D142" s="34">
+      <c r="D142" s="11">
         <v>9.23</v>
       </c>
       <c r="E142" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="F142" s="35">
+      <c r="F142" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4706,13 +4669,13 @@
       <c r="C143" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D143" s="34">
+      <c r="D143" s="11">
         <v>11.14</v>
       </c>
       <c r="E143" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="F143" s="35">
+      <c r="F143" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4721,13 +4684,13 @@
       <c r="B144" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="D144" s="34">
+      <c r="D144" s="11">
         <v>3.17</v>
       </c>
       <c r="E144" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="F144" s="35">
+      <c r="F144" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4741,13 +4704,13 @@
       <c r="C145" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="D145" s="34">
+      <c r="D145" s="11">
         <v>7.2</v>
       </c>
       <c r="E145" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="F145" s="35">
+      <c r="F145" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4761,13 +4724,13 @@
       <c r="C146" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="D146" s="34">
+      <c r="D146" s="11">
         <v>18.11</v>
       </c>
       <c r="E146" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="F146" s="35">
+      <c r="F146" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4781,13 +4744,13 @@
       <c r="C147" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D147" s="34">
+      <c r="D147" s="11">
         <v>11.94</v>
       </c>
       <c r="E147" s="19" t="s">
         <v>274</v>
       </c>
-      <c r="F147" s="35">
+      <c r="F147" s="12">
         <v>99</v>
       </c>
     </row>
@@ -4801,13 +4764,13 @@
       <c r="C148" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="D148" s="34">
+      <c r="D148" s="11">
         <v>15.16</v>
       </c>
       <c r="E148" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="F148" s="35">
+      <c r="F148" s="12">
         <v>47</v>
       </c>
     </row>
@@ -4821,13 +4784,13 @@
       <c r="C149" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D149" s="34">
+      <c r="D149" s="11">
         <v>13.52</v>
       </c>
       <c r="E149" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="F149" s="35">
+      <c r="F149" s="12">
         <v>106</v>
       </c>
     </row>
@@ -4841,13 +4804,13 @@
       <c r="C150" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="D150" s="34">
+      <c r="D150" s="11">
         <v>24.89</v>
       </c>
       <c r="E150" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="F150" s="35">
+      <c r="F150" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4928,7 +4891,7 @@
         <v>429</v>
       </c>
       <c r="F154" s="12">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
@@ -4941,13 +4904,13 @@
       <c r="C155" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D155" s="36">
+      <c r="D155" s="11">
         <v>9.82</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="F155" s="37">
+      <c r="F155" s="12">
         <v>1</v>
       </c>
     </row>
@@ -4961,13 +4924,13 @@
       <c r="C156" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D156" s="36">
+      <c r="D156" s="11">
         <v>9.82</v>
       </c>
       <c r="E156" s="10" t="s">
         <v>439</v>
       </c>
-      <c r="F156" s="37">
+      <c r="F156" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4981,13 +4944,13 @@
       <c r="C157" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D157" s="36">
+      <c r="D157" s="11">
         <v>9.82</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>440</v>
       </c>
-      <c r="F157" s="37">
+      <c r="F157" s="12">
         <v>0</v>
       </c>
     </row>
@@ -5001,13 +4964,13 @@
       <c r="C158" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D158" s="36">
+      <c r="D158" s="11">
         <v>9.82</v>
       </c>
       <c r="E158" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="F158" s="37">
+      <c r="F158" s="12">
         <v>2</v>
       </c>
     </row>
@@ -5021,13 +4984,13 @@
       <c r="C159" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D159" s="36">
+      <c r="D159" s="11">
         <v>9.82</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="F159" s="37">
+      <c r="F159" s="12">
         <v>0</v>
       </c>
     </row>
@@ -5041,13 +5004,13 @@
       <c r="C160" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D160" s="36">
+      <c r="D160" s="11">
         <v>9.82</v>
       </c>
       <c r="E160" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="F160" s="37">
+      <c r="F160" s="12">
         <v>0</v>
       </c>
     </row>
@@ -5061,13 +5024,13 @@
       <c r="C161" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="D161" s="36">
+      <c r="D161" s="11">
         <v>6.3</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="F161" s="37">
+      <c r="F161" s="12">
         <v>4</v>
       </c>
     </row>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\bois\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A98CCFC-8FD7-4846-8953-66AB40EBEF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05FD4653-F7C8-4F8B-A093-1E25371FF0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="23124" yWindow="12" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -1514,7 +1514,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1584,6 +1584,30 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1963,14 +1987,14 @@
       <c r="C2" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="25">
         <v>15.44</v>
       </c>
       <c r="E2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="12">
-        <v>117.38500000000023</v>
+      <c r="F2" s="26">
+        <v>104.88500000000023</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1983,13 +2007,13 @@
       <c r="C3" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="25">
         <v>18.73</v>
       </c>
       <c r="E3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2003,14 +2027,14 @@
       <c r="C4" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="25">
         <v>8.81</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="12">
-        <v>343.69899999999916</v>
+      <c r="F4" s="26">
+        <v>132.01899999999907</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -2023,14 +2047,14 @@
       <c r="C5" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="25">
         <v>10.78</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="12">
-        <v>385.91999999999973</v>
+      <c r="F5" s="26">
+        <v>256.31999999999971</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -2043,14 +2067,14 @@
       <c r="C6" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="25">
         <v>12.41</v>
       </c>
       <c r="E6" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="12">
-        <v>443.51999999999975</v>
+      <c r="F6" s="26">
+        <v>374.39999999999981</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -2063,14 +2087,14 @@
       <c r="C7" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="25">
         <v>15.74</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="12">
-        <v>119.51800000000065</v>
+      <c r="F7" s="26">
+        <v>83.518000000000654</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -2078,14 +2102,14 @@
       <c r="B8" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="25">
         <v>14.71</v>
       </c>
       <c r="E8" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="12">
-        <v>45</v>
+      <c r="F8" s="26">
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2093,14 +2117,14 @@
       <c r="B9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="11">
-        <v>21.56</v>
+      <c r="D9" s="25">
+        <v>22.580000000000002</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="12">
-        <v>-3.5527136788005009E-15</v>
+      <c r="F9" s="26">
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -2108,13 +2132,13 @@
       <c r="B10" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="25">
         <v>44.06</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="26">
         <v>11.519999999999982</v>
       </c>
     </row>
@@ -2123,13 +2147,13 @@
       <c r="B11" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="25">
         <v>91.48</v>
       </c>
       <c r="E11" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2138,13 +2162,13 @@
       <c r="B12" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="25">
         <v>2.31</v>
       </c>
       <c r="E12" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2158,13 +2182,13 @@
       <c r="C13" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="25">
         <v>7.79</v>
       </c>
       <c r="E13" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="26">
         <v>14.900000000000224</v>
       </c>
     </row>
@@ -2178,13 +2202,13 @@
       <c r="C14" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="25">
         <v>10.83</v>
       </c>
       <c r="E14" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="26">
         <v>32.024999999999835</v>
       </c>
     </row>
@@ -2198,14 +2222,14 @@
       <c r="C15" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="25">
         <v>13.94</v>
       </c>
       <c r="E15" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="12">
-        <v>12.150000000000212</v>
+      <c r="F15" s="26">
+        <v>4.4750000000002101</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -2218,13 +2242,13 @@
       <c r="C16" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="25">
         <v>0</v>
       </c>
       <c r="E16" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2238,13 +2262,13 @@
       <c r="C17" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="25">
         <v>20.09</v>
       </c>
       <c r="E17" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="26">
         <v>4.9999999981578114E-3</v>
       </c>
     </row>
@@ -2258,13 +2282,13 @@
       <c r="C18" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="25">
         <v>16.75</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2278,14 +2302,14 @@
       <c r="C19" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="25">
         <v>19.990000000000002</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="12">
-        <v>140.29799999999338</v>
+      <c r="F19" s="26">
+        <v>120.08799999999336</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2298,13 +2322,13 @@
       <c r="C20" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="25">
         <v>28.560000000000002</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="26">
         <v>167.15000000000467</v>
       </c>
     </row>
@@ -2318,14 +2342,14 @@
       <c r="C21" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="25">
         <v>28.34</v>
       </c>
       <c r="E21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="12">
-        <v>150.97200000000186</v>
+      <c r="F21" s="26">
+        <v>144.26200000000185</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2338,13 +2362,13 @@
       <c r="C22" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="25">
         <v>54.51</v>
       </c>
       <c r="E22" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="26">
         <v>-4.9999999999914557E-3</v>
       </c>
     </row>
@@ -2358,13 +2382,13 @@
       <c r="C23" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="25">
         <v>39.340000000000003</v>
       </c>
       <c r="E23" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2378,13 +2402,13 @@
       <c r="C24" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="25">
         <v>9.4500000000000011</v>
       </c>
       <c r="E24" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="26">
         <v>35.736999999999895</v>
       </c>
     </row>
@@ -2398,13 +2422,13 @@
       <c r="C25" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="25">
         <v>10.39</v>
       </c>
       <c r="E25" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2418,14 +2442,14 @@
       <c r="C26" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="25">
         <v>8.98</v>
       </c>
       <c r="E26" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="12">
-        <v>74.247999999999593</v>
+      <c r="F26" s="26">
+        <v>65.337999999999596</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2438,14 +2462,14 @@
       <c r="C27" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="25">
         <v>10.81</v>
       </c>
       <c r="E27" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="12">
-        <v>145.5270000000001</v>
+      <c r="F27" s="26">
+        <v>142.54700000000011</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2458,13 +2482,13 @@
       <c r="C28" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="25">
         <v>8.8000000000000007</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2478,14 +2502,14 @@
       <c r="C29" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="25">
         <v>16.080000000000002</v>
       </c>
       <c r="E29" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="12">
-        <v>178.6339999999939</v>
+      <c r="F29" s="26">
+        <v>176.0489999999939</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2498,13 +2522,13 @@
       <c r="C30" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="25">
         <v>15.71</v>
       </c>
       <c r="E30" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2518,13 +2542,13 @@
       <c r="C31" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="25">
         <v>31.3</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2538,13 +2562,13 @@
       <c r="C32" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="25">
         <v>31.3</v>
       </c>
       <c r="E32" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2558,13 +2582,13 @@
       <c r="C33" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="25">
         <v>12.98</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="26">
         <v>152.56700000000018</v>
       </c>
     </row>
@@ -2578,14 +2602,14 @@
       <c r="C34" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="25">
         <v>18.11</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="F34" s="12">
-        <v>169.2409999999937</v>
+      <c r="F34" s="26">
+        <v>152.87599999999372</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2598,13 +2622,13 @@
       <c r="C35" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="25">
         <v>18.97</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2618,13 +2642,13 @@
       <c r="C36" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="25">
         <v>24.560000000000002</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2638,13 +2662,13 @@
       <c r="C37" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="25">
         <v>56.24</v>
       </c>
       <c r="E37" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2658,13 +2682,13 @@
       <c r="C38" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="25">
         <v>91.48</v>
       </c>
       <c r="E38" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2678,13 +2702,13 @@
       <c r="C39" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="25">
         <v>30.060000000000002</v>
       </c>
       <c r="E39" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="26">
         <v>87.61900000000422</v>
       </c>
     </row>
@@ -2693,13 +2717,13 @@
       <c r="B40" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="25">
         <v>34.82</v>
       </c>
       <c r="E40" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F40" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2708,13 +2732,13 @@
       <c r="B41" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="25">
         <v>16.64</v>
       </c>
       <c r="E41" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="F41" s="12">
+      <c r="F41" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2723,13 +2747,13 @@
       <c r="B42" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="25">
         <v>24.72</v>
       </c>
       <c r="E42" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="26">
         <v>2.34</v>
       </c>
     </row>
@@ -2738,13 +2762,13 @@
       <c r="B43" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="25">
         <v>25.16</v>
       </c>
       <c r="E43" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F43" s="12">
+      <c r="F43" s="26">
         <v>4.3964831775156199E-14</v>
       </c>
     </row>
@@ -2753,13 +2777,13 @@
       <c r="B44" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="25">
         <v>28.8</v>
       </c>
       <c r="E44" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="12">
+      <c r="F44" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2768,13 +2792,13 @@
       <c r="B45" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="25">
         <v>52.6</v>
       </c>
       <c r="E45" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="F45" s="12">
+      <c r="F45" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2783,13 +2807,13 @@
       <c r="B46" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="25">
         <v>33.380000000000003</v>
       </c>
       <c r="E46" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2798,13 +2822,13 @@
       <c r="B47" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="25">
         <v>40.730000000000004</v>
       </c>
       <c r="E47" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="12">
+      <c r="F47" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2813,13 +2837,13 @@
       <c r="B48" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="25">
         <v>85.05</v>
       </c>
       <c r="E48" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F48" s="12">
+      <c r="F48" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2828,13 +2852,13 @@
       <c r="B49" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="25">
         <v>97.73</v>
       </c>
       <c r="E49" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F49" s="12">
+      <c r="F49" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2848,13 +2872,13 @@
       <c r="C50" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="D50" s="11">
+      <c r="D50" s="25">
         <v>30.95</v>
       </c>
       <c r="E50" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F50" s="12">
+      <c r="F50" s="26">
         <v>4.6799999999999837</v>
       </c>
     </row>
@@ -2868,13 +2892,13 @@
       <c r="C51" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D51" s="11">
+      <c r="D51" s="25">
         <v>25.310000000000002</v>
       </c>
       <c r="E51" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="12">
+      <c r="F51" s="26">
         <v>10.921000000000276</v>
       </c>
     </row>
@@ -2888,14 +2912,14 @@
       <c r="C52" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="25">
         <v>26.55</v>
       </c>
       <c r="E52" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="12">
-        <v>81.549999999997638</v>
+      <c r="F52" s="26">
+        <v>80.649999999997618</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2908,14 +2932,14 @@
       <c r="C53" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="25">
         <v>37.869999999999997</v>
       </c>
       <c r="E53" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F53" s="12">
-        <v>-1.0000000018073329E-3</v>
+      <c r="F53" s="26">
+        <v>-3.3010000000018076</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2928,14 +2952,14 @@
       <c r="C54" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="25">
         <v>22.59</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="F54" s="12">
-        <v>143.72999999999942</v>
+      <c r="F54" s="26">
+        <v>134.36999999999941</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2948,14 +2972,14 @@
       <c r="C55" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="25">
         <v>33.380000000000003</v>
       </c>
       <c r="E55" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F55" s="12">
-        <v>105.33000000001158</v>
+      <c r="F55" s="26">
+        <v>95.970000000011566</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2963,13 +2987,13 @@
       <c r="B56" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="25">
         <v>71.77</v>
       </c>
       <c r="E56" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F56" s="12">
+      <c r="F56" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2978,13 +3002,13 @@
       <c r="B57" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="25">
         <v>68.930000000000007</v>
       </c>
       <c r="E57" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F57" s="12">
+      <c r="F57" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2998,13 +3022,13 @@
       <c r="C58" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="25">
         <v>47.94</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F58" s="12">
+      <c r="F58" s="26">
         <v>62.399999999999942</v>
       </c>
     </row>
@@ -3018,13 +3042,13 @@
       <c r="C59" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D59" s="11">
+      <c r="D59" s="25">
         <v>25.18</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="F59" s="12">
+      <c r="F59" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3038,13 +3062,13 @@
       <c r="C60" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="25">
         <v>39.07</v>
       </c>
       <c r="E60" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="F60" s="12">
+      <c r="F60" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3058,13 +3082,13 @@
       <c r="C61" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="25">
         <v>42.52</v>
       </c>
       <c r="E61" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F61" s="12">
+      <c r="F61" s="26">
         <v>-4.9999999997818456E-3</v>
       </c>
     </row>
@@ -3078,13 +3102,13 @@
       <c r="C62" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D62" s="11">
+      <c r="D62" s="25">
         <v>39.910000000000004</v>
       </c>
       <c r="E62" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="F62" s="12">
+      <c r="F62" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3093,13 +3117,13 @@
       <c r="B63" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="25">
         <v>33.730000000000004</v>
       </c>
       <c r="E63" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="F63" s="12">
+      <c r="F63" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3113,13 +3137,13 @@
       <c r="C64" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D64" s="11">
+      <c r="D64" s="25">
         <v>38.94</v>
       </c>
       <c r="E64" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="F64" s="12">
+      <c r="F64" s="26">
         <v>12.200000000000017</v>
       </c>
     </row>
@@ -3133,13 +3157,13 @@
       <c r="C65" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="D65" s="11">
+      <c r="D65" s="25">
         <v>46.37</v>
       </c>
       <c r="E65" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="F65" s="12">
+      <c r="F65" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3148,13 +3172,13 @@
       <c r="B66" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="11">
+      <c r="D66" s="25">
         <v>59.300000000000004</v>
       </c>
       <c r="E66" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F66" s="12">
+      <c r="F66" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3163,13 +3187,13 @@
       <c r="B67" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D67" s="11">
+      <c r="D67" s="25">
         <v>88.92</v>
       </c>
       <c r="E67" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="F67" s="12">
+      <c r="F67" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3178,13 +3202,13 @@
       <c r="B68" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D68" s="11">
+      <c r="D68" s="25">
         <v>118.54</v>
       </c>
       <c r="E68" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F68" s="12">
+      <c r="F68" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3193,13 +3217,13 @@
       <c r="B69" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="25">
         <v>185.26</v>
       </c>
       <c r="E69" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F69" s="12">
+      <c r="F69" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3208,13 +3232,13 @@
       <c r="B70" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="D70" s="11">
-        <v>222.33</v>
+      <c r="D70" s="25">
+        <v>169.62</v>
       </c>
       <c r="E70" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="12">
+      <c r="F70" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3226,14 +3250,14 @@
       <c r="C71" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="D71" s="11">
+      <c r="D71" s="28">
         <v>0.69000000000000006</v>
       </c>
       <c r="E71" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="F71" s="12">
-        <v>576.00000000000136</v>
+      <c r="F71" s="27">
+        <v>550.80000000000132</v>
       </c>
       <c r="G71" s="10"/>
     </row>
@@ -3242,13 +3266,13 @@
       <c r="B72" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D72" s="11">
+      <c r="D72" s="28">
         <v>0.54</v>
       </c>
       <c r="E72" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="F72" s="12">
+      <c r="F72" s="27">
         <v>0</v>
       </c>
       <c r="G72" s="10"/>
@@ -3258,13 +3282,13 @@
       <c r="B73" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="28">
         <v>0.35000000000000003</v>
       </c>
       <c r="E73" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="F73" s="12">
+      <c r="F73" s="27">
         <v>0</v>
       </c>
       <c r="G73" s="10"/>
@@ -3274,13 +3298,13 @@
       <c r="B74" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D74" s="11">
+      <c r="D74" s="28">
         <v>0.28000000000000003</v>
       </c>
       <c r="E74" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="F74" s="12">
+      <c r="F74" s="27">
         <v>0</v>
       </c>
       <c r="G74" s="10"/>
@@ -3290,13 +3314,13 @@
       <c r="B75" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D75" s="11">
+      <c r="D75" s="28">
         <v>0.64</v>
       </c>
       <c r="E75" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="F75" s="12">
+      <c r="F75" s="27">
         <v>0</v>
       </c>
       <c r="G75" s="10"/>
@@ -3311,14 +3335,14 @@
       <c r="C76" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="D76" s="11">
+      <c r="D76" s="28">
         <v>1.33</v>
       </c>
       <c r="E76" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="F76" s="12">
-        <v>179</v>
+      <c r="F76" s="27">
+        <v>146</v>
       </c>
       <c r="G76" s="10"/>
     </row>
@@ -3332,14 +3356,14 @@
       <c r="C77" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D77" s="11">
+      <c r="D77" s="28">
         <v>1.49</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="F77" s="12">
-        <v>151</v>
+      <c r="F77" s="27">
+        <v>109</v>
       </c>
       <c r="G77" s="10"/>
     </row>
@@ -3353,14 +3377,14 @@
       <c r="C78" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="D78" s="11">
+      <c r="D78" s="28">
         <v>1.6300000000000001</v>
       </c>
       <c r="E78" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="F78" s="12">
-        <v>302</v>
+      <c r="F78" s="27">
+        <v>272</v>
       </c>
       <c r="G78" s="10"/>
     </row>
@@ -3374,14 +3398,14 @@
       <c r="C79" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="D79" s="11">
+      <c r="D79" s="28">
         <v>1.82</v>
       </c>
       <c r="E79" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="F79" s="12">
-        <v>101</v>
+      <c r="F79" s="27">
+        <v>50</v>
       </c>
       <c r="G79" s="10"/>
     </row>
@@ -3395,14 +3419,14 @@
       <c r="C80" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="D80" s="11">
+      <c r="D80" s="28">
         <v>1.96</v>
       </c>
       <c r="E80" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="F80" s="12">
-        <v>59</v>
+      <c r="F80" s="27">
+        <v>24</v>
       </c>
       <c r="G80" s="10"/>
     </row>
@@ -3416,13 +3440,13 @@
       <c r="C81" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="D81" s="11">
+      <c r="D81" s="28">
         <v>2.13</v>
       </c>
       <c r="E81" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="F81" s="12">
+      <c r="F81" s="27">
         <v>156</v>
       </c>
       <c r="G81" s="10"/>
@@ -3437,14 +3461,14 @@
       <c r="C82" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="D82" s="11">
+      <c r="D82" s="28">
         <v>2.29</v>
       </c>
       <c r="E82" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="F82" s="12">
-        <v>138</v>
+      <c r="F82" s="27">
+        <v>97</v>
       </c>
       <c r="G82" s="10"/>
     </row>
@@ -3458,13 +3482,13 @@
       <c r="C83" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D83" s="28">
         <v>2.4700000000000002</v>
       </c>
       <c r="E83" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="F83" s="12">
+      <c r="F83" s="27">
         <v>2</v>
       </c>
       <c r="G83" s="10"/>
@@ -3479,13 +3503,13 @@
       <c r="C84" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="D84" s="11">
+      <c r="D84" s="28">
         <v>2.61</v>
       </c>
       <c r="E84" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="F84" s="12">
+      <c r="F84" s="27">
         <v>0</v>
       </c>
       <c r="G84" s="10"/>
@@ -3500,14 +3524,14 @@
       <c r="C85" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="D85" s="11">
-        <v>1.33</v>
+      <c r="D85" s="28">
+        <v>1.59</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="F85" s="12">
-        <v>167</v>
+      <c r="F85" s="27">
+        <v>166</v>
       </c>
       <c r="G85" s="10"/>
     </row>
@@ -3521,13 +3545,13 @@
       <c r="C86" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="D86" s="11">
-        <v>1.59</v>
+      <c r="D86" s="28">
+        <v>1.98</v>
       </c>
       <c r="E86" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="F86" s="12">
+      <c r="F86" s="27">
         <v>-3</v>
       </c>
       <c r="G86" s="10"/>
@@ -3542,13 +3566,13 @@
       <c r="C87" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="D87" s="11">
-        <v>1.98</v>
+      <c r="D87" s="28">
+        <v>2.38</v>
       </c>
       <c r="E87" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="F87" s="12">
+      <c r="F87" s="27">
         <v>0</v>
       </c>
       <c r="G87" s="10"/>
@@ -3563,14 +3587,14 @@
       <c r="C88" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D88" s="11">
-        <v>2.38</v>
+      <c r="D88" s="28">
+        <v>2.7600000000000002</v>
       </c>
       <c r="E88" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="F88" s="12">
-        <v>-10</v>
+      <c r="F88" s="27">
+        <v>-40</v>
       </c>
       <c r="G88" s="10"/>
     </row>
@@ -3579,13 +3603,13 @@
       <c r="B89" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="D89" s="11">
-        <v>2.7600000000000002</v>
+      <c r="D89" s="28">
+        <v>1.31</v>
       </c>
       <c r="E89" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="F89" s="12">
+      <c r="F89" s="27">
         <v>0</v>
       </c>
       <c r="G89" s="10"/>
@@ -3600,14 +3624,14 @@
       <c r="C90" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D90" s="11">
-        <v>1.31</v>
+      <c r="D90" s="28">
+        <v>3.12</v>
       </c>
       <c r="E90" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="F90" s="12">
-        <v>-11</v>
+      <c r="F90" s="27">
+        <v>68</v>
       </c>
       <c r="G90" s="10"/>
     </row>
@@ -3621,14 +3645,14 @@
       <c r="C91" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D91" s="11">
-        <v>3.12</v>
+      <c r="D91" s="28">
+        <v>3.5100000000000002</v>
       </c>
       <c r="E91" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="F91" s="12">
-        <v>50</v>
+      <c r="F91" s="27">
+        <v>43</v>
       </c>
       <c r="G91" s="10"/>
     </row>
@@ -3642,14 +3666,14 @@
       <c r="C92" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="D92" s="11">
-        <v>3.5100000000000002</v>
+      <c r="D92" s="28">
+        <v>3.91</v>
       </c>
       <c r="E92" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="F92" s="12">
-        <v>7</v>
+      <c r="F92" s="27">
+        <v>101</v>
       </c>
       <c r="G92" s="10"/>
     </row>
@@ -3663,14 +3687,14 @@
       <c r="C93" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="D93" s="11">
-        <v>3.91</v>
+      <c r="D93" s="28">
+        <v>4.3100000000000005</v>
       </c>
       <c r="E93" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="F93" s="12">
-        <v>112</v>
+      <c r="F93" s="27">
+        <v>92</v>
       </c>
       <c r="G93" s="10"/>
     </row>
@@ -3684,14 +3708,14 @@
       <c r="C94" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="D94" s="11">
-        <v>4.3100000000000005</v>
+      <c r="D94" s="28">
+        <v>4.68</v>
       </c>
       <c r="E94" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="F94" s="12">
-        <v>74</v>
+      <c r="F94" s="27">
+        <v>62</v>
       </c>
       <c r="G94" s="10"/>
     </row>
@@ -3705,13 +3729,13 @@
       <c r="C95" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D95" s="11">
-        <v>4.68</v>
+      <c r="D95" s="28">
+        <v>5.07</v>
       </c>
       <c r="E95" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="F95" s="12">
+      <c r="F95" s="27">
         <v>75</v>
       </c>
       <c r="G95" s="10"/>
@@ -3726,13 +3750,13 @@
       <c r="C96" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="D96" s="11">
-        <v>5.07</v>
+      <c r="D96" s="28">
+        <v>5.47</v>
       </c>
       <c r="E96" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="F96" s="12">
+      <c r="F96" s="27">
         <v>124</v>
       </c>
       <c r="G96" s="10"/>
@@ -3747,13 +3771,13 @@
       <c r="C97" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D97" s="11">
-        <v>5.47</v>
+      <c r="D97" s="28">
+        <v>5.87</v>
       </c>
       <c r="E97" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="F97" s="12">
+      <c r="F97" s="27">
         <v>28</v>
       </c>
       <c r="G97" s="10"/>
@@ -3763,13 +3787,13 @@
       <c r="B98" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="D98" s="11">
-        <v>5.87</v>
+      <c r="D98" s="28">
+        <v>1.69</v>
       </c>
       <c r="E98" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="F98" s="12">
+      <c r="F98" s="27">
         <v>91</v>
       </c>
       <c r="G98" s="10"/>
@@ -3784,14 +3808,14 @@
       <c r="C99" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="D99" s="11">
-        <v>1.69</v>
+      <c r="D99" s="28">
+        <v>3.98</v>
       </c>
       <c r="E99" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="F99" s="12">
-        <v>77</v>
+      <c r="F99" s="27">
+        <v>62</v>
       </c>
       <c r="G99" s="10"/>
     </row>
@@ -3805,13 +3829,13 @@
       <c r="C100" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="D100" s="11">
-        <v>3.98</v>
+      <c r="D100" s="28">
+        <v>5.12</v>
       </c>
       <c r="E100" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="F100" s="12">
+      <c r="F100" s="27">
         <v>60</v>
       </c>
       <c r="G100" s="10"/>
@@ -3826,13 +3850,13 @@
       <c r="C101" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="D101" s="11">
-        <v>5.12</v>
+      <c r="D101" s="28">
+        <v>5.94</v>
       </c>
       <c r="E101" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="F101" s="12">
+      <c r="F101" s="27">
         <v>52</v>
       </c>
       <c r="G101" s="10"/>
@@ -3847,13 +3871,13 @@
       <c r="C102" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="D102" s="11">
-        <v>5.94</v>
+      <c r="D102" s="28">
+        <v>6.92</v>
       </c>
       <c r="E102" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="F102" s="12">
+      <c r="F102" s="27">
         <v>58</v>
       </c>
       <c r="G102" s="10"/>
@@ -3863,13 +3887,13 @@
       <c r="B103" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="D103" s="11">
-        <v>6.92</v>
+      <c r="D103" s="28">
+        <v>2.13</v>
       </c>
       <c r="E103" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="F103" s="12">
+      <c r="F103" s="27">
         <v>0</v>
       </c>
       <c r="G103" s="10"/>
@@ -3884,14 +3908,14 @@
       <c r="C104" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="D104" s="11">
-        <v>2.13</v>
+      <c r="D104" s="28">
+        <v>5.1100000000000003</v>
       </c>
       <c r="E104" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="F104" s="12">
-        <v>21</v>
+      <c r="F104" s="27">
+        <v>39</v>
       </c>
       <c r="G104" s="10"/>
     </row>
@@ -3905,14 +3929,14 @@
       <c r="C105" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="D105" s="11">
-        <v>5.1100000000000003</v>
+      <c r="D105" s="28">
+        <v>5.76</v>
       </c>
       <c r="E105" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="F105" s="12">
-        <v>130</v>
+      <c r="F105" s="27">
+        <v>108</v>
       </c>
       <c r="G105" s="10"/>
     </row>
@@ -3926,14 +3950,14 @@
       <c r="C106" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="D106" s="11">
-        <v>5.76</v>
+      <c r="D106" s="28">
+        <v>6.3900000000000006</v>
       </c>
       <c r="E106" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="F106" s="12">
-        <v>66</v>
+      <c r="F106" s="27">
+        <v>17</v>
       </c>
       <c r="G106" s="10"/>
     </row>
@@ -3947,13 +3971,13 @@
       <c r="C107" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="D107" s="11">
-        <v>6.3900000000000006</v>
+      <c r="D107" s="28">
+        <v>7.03</v>
       </c>
       <c r="E107" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="F107" s="12">
+      <c r="F107" s="27">
         <v>47</v>
       </c>
       <c r="G107" s="10"/>
@@ -3968,14 +3992,14 @@
       <c r="C108" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="D108" s="11">
-        <v>7.03</v>
+      <c r="D108" s="28">
+        <v>7.68</v>
       </c>
       <c r="E108" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="F108" s="12">
-        <v>104</v>
+      <c r="F108" s="27">
+        <v>100</v>
       </c>
       <c r="G108" s="10"/>
     </row>
@@ -3989,13 +4013,13 @@
       <c r="C109" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="D109" s="11">
-        <v>7.68</v>
+      <c r="D109" s="28">
+        <v>8.31</v>
       </c>
       <c r="E109" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="F109" s="12">
+      <c r="F109" s="27">
         <v>169</v>
       </c>
       <c r="G109" s="10"/>
@@ -4010,13 +4034,13 @@
       <c r="C110" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="D110" s="11">
-        <v>8.31</v>
+      <c r="D110" s="28">
+        <v>8.9500000000000011</v>
       </c>
       <c r="E110" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="F110" s="12">
+      <c r="F110" s="27">
         <v>23</v>
       </c>
       <c r="G110" s="10"/>
@@ -4031,13 +4055,13 @@
       <c r="C111" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D111" s="11">
-        <v>8.9500000000000011</v>
+      <c r="D111" s="28">
+        <v>9.61</v>
       </c>
       <c r="E111" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="F111" s="12">
+      <c r="F111" s="27">
         <v>8</v>
       </c>
       <c r="G111" s="10"/>
@@ -4047,13 +4071,13 @@
       <c r="B112" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D112" s="11">
-        <v>9.61</v>
+      <c r="D112" s="28">
+        <v>4.2700000000000005</v>
       </c>
       <c r="E112" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="F112" s="12">
+      <c r="F112" s="27">
         <v>0</v>
       </c>
       <c r="G112" s="10"/>
@@ -4068,14 +4092,14 @@
       <c r="C113" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="D113" s="11">
-        <v>4.2700000000000005</v>
+      <c r="D113" s="28">
+        <v>10.220000000000001</v>
       </c>
       <c r="E113" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="F113" s="12">
-        <v>10</v>
+      <c r="F113" s="27">
+        <v>23</v>
       </c>
       <c r="G113" s="10"/>
     </row>
@@ -4089,14 +4113,14 @@
       <c r="C114" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D114" s="11">
-        <v>10.220000000000001</v>
+      <c r="D114" s="28">
+        <v>11.5</v>
       </c>
       <c r="E114" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="F114" s="12">
-        <v>18</v>
+      <c r="F114" s="27">
+        <v>14</v>
       </c>
       <c r="G114" s="10"/>
     </row>
@@ -4110,14 +4134,14 @@
       <c r="C115" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D115" s="11">
-        <v>11.5</v>
+      <c r="D115" s="28">
+        <v>12.780000000000001</v>
       </c>
       <c r="E115" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="F115" s="12">
-        <v>16</v>
+      <c r="F115" s="27">
+        <v>8</v>
       </c>
       <c r="G115" s="10"/>
     </row>
@@ -4131,14 +4155,14 @@
       <c r="C116" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="D116" s="11">
-        <v>12.780000000000001</v>
+      <c r="D116" s="28">
+        <v>14.07</v>
       </c>
       <c r="E116" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="F116" s="12">
-        <v>2</v>
+      <c r="F116" s="27">
+        <v>12</v>
       </c>
       <c r="G116" s="10"/>
     </row>
@@ -4152,14 +4176,14 @@
       <c r="C117" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="D117" s="11">
-        <v>14.07</v>
+      <c r="D117" s="28">
+        <v>15.34</v>
       </c>
       <c r="E117" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F117" s="12">
-        <v>16</v>
+      <c r="F117" s="27">
+        <v>15</v>
       </c>
       <c r="G117" s="10"/>
     </row>
@@ -4173,13 +4197,13 @@
       <c r="C118" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="D118" s="11">
-        <v>15.34</v>
+      <c r="D118" s="28">
+        <v>16.61</v>
       </c>
       <c r="E118" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="F118" s="12">
+      <c r="F118" s="27">
         <v>32</v>
       </c>
       <c r="G118" s="10"/>
@@ -4194,14 +4218,14 @@
       <c r="C119" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D119" s="11">
-        <v>16.61</v>
+      <c r="D119" s="28">
+        <v>17.88</v>
       </c>
       <c r="E119" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="F119" s="12">
-        <v>25</v>
+      <c r="F119" s="27">
+        <v>23</v>
       </c>
       <c r="G119" s="10"/>
     </row>
@@ -4215,13 +4239,13 @@
       <c r="C120" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="D120" s="11">
-        <v>17.88</v>
+      <c r="D120" s="28">
+        <v>19.12</v>
       </c>
       <c r="E120" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="F120" s="12">
+      <c r="F120" s="27">
         <v>11</v>
       </c>
       <c r="G120" s="10"/>
@@ -4231,13 +4255,13 @@
       <c r="B121" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="D121" s="11">
-        <v>19.12</v>
+      <c r="D121" s="28">
+        <v>8.02</v>
       </c>
       <c r="E121" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="F121" s="12">
+      <c r="F121" s="27">
         <v>0</v>
       </c>
       <c r="G121" s="10"/>
@@ -4252,13 +4276,13 @@
       <c r="C122" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D122" s="11">
-        <v>8.02</v>
+      <c r="D122" s="28">
+        <v>18.100000000000001</v>
       </c>
       <c r="E122" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="F122" s="12">
+      <c r="F122" s="27">
         <v>18</v>
       </c>
       <c r="G122" s="10"/>
@@ -4273,13 +4297,13 @@
       <c r="C123" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="D123" s="11">
-        <v>18.100000000000001</v>
+      <c r="D123" s="28">
+        <v>22.64</v>
       </c>
       <c r="E123" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="F123" s="12">
+      <c r="F123" s="27">
         <v>26</v>
       </c>
       <c r="G123" s="10"/>
@@ -4294,13 +4318,13 @@
       <c r="C124" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="D124" s="11">
-        <v>22.64</v>
+      <c r="D124" s="28">
+        <v>27.150000000000002</v>
       </c>
       <c r="E124" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="F124" s="12">
+      <c r="F124" s="27">
         <v>23</v>
       </c>
       <c r="G124" s="10"/>
@@ -4315,13 +4339,13 @@
       <c r="C125" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="D125" s="11">
-        <v>27.150000000000002</v>
+      <c r="D125" s="28">
+        <v>31.69</v>
       </c>
       <c r="E125" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="F125" s="12">
+      <c r="F125" s="27">
         <v>15</v>
       </c>
       <c r="G125" s="10"/>
@@ -4336,13 +4360,13 @@
       <c r="C126" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D126" s="11">
-        <v>31.69</v>
+      <c r="D126" s="28">
+        <v>33.94</v>
       </c>
       <c r="E126" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="F126" s="12">
+      <c r="F126" s="27">
         <v>0</v>
       </c>
       <c r="G126" s="10"/>
@@ -4357,13 +4381,13 @@
       <c r="C127" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="D127" s="11">
-        <v>33.94</v>
+      <c r="D127" s="28">
+        <v>36.22</v>
       </c>
       <c r="E127" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="F127" s="12">
+      <c r="F127" s="27">
         <v>0</v>
       </c>
       <c r="G127" s="10"/>
@@ -4374,7 +4398,7 @@
         <v>278</v>
       </c>
       <c r="D128" s="11">
-        <v>36.22</v>
+        <v>0</v>
       </c>
       <c r="E128" s="19" t="s">
         <v>255</v>
@@ -4394,13 +4418,13 @@
       <c r="C129" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="D129" s="11">
+      <c r="D129" s="29">
         <v>5.12</v>
       </c>
       <c r="E129" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="F129" s="12">
+      <c r="F129" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4414,14 +4438,14 @@
       <c r="C130" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="D130" s="11">
-        <v>4.07</v>
+      <c r="D130" s="29">
+        <v>3.93</v>
       </c>
       <c r="E130" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="F130" s="12">
-        <v>302</v>
+      <c r="F130" s="30">
+        <v>111</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
@@ -4434,14 +4458,14 @@
       <c r="C131" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="D131" s="11">
+      <c r="D131" s="29">
         <v>4.53</v>
       </c>
       <c r="E131" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="F131" s="12">
-        <v>9</v>
+      <c r="F131" s="30">
+        <v>276</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
@@ -4454,14 +4478,14 @@
       <c r="C132" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D132" s="11">
+      <c r="D132" s="29">
         <v>6.7</v>
       </c>
       <c r="E132" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="F132" s="12">
-        <v>221</v>
+      <c r="F132" s="30">
+        <v>201</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
@@ -4474,13 +4498,13 @@
       <c r="C133" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D133" s="11">
+      <c r="D133" s="29">
         <v>8.31</v>
       </c>
       <c r="E133" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="F133" s="12">
+      <c r="F133" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4494,13 +4518,13 @@
       <c r="C134" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="D134" s="11">
+      <c r="D134" s="29">
         <v>7.8900000000000006</v>
       </c>
       <c r="E134" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="F134" s="12">
+      <c r="F134" s="30">
         <v>373</v>
       </c>
     </row>
@@ -4514,13 +4538,13 @@
       <c r="C135" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="D135" s="11">
+      <c r="D135" s="29">
         <v>9.61</v>
       </c>
       <c r="E135" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="F135" s="12">
+      <c r="F135" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4529,13 +4553,13 @@
       <c r="B136" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="D136" s="11">
+      <c r="D136" s="29">
         <v>3.5500000000000003</v>
       </c>
       <c r="E136" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="F136" s="12">
+      <c r="F136" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4549,14 +4573,14 @@
       <c r="C137" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="D137" s="11">
+      <c r="D137" s="29">
         <v>6.22</v>
       </c>
       <c r="E137" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="F137" s="12">
-        <v>351</v>
+      <c r="F137" s="30">
+        <v>332</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
@@ -4569,14 +4593,14 @@
       <c r="C138" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D138" s="11">
-        <v>6.91</v>
+      <c r="D138" s="29">
+        <v>6.7</v>
       </c>
       <c r="E138" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="F138" s="12">
-        <v>162</v>
+      <c r="F138" s="30">
+        <v>83</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
@@ -4589,13 +4613,13 @@
       <c r="C139" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D139" s="11">
+      <c r="D139" s="29">
         <v>10.91</v>
       </c>
       <c r="E139" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="F139" s="12">
+      <c r="F139" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4609,14 +4633,14 @@
       <c r="C140" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="D140" s="11">
+      <c r="D140" s="29">
         <v>10.370000000000001</v>
       </c>
       <c r="E140" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="F140" s="12">
-        <v>223</v>
+      <c r="F140" s="30">
+        <v>203</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
@@ -4629,14 +4653,14 @@
       <c r="C141" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D141" s="11">
-        <v>13.88</v>
+      <c r="D141" s="29">
+        <v>6.76</v>
       </c>
       <c r="E141" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="F141" s="12">
-        <v>143</v>
+      <c r="F141" s="30">
+        <v>141</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
@@ -4649,13 +4673,13 @@
       <c r="C142" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="D142" s="11">
+      <c r="D142" s="29">
         <v>9.23</v>
       </c>
       <c r="E142" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="F142" s="12">
+      <c r="F142" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4669,13 +4693,13 @@
       <c r="C143" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D143" s="11">
+      <c r="D143" s="29">
         <v>11.14</v>
       </c>
       <c r="E143" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="F143" s="12">
+      <c r="F143" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4684,13 +4708,13 @@
       <c r="B144" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="D144" s="11">
+      <c r="D144" s="29">
         <v>3.17</v>
       </c>
       <c r="E144" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="F144" s="12">
+      <c r="F144" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4704,13 +4728,13 @@
       <c r="C145" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="D145" s="11">
+      <c r="D145" s="29">
         <v>7.2</v>
       </c>
       <c r="E145" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="F145" s="12">
+      <c r="F145" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4724,13 +4748,13 @@
       <c r="C146" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="D146" s="11">
+      <c r="D146" s="29">
         <v>18.11</v>
       </c>
       <c r="E146" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="F146" s="12">
+      <c r="F146" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4744,14 +4768,14 @@
       <c r="C147" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D147" s="11">
+      <c r="D147" s="29">
         <v>11.94</v>
       </c>
       <c r="E147" s="19" t="s">
         <v>274</v>
       </c>
-      <c r="F147" s="12">
-        <v>99</v>
+      <c r="F147" s="30">
+        <v>88</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
@@ -4764,13 +4788,13 @@
       <c r="C148" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="D148" s="11">
+      <c r="D148" s="29">
         <v>15.16</v>
       </c>
       <c r="E148" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="F148" s="12">
+      <c r="F148" s="30">
         <v>47</v>
       </c>
     </row>
@@ -4784,14 +4808,14 @@
       <c r="C149" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D149" s="11">
+      <c r="D149" s="29">
         <v>13.52</v>
       </c>
       <c r="E149" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="F149" s="12">
-        <v>106</v>
+      <c r="F149" s="30">
+        <v>50</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
@@ -4804,13 +4828,13 @@
       <c r="C150" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="D150" s="11">
+      <c r="D150" s="29">
         <v>24.89</v>
       </c>
       <c r="E150" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="F150" s="12">
+      <c r="F150" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4904,13 +4928,13 @@
       <c r="C155" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D155" s="11">
+      <c r="D155" s="31">
         <v>9.82</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="F155" s="12">
+      <c r="F155" s="32">
         <v>1</v>
       </c>
     </row>
@@ -4924,14 +4948,14 @@
       <c r="C156" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D156" s="11">
+      <c r="D156" s="31">
         <v>9.82</v>
       </c>
       <c r="E156" s="10" t="s">
         <v>439</v>
       </c>
-      <c r="F156" s="12">
-        <v>0</v>
+      <c r="F156" s="32">
+        <v>-2</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
@@ -4944,13 +4968,13 @@
       <c r="C157" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D157" s="11">
+      <c r="D157" s="31">
         <v>9.82</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>440</v>
       </c>
-      <c r="F157" s="12">
+      <c r="F157" s="32">
         <v>0</v>
       </c>
     </row>
@@ -4964,13 +4988,13 @@
       <c r="C158" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D158" s="11">
+      <c r="D158" s="31">
         <v>9.82</v>
       </c>
       <c r="E158" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="F158" s="12">
+      <c r="F158" s="32">
         <v>2</v>
       </c>
     </row>
@@ -4984,13 +5008,13 @@
       <c r="C159" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D159" s="11">
+      <c r="D159" s="31">
         <v>9.82</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="F159" s="12">
+      <c r="F159" s="32">
         <v>0</v>
       </c>
     </row>
@@ -5004,13 +5028,13 @@
       <c r="C160" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D160" s="11">
+      <c r="D160" s="31">
         <v>9.82</v>
       </c>
       <c r="E160" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="F160" s="12">
+      <c r="F160" s="32">
         <v>0</v>
       </c>
     </row>
@@ -5024,14 +5048,14 @@
       <c r="C161" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="D161" s="11">
+      <c r="D161" s="31">
         <v>6.3</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="F161" s="12">
-        <v>4</v>
+      <c r="F161" s="32">
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\bois\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05FD4653-F7C8-4F8B-A093-1E25371FF0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FA628D-EB14-477E-BD77-AE4079CEFEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23124" yWindow="12" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="471">
   <si>
     <t>path</t>
   </si>
@@ -977,18 +977,6 @@
     <t>galerie/sous-toiture.png</t>
   </si>
   <si>
-    <t>OSB12-59x244</t>
-  </si>
-  <si>
-    <t>OSB15-59x244</t>
-  </si>
-  <si>
-    <t>OSB22-59x244</t>
-  </si>
-  <si>
-    <t>OSB18-59x244</t>
-  </si>
-  <si>
     <t>3mm-122x244</t>
   </si>
   <si>
@@ -1431,6 +1419,36 @@
   </si>
   <si>
     <t>71175236</t>
+  </si>
+  <si>
+    <t>11201111</t>
+  </si>
+  <si>
+    <t>11201112</t>
+  </si>
+  <si>
+    <t>OSB III 12 rainuré 59x244 KRONO</t>
+  </si>
+  <si>
+    <t>OSB III 18 rainuré 59x244 KRONO</t>
+  </si>
+  <si>
+    <t>OSB12-59x244-Krono</t>
+  </si>
+  <si>
+    <t>OSB18-59x244-Krono</t>
+  </si>
+  <si>
+    <t>OSB12-59x244-Sterling</t>
+  </si>
+  <si>
+    <t>OSB15-59x244-Sterling</t>
+  </si>
+  <si>
+    <t>OSB18-59x244-Sterling</t>
+  </si>
+  <si>
+    <t>OSB22-59x244-Sterling</t>
   </si>
 </sst>
 </file>
@@ -1514,7 +1532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1586,22 +1604,29 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1944,7 +1969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065E4AF0-A4F8-4CE3-9E23-EDCEACB756BD}">
-  <dimension ref="A1:G451"/>
+  <dimension ref="A1:G453"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37" style="4" bestFit="1" customWidth="1"/>
@@ -1975,7 +2000,7 @@
       <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -1985,17 +2010,18 @@
         <v>75</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D2" s="25">
+        <v>337</v>
+      </c>
+      <c r="D2" s="11">
         <v>15.44</v>
       </c>
       <c r="E2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="12">
         <v>104.88500000000023</v>
       </c>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -2005,17 +2031,18 @@
         <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D3" s="25">
+        <v>338</v>
+      </c>
+      <c r="D3" s="11">
         <v>18.73</v>
       </c>
       <c r="E3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="12">
         <v>0</v>
       </c>
+      <c r="G3" s="26"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -2025,17 +2052,18 @@
         <v>77</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D4" s="25">
+        <v>467</v>
+      </c>
+      <c r="D4" s="11">
         <v>8.81</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="12">
         <v>132.01899999999907</v>
       </c>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
@@ -2045,3034 +2073,3144 @@
         <v>78</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="D5" s="25">
+        <v>468</v>
+      </c>
+      <c r="D5" s="11">
         <v>10.78</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="12">
         <v>256.31999999999971</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="G5" s="26"/>
+    </row>
+    <row r="6" spans="1:7" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D6" s="27">
+        <v>8.01</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>461</v>
+      </c>
+      <c r="F6" s="28">
+        <v>374.22</v>
+      </c>
+      <c r="G6" s="26"/>
+    </row>
+    <row r="7" spans="1:7" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D7" s="27">
+        <v>11.33</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>462</v>
+      </c>
+      <c r="F7" s="28">
+        <v>287.92</v>
+      </c>
+      <c r="G7" s="26"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B8" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="D6" s="25">
+      <c r="C8" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D8" s="11">
         <v>12.41</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E8" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F8" s="12">
         <v>374.39999999999981</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="G8" s="26"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B9" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D7" s="25">
+      <c r="C9" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D9" s="11">
         <v>15.74</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F9" s="12">
         <v>83.518000000000654</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="25">
-        <v>14.71</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="26">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" s="25">
-        <v>22.580000000000002</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="26">
-        <v>90</v>
-      </c>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" s="25">
-        <v>44.06</v>
+        <v>81</v>
+      </c>
+      <c r="D10" s="11">
+        <v>14.71</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="26">
-        <v>11.519999999999982</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F10" s="12">
+        <v>30</v>
+      </c>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="25">
-        <v>91.48</v>
+        <v>82</v>
+      </c>
+      <c r="D11" s="11">
+        <v>22.580000000000002</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="26">
-        <v>0</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F11" s="12">
+        <v>90</v>
+      </c>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="11">
+        <v>44.06</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="12">
+        <v>11.519999999999982</v>
+      </c>
+      <c r="G12" s="26"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="11">
+        <v>91.48</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="12">
+        <v>0</v>
+      </c>
+      <c r="G13" s="26"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D14" s="11">
         <v>2.31</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E14" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F14" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="D13" s="25">
-        <v>7.79</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="26">
-        <v>14.900000000000224</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D14" s="25">
-        <v>10.83</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="26">
-        <v>32.024999999999835</v>
-      </c>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D15" s="25">
-        <v>13.94</v>
+        <v>313</v>
+      </c>
+      <c r="D15" s="11">
+        <v>7.79</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="26">
-        <v>4.4750000000002101</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F15" s="12">
+        <v>14.900000000000224</v>
+      </c>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>304</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D16" s="25">
-        <v>0</v>
+        <v>314</v>
+      </c>
+      <c r="D16" s="11">
+        <v>10.83</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="F16" s="12">
+        <v>32.024999999999835</v>
+      </c>
+      <c r="G16" s="26"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>304</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D17" s="25">
-        <v>20.09</v>
+        <v>315</v>
+      </c>
+      <c r="D17" s="11">
+        <v>13.94</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="26">
-        <v>4.9999999981578114E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="F17" s="12">
+        <v>4.4750000000002101</v>
+      </c>
+      <c r="G17" s="26"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>304</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D18" s="25">
-        <v>16.75</v>
+        <v>316</v>
+      </c>
+      <c r="D18" s="11">
+        <v>0</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="26">
+        <v>20</v>
+      </c>
+      <c r="F18" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="26"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>304</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D19" s="25">
-        <v>19.990000000000002</v>
+        <v>317</v>
+      </c>
+      <c r="D19" s="11">
+        <v>20.09</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="26">
-        <v>120.08799999999336</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="F19" s="12">
+        <v>4.9999999981578114E-3</v>
+      </c>
+      <c r="G19" s="26"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>304</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="D20" s="25">
-        <v>28.560000000000002</v>
+        <v>91</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D20" s="11">
+        <v>16.75</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="26">
-        <v>167.15000000000467</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="F20" s="12">
+        <v>0</v>
+      </c>
+      <c r="G20" s="26"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>304</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="D21" s="25">
-        <v>28.34</v>
+        <v>92</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D21" s="11">
+        <v>19.990000000000002</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="26">
-        <v>144.26200000000185</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="F21" s="12">
+        <v>120.08799999999336</v>
+      </c>
+      <c r="G21" s="26"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>304</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="D22" s="25">
-        <v>54.51</v>
+        <v>93</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D22" s="11">
+        <v>28.560000000000002</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="26">
-        <v>-4.9999999999914557E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="F22" s="12">
+        <v>167.15000000000467</v>
+      </c>
+      <c r="G22" s="26"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>304</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="D23" s="11">
+        <v>28.34</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="12">
+        <v>144.26200000000185</v>
+      </c>
+      <c r="G23" s="26"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D24" s="11">
+        <v>54.51</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="12">
+        <v>-4.9999999999914557E-3</v>
+      </c>
+      <c r="G24" s="26"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D23" s="25">
+      <c r="C25" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D25" s="11">
         <v>39.340000000000003</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E25" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="26">
+      <c r="F25" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D24" s="25">
-        <v>9.4500000000000011</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="26">
-        <v>35.736999999999895</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="D25" s="25">
-        <v>10.39</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="F25" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25" s="26"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>305</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D26" s="25">
-        <v>8.98</v>
+        <v>324</v>
+      </c>
+      <c r="D26" s="11">
+        <v>9.4500000000000011</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="26">
-        <v>65.337999999999596</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="F26" s="12">
+        <v>35.736999999999895</v>
+      </c>
+      <c r="G26" s="26"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>305</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="D27" s="25">
-        <v>10.81</v>
+        <v>325</v>
+      </c>
+      <c r="D27" s="11">
+        <v>10.39</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" s="26">
-        <v>142.54700000000011</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="F27" s="12">
+        <v>0</v>
+      </c>
+      <c r="G27" s="26"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>305</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="D28" s="25">
-        <v>8.8000000000000007</v>
+        <v>326</v>
+      </c>
+      <c r="D28" s="11">
+        <v>8.98</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="F28" s="12">
+        <v>65.337999999999596</v>
+      </c>
+      <c r="G28" s="26"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>305</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="D29" s="25">
-        <v>16.080000000000002</v>
+        <v>327</v>
+      </c>
+      <c r="D29" s="11">
+        <v>10.81</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="F29" s="26">
-        <v>176.0489999999939</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="F29" s="12">
+        <v>142.54700000000011</v>
+      </c>
+      <c r="G29" s="26"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>305</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D30" s="25">
-        <v>15.71</v>
+        <v>328</v>
+      </c>
+      <c r="D30" s="11">
+        <v>8.8000000000000007</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F30" s="26">
+        <v>32</v>
+      </c>
+      <c r="F30" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="26"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>305</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="D31" s="25">
-        <v>31.3</v>
+        <v>330</v>
+      </c>
+      <c r="D31" s="11">
+        <v>16.080000000000002</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="F31" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="F31" s="12">
+        <v>176.0489999999939</v>
+      </c>
+      <c r="G31" s="26"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>305</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D32" s="25">
-        <v>31.3</v>
+        <v>329</v>
+      </c>
+      <c r="D32" s="11">
+        <v>15.71</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F32" s="26">
+        <v>34</v>
+      </c>
+      <c r="F32" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32" s="26"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>305</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D33" s="25">
-        <v>12.98</v>
+        <v>331</v>
+      </c>
+      <c r="D33" s="11">
+        <v>31.3</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="F33" s="26">
-        <v>152.56700000000018</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="F33" s="12">
+        <v>0</v>
+      </c>
+      <c r="G33" s="26"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>305</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D34" s="25">
-        <v>18.11</v>
+        <v>332</v>
+      </c>
+      <c r="D34" s="11">
+        <v>31.3</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" s="26">
-        <v>152.87599999999372</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="F34" s="12">
+        <v>0</v>
+      </c>
+      <c r="G34" s="26"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>305</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="D35" s="25">
-        <v>18.97</v>
+        <v>336</v>
+      </c>
+      <c r="D35" s="11">
+        <v>12.98</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="F35" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="F35" s="12">
+        <v>152.56700000000018</v>
+      </c>
+      <c r="G35" s="26"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>305</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D36" s="25">
-        <v>24.560000000000002</v>
+        <v>335</v>
+      </c>
+      <c r="D36" s="11">
+        <v>18.11</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="F36" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="F36" s="12">
+        <v>152.87599999999372</v>
+      </c>
+      <c r="G36" s="26"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>305</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D37" s="25">
-        <v>56.24</v>
+        <v>333</v>
+      </c>
+      <c r="D37" s="11">
+        <v>18.97</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="F37" s="26">
+        <v>39</v>
+      </c>
+      <c r="F37" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37" s="26"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>305</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D38" s="25">
-        <v>91.48</v>
+        <v>339</v>
+      </c>
+      <c r="D38" s="11">
+        <v>24.560000000000002</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="F38" s="26">
+        <v>40</v>
+      </c>
+      <c r="F38" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38" s="26"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>305</v>
       </c>
       <c r="B39" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D39" s="11">
+        <v>56.24</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F39" s="12">
+        <v>0</v>
+      </c>
+      <c r="G39" s="26"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D40" s="11">
+        <v>91.48</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="12">
+        <v>0</v>
+      </c>
+      <c r="G40" s="26"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D39" s="25">
+      <c r="C41" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D41" s="11">
         <v>30.060000000000002</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E41" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="26">
+      <c r="F41" s="12">
         <v>87.61900000000422</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="5"/>
-      <c r="B40" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D40" s="25">
-        <v>34.82</v>
-      </c>
-      <c r="E40" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F40" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="5"/>
-      <c r="B41" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D41" s="25">
-        <v>16.64</v>
-      </c>
-      <c r="E41" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="F41" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41" s="26"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="D42" s="25">
-        <v>24.72</v>
+        <v>112</v>
+      </c>
+      <c r="D42" s="11">
+        <v>34.82</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F42" s="26">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="F42" s="12">
+        <v>0</v>
+      </c>
+      <c r="G42" s="26"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D43" s="25">
-        <v>25.16</v>
+        <v>113</v>
+      </c>
+      <c r="D43" s="11">
+        <v>16.64</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="F43" s="26">
-        <v>4.3964831775156199E-14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="F43" s="12">
+        <v>0</v>
+      </c>
+      <c r="G43" s="26"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D44" s="25">
-        <v>28.8</v>
+        <v>114</v>
+      </c>
+      <c r="D44" s="11">
+        <v>24.72</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F44" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="F44" s="12">
+        <v>2.34</v>
+      </c>
+      <c r="G44" s="26"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="D45" s="25">
-        <v>52.6</v>
+        <v>115</v>
+      </c>
+      <c r="D45" s="11">
+        <v>25.16</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="F45" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="F45" s="12">
+        <v>4.3964831775156199E-14</v>
+      </c>
+      <c r="G45" s="26"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="D46" s="25">
-        <v>33.380000000000003</v>
+        <v>116</v>
+      </c>
+      <c r="D46" s="11">
+        <v>28.8</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="F46" s="26">
+        <v>48</v>
+      </c>
+      <c r="F46" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G46" s="26"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="D47" s="25">
-        <v>40.730000000000004</v>
+        <v>117</v>
+      </c>
+      <c r="D47" s="11">
+        <v>52.6</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="F47" s="26">
+        <v>49</v>
+      </c>
+      <c r="F47" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G47" s="26"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D48" s="25">
-        <v>85.05</v>
+        <v>118</v>
+      </c>
+      <c r="D48" s="11">
+        <v>33.380000000000003</v>
       </c>
       <c r="E48" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F48" s="26">
+        <v>50</v>
+      </c>
+      <c r="F48" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G48" s="26"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D49" s="11">
+        <v>40.730000000000004</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F49" s="12">
+        <v>0</v>
+      </c>
+      <c r="G49" s="26"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="5"/>
+      <c r="B50" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D50" s="11">
+        <v>85.05</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F50" s="12">
+        <v>0</v>
+      </c>
+      <c r="G50" s="26"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="5"/>
+      <c r="B51" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="25">
+      <c r="D51" s="11">
         <v>97.73</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="E51" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F49" s="26">
+      <c r="F51" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D50" s="25">
-        <v>30.95</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="F50" s="26">
-        <v>4.6799999999999837</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D51" s="25">
-        <v>25.310000000000002</v>
-      </c>
-      <c r="E51" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="F51" s="26">
-        <v>10.921000000000276</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G51" s="26"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>306</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="D52" s="25">
-        <v>26.55</v>
+        <v>342</v>
+      </c>
+      <c r="D52" s="11">
+        <v>30.95</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="F52" s="26">
-        <v>80.649999999997618</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F52" s="12">
+        <v>4.6799999999999837</v>
+      </c>
+      <c r="G52" s="26"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>306</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D53" s="25">
-        <v>37.869999999999997</v>
+        <v>343</v>
+      </c>
+      <c r="D53" s="11">
+        <v>25.310000000000002</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="F53" s="26">
-        <v>-3.3010000000018076</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F53" s="12">
+        <v>10.921000000000276</v>
+      </c>
+      <c r="G53" s="26"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>306</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D54" s="25">
-        <v>22.59</v>
+        <v>344</v>
+      </c>
+      <c r="D54" s="11">
+        <v>26.55</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="F54" s="26">
-        <v>134.36999999999941</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+      <c r="F54" s="12">
+        <v>80.649999999997618</v>
+      </c>
+      <c r="G54" s="26"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>306</v>
       </c>
       <c r="B55" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D55" s="11">
+        <v>37.869999999999997</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F55" s="12">
+        <v>-3.3010000000018076</v>
+      </c>
+      <c r="G55" s="26"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D56" s="11">
+        <v>22.59</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="F56" s="12">
+        <v>134.36999999999941</v>
+      </c>
+      <c r="G56" s="26"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B57" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D55" s="25">
+      <c r="C57" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D57" s="11">
         <v>33.380000000000003</v>
       </c>
-      <c r="E55" s="19" t="s">
+      <c r="E57" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F55" s="26">
+      <c r="F57" s="12">
         <v>95.970000000011566</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="5"/>
-      <c r="B56" s="14" t="s">
+      <c r="G57" s="26"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="5"/>
+      <c r="B58" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D56" s="25">
+      <c r="D58" s="11">
         <v>71.77</v>
       </c>
-      <c r="E56" s="19" t="s">
+      <c r="E58" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F56" s="26">
+      <c r="F58" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="5"/>
-      <c r="B57" s="14" t="s">
+      <c r="G58" s="26"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="5"/>
+      <c r="B59" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="25">
+      <c r="D59" s="11">
         <v>68.930000000000007</v>
       </c>
-      <c r="E57" s="19" t="s">
+      <c r="E59" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F57" s="26">
+      <c r="F59" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D58" s="25">
-        <v>47.94</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="F58" s="26">
-        <v>62.399999999999942</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D59" s="25">
-        <v>25.18</v>
-      </c>
-      <c r="E59" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="F59" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G59" s="26"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>306</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="D60" s="25">
-        <v>39.07</v>
+        <v>350</v>
+      </c>
+      <c r="D60" s="11">
+        <v>47.94</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="F60" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+      <c r="F60" s="12">
+        <v>62.399999999999942</v>
+      </c>
+      <c r="G60" s="26"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>306</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D61" s="25">
-        <v>42.52</v>
+        <v>350</v>
+      </c>
+      <c r="D61" s="11">
+        <v>25.18</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F61" s="26">
-        <v>-4.9999999997818456E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+      <c r="F61" s="12">
+        <v>0</v>
+      </c>
+      <c r="G61" s="26"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>306</v>
       </c>
       <c r="B62" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D62" s="11">
+        <v>39.07</v>
+      </c>
+      <c r="E62" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F62" s="12">
+        <v>0</v>
+      </c>
+      <c r="G62" s="26"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D63" s="11">
+        <v>42.52</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F63" s="12">
+        <v>-4.9999999997818456E-3</v>
+      </c>
+      <c r="G63" s="26"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B64" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D62" s="25">
-        <v>39.910000000000004</v>
-      </c>
-      <c r="E62" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="F62" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="5"/>
-      <c r="B63" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D63" s="25">
-        <v>33.730000000000004</v>
-      </c>
-      <c r="E63" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="F63" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>136</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D64" s="25">
+      <c r="D64" s="11">
+        <v>39.910000000000004</v>
+      </c>
+      <c r="E64" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F64" s="12">
+        <v>0</v>
+      </c>
+      <c r="G64" s="26"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="5"/>
+      <c r="B65" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" s="11">
+        <v>33.730000000000004</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F65" s="12">
+        <v>0</v>
+      </c>
+      <c r="G65" s="26"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D66" s="11">
         <v>38.94</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="E66" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="F64" s="26">
+      <c r="F66" s="12">
         <v>12.200000000000017</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="5" t="s">
+      <c r="G66" s="26"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B67" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D65" s="25">
+      <c r="C67" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D67" s="11">
         <v>46.37</v>
       </c>
-      <c r="E65" s="19" t="s">
+      <c r="E67" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="F65" s="26">
+      <c r="F67" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="5"/>
-      <c r="B66" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D66" s="25">
-        <v>59.300000000000004</v>
-      </c>
-      <c r="E66" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F66" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="5"/>
-      <c r="B67" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="D67" s="25">
-        <v>88.92</v>
-      </c>
-      <c r="E67" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="F67" s="26">
-        <v>0</v>
-      </c>
+      <c r="G67" s="26"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D68" s="25">
-        <v>118.54</v>
+        <v>138</v>
+      </c>
+      <c r="D68" s="11">
+        <v>59.300000000000004</v>
       </c>
       <c r="E68" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="F68" s="26">
+        <v>70</v>
+      </c>
+      <c r="F68" s="12">
         <v>0</v>
       </c>
+      <c r="G68" s="26"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D69" s="25">
-        <v>185.26</v>
+        <v>139</v>
+      </c>
+      <c r="D69" s="11">
+        <v>88.92</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="F69" s="26">
+        <v>71</v>
+      </c>
+      <c r="F69" s="12">
         <v>0</v>
       </c>
+      <c r="G69" s="26"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="D70" s="25">
-        <v>169.62</v>
+        <v>140</v>
+      </c>
+      <c r="D70" s="11">
+        <v>118.54</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="F70" s="26">
+        <v>72</v>
+      </c>
+      <c r="F70" s="12">
         <v>0</v>
       </c>
+      <c r="G70" s="26"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
-      <c r="B71" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D71" s="28">
-        <v>0.69000000000000006</v>
-      </c>
-      <c r="E71" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="F71" s="27">
-        <v>550.80000000000132</v>
-      </c>
-      <c r="G71" s="10"/>
+      <c r="B71" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D71" s="11">
+        <v>185.26</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F71" s="12">
+        <v>0</v>
+      </c>
+      <c r="G71" s="26"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
-      <c r="B72" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="D72" s="28">
-        <v>0.54</v>
-      </c>
-      <c r="E72" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="F72" s="27">
+      <c r="B72" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D72" s="11">
+        <v>169.62</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F72" s="12">
         <v>0</v>
       </c>
-      <c r="G72" s="10"/>
+      <c r="G72" s="30"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
-      <c r="B73" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="D73" s="28">
-        <v>0.35000000000000003</v>
+      <c r="B73" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D73" s="31">
+        <v>0.69000000000000006</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="F73" s="27">
-        <v>0</v>
-      </c>
-      <c r="G73" s="10"/>
+        <v>199</v>
+      </c>
+      <c r="F73" s="32">
+        <v>550.80000000000132</v>
+      </c>
+      <c r="G73" s="30"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D74" s="28">
-        <v>0.28000000000000003</v>
+        <v>144</v>
+      </c>
+      <c r="D74" s="31">
+        <v>0.54</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="F74" s="27">
+        <v>200</v>
+      </c>
+      <c r="F74" s="32">
         <v>0</v>
       </c>
-      <c r="G74" s="10"/>
+      <c r="G74" s="30"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D75" s="31">
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="E75" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="F75" s="32">
+        <v>0</v>
+      </c>
+      <c r="G75" s="30"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="5"/>
+      <c r="B76" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D76" s="31">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="F76" s="32">
+        <v>0</v>
+      </c>
+      <c r="G76" s="30"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="5"/>
+      <c r="B77" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D75" s="28">
+      <c r="D77" s="31">
         <v>0.64</v>
       </c>
-      <c r="E75" s="19" t="s">
+      <c r="E77" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="F75" s="27">
+      <c r="F77" s="32">
         <v>0</v>
       </c>
-      <c r="G75" s="10"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C76" s="17" t="s">
-        <v>358</v>
-      </c>
-      <c r="D76" s="28">
-        <v>1.33</v>
-      </c>
-      <c r="E76" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="F76" s="27">
-        <v>146</v>
-      </c>
-      <c r="G76" s="10"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="B77" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D77" s="28">
-        <v>1.49</v>
-      </c>
-      <c r="E77" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="F77" s="27">
-        <v>109</v>
-      </c>
-      <c r="G77" s="10"/>
+      <c r="G77" s="30"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>362</v>
-      </c>
-      <c r="D78" s="28">
-        <v>1.6300000000000001</v>
+        <v>354</v>
+      </c>
+      <c r="D78" s="31">
+        <v>1.33</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="F78" s="27">
-        <v>272</v>
-      </c>
-      <c r="G78" s="10"/>
+        <v>204</v>
+      </c>
+      <c r="F78" s="32">
+        <v>16</v>
+      </c>
+      <c r="G78" s="30"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D79" s="28">
-        <v>1.82</v>
+        <v>355</v>
+      </c>
+      <c r="D79" s="31">
+        <v>1.49</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="F79" s="27">
-        <v>50</v>
-      </c>
-      <c r="G79" s="10"/>
+        <v>205</v>
+      </c>
+      <c r="F79" s="32">
+        <v>62</v>
+      </c>
+      <c r="G79" s="30"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>366</v>
-      </c>
-      <c r="D80" s="28">
-        <v>1.96</v>
+        <v>358</v>
+      </c>
+      <c r="D80" s="31">
+        <v>1.6300000000000001</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="F80" s="27">
-        <v>24</v>
-      </c>
-      <c r="G80" s="10"/>
+        <v>206</v>
+      </c>
+      <c r="F80" s="32">
+        <v>239</v>
+      </c>
+      <c r="G80" s="30"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D81" s="28">
-        <v>2.13</v>
+        <v>360</v>
+      </c>
+      <c r="D81" s="31">
+        <v>1.82</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="F81" s="27">
-        <v>156</v>
-      </c>
-      <c r="G81" s="10"/>
+        <v>207</v>
+      </c>
+      <c r="F81" s="32">
+        <v>0</v>
+      </c>
+      <c r="G81" s="30"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>374</v>
-      </c>
-      <c r="D82" s="28">
-        <v>2.29</v>
+        <v>362</v>
+      </c>
+      <c r="D82" s="31">
+        <v>1.96</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="F82" s="27">
-        <v>97</v>
-      </c>
-      <c r="G82" s="10"/>
+        <v>208</v>
+      </c>
+      <c r="F82" s="32">
+        <v>13</v>
+      </c>
+      <c r="G82" s="30"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D83" s="28">
-        <v>2.4700000000000002</v>
+        <v>368</v>
+      </c>
+      <c r="D83" s="31">
+        <v>2.13</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="F83" s="27">
-        <v>2</v>
-      </c>
-      <c r="G83" s="10"/>
+        <v>209</v>
+      </c>
+      <c r="F83" s="32">
+        <v>125</v>
+      </c>
+      <c r="G83" s="30"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="D84" s="28">
-        <v>2.61</v>
+        <v>370</v>
+      </c>
+      <c r="D84" s="31">
+        <v>2.29</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F84" s="27">
-        <v>0</v>
-      </c>
-      <c r="G84" s="10"/>
+        <v>210</v>
+      </c>
+      <c r="F84" s="32">
+        <v>65</v>
+      </c>
+      <c r="G84" s="30"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="C85" s="17" t="s">
-        <v>462</v>
-      </c>
-      <c r="D85" s="28">
-        <v>1.59</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>461</v>
-      </c>
-      <c r="F85" s="27">
-        <v>166</v>
-      </c>
-      <c r="G85" s="10"/>
+        <v>155</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D85" s="31">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="E85" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="F85" s="32">
+        <v>2</v>
+      </c>
+      <c r="G85" s="30"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D86" s="28">
-        <v>1.98</v>
+        <v>156</v>
+      </c>
+      <c r="C86" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="D86" s="31">
+        <v>2.61</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="F86" s="27">
-        <v>-3</v>
-      </c>
-      <c r="G86" s="10"/>
+        <v>212</v>
+      </c>
+      <c r="F86" s="32">
+        <v>0</v>
+      </c>
+      <c r="G86" s="30"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D87" s="28">
-        <v>2.38</v>
-      </c>
-      <c r="E87" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="F87" s="27">
-        <v>0</v>
-      </c>
-      <c r="G87" s="10"/>
+        <v>459</v>
+      </c>
+      <c r="C87" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="D87" s="31">
+        <v>1.59</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="F87" s="32">
+        <v>82</v>
+      </c>
+      <c r="G87" s="30"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>303</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D88" s="28">
-        <v>2.7600000000000002</v>
+        <v>363</v>
+      </c>
+      <c r="D88" s="31">
+        <v>1.98</v>
       </c>
       <c r="E88" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="F88" s="27">
-        <v>-40</v>
-      </c>
-      <c r="G88" s="10"/>
+        <v>213</v>
+      </c>
+      <c r="F88" s="32">
+        <v>-3</v>
+      </c>
+      <c r="G88" s="30"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="5"/>
-      <c r="B89" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="D89" s="28">
-        <v>1.31</v>
+      <c r="A89" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D89" s="31">
+        <v>2.38</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="F89" s="27">
+        <v>214</v>
+      </c>
+      <c r="F89" s="32">
         <v>0</v>
       </c>
-      <c r="G89" s="10"/>
+      <c r="G89" s="30"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D90" s="28">
-        <v>3.12</v>
+        <v>365</v>
+      </c>
+      <c r="D90" s="31">
+        <v>2.7600000000000002</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="F90" s="27">
-        <v>68</v>
-      </c>
-      <c r="G90" s="10"/>
+        <v>215</v>
+      </c>
+      <c r="F90" s="32">
+        <v>-40</v>
+      </c>
+      <c r="G90" s="30"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="B91" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D91" s="28">
-        <v>3.5100000000000002</v>
+      <c r="A91" s="5"/>
+      <c r="B91" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D91" s="31">
+        <v>1.31</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="F91" s="27">
-        <v>43</v>
-      </c>
-      <c r="G91" s="10"/>
+        <v>216</v>
+      </c>
+      <c r="F91" s="32">
+        <v>0</v>
+      </c>
+      <c r="G91" s="30"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D92" s="28">
-        <v>3.91</v>
+        <v>356</v>
+      </c>
+      <c r="D92" s="31">
+        <v>3.12</v>
       </c>
       <c r="E92" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="F92" s="27">
-        <v>101</v>
-      </c>
-      <c r="G92" s="10"/>
+        <v>217</v>
+      </c>
+      <c r="F92" s="32">
+        <v>-5</v>
+      </c>
+      <c r="G92" s="30"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D93" s="28">
-        <v>4.3100000000000005</v>
+        <v>357</v>
+      </c>
+      <c r="D93" s="31">
+        <v>3.5100000000000002</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="F93" s="27">
-        <v>92</v>
-      </c>
-      <c r="G93" s="10"/>
+        <v>218</v>
+      </c>
+      <c r="F93" s="32">
+        <v>34</v>
+      </c>
+      <c r="G93" s="30"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D94" s="28">
-        <v>4.68</v>
+        <v>359</v>
+      </c>
+      <c r="D94" s="31">
+        <v>3.91</v>
       </c>
       <c r="E94" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="F94" s="27">
-        <v>62</v>
-      </c>
-      <c r="G94" s="10"/>
+        <v>219</v>
+      </c>
+      <c r="F94" s="32">
+        <v>82</v>
+      </c>
+      <c r="G94" s="30"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D95" s="28">
-        <v>5.07</v>
+        <v>361</v>
+      </c>
+      <c r="D95" s="31">
+        <v>4.3100000000000005</v>
       </c>
       <c r="E95" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="F95" s="27">
-        <v>75</v>
-      </c>
-      <c r="G95" s="10"/>
+        <v>220</v>
+      </c>
+      <c r="F95" s="32">
+        <v>64</v>
+      </c>
+      <c r="G95" s="30"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="D96" s="28">
-        <v>5.47</v>
+        <v>366</v>
+      </c>
+      <c r="D96" s="31">
+        <v>4.68</v>
       </c>
       <c r="E96" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="F96" s="27">
-        <v>124</v>
-      </c>
-      <c r="G96" s="10"/>
+        <v>221</v>
+      </c>
+      <c r="F96" s="32">
+        <v>61</v>
+      </c>
+      <c r="G96" s="30"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="D97" s="28">
-        <v>5.87</v>
+        <v>367</v>
+      </c>
+      <c r="D97" s="31">
+        <v>5.07</v>
       </c>
       <c r="E97" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="F97" s="27">
-        <v>28</v>
-      </c>
-      <c r="G97" s="10"/>
+        <v>222</v>
+      </c>
+      <c r="F97" s="32">
+        <v>66</v>
+      </c>
+      <c r="G97" s="30"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="5"/>
-      <c r="B98" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="D98" s="28">
-        <v>1.69</v>
+      <c r="A98" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D98" s="31">
+        <v>5.47</v>
       </c>
       <c r="E98" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="F98" s="27">
-        <v>91</v>
-      </c>
-      <c r="G98" s="10"/>
+        <v>223</v>
+      </c>
+      <c r="F98" s="32">
+        <v>113</v>
+      </c>
+      <c r="G98" s="30"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D99" s="28">
-        <v>3.98</v>
+        <v>378</v>
+      </c>
+      <c r="D99" s="31">
+        <v>5.87</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="F99" s="27">
-        <v>62</v>
-      </c>
-      <c r="G99" s="10"/>
+        <v>224</v>
+      </c>
+      <c r="F99" s="32">
+        <v>28</v>
+      </c>
+      <c r="G99" s="30"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="B100" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="D100" s="28">
-        <v>5.12</v>
+      <c r="A100" s="5"/>
+      <c r="B100" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D100" s="31">
+        <v>1.69</v>
       </c>
       <c r="E100" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="F100" s="27">
-        <v>60</v>
-      </c>
-      <c r="G100" s="10"/>
+        <v>225</v>
+      </c>
+      <c r="F100" s="32">
+        <v>91</v>
+      </c>
+      <c r="G100" s="30"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="D101" s="28">
-        <v>5.94</v>
+        <v>372</v>
+      </c>
+      <c r="D101" s="31">
+        <v>3.98</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="F101" s="27">
-        <v>52</v>
-      </c>
-      <c r="G101" s="10"/>
+        <v>226</v>
+      </c>
+      <c r="F101" s="32">
+        <v>55</v>
+      </c>
+      <c r="G101" s="30"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="D102" s="28">
-        <v>6.92</v>
+        <v>374</v>
+      </c>
+      <c r="D102" s="31">
+        <v>5.12</v>
       </c>
       <c r="E102" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="F102" s="27">
-        <v>58</v>
-      </c>
-      <c r="G102" s="10"/>
+        <v>227</v>
+      </c>
+      <c r="F102" s="32">
+        <v>45</v>
+      </c>
+      <c r="G102" s="30"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" s="5"/>
-      <c r="B103" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="D103" s="28">
-        <v>2.13</v>
+      <c r="A103" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D103" s="31">
+        <v>5.94</v>
       </c>
       <c r="E103" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="F103" s="27">
-        <v>0</v>
-      </c>
-      <c r="G103" s="10"/>
+        <v>228</v>
+      </c>
+      <c r="F103" s="32">
+        <v>52</v>
+      </c>
+      <c r="G103" s="30"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="D104" s="28">
-        <v>5.1100000000000003</v>
+        <v>376</v>
+      </c>
+      <c r="D104" s="31">
+        <v>6.92</v>
       </c>
       <c r="E104" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="F104" s="27">
-        <v>39</v>
-      </c>
-      <c r="G104" s="10"/>
+        <v>229</v>
+      </c>
+      <c r="F104" s="32">
+        <v>41</v>
+      </c>
+      <c r="G104" s="30"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B105" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="D105" s="28">
-        <v>5.76</v>
+      <c r="A105" s="5"/>
+      <c r="B105" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D105" s="31">
+        <v>2.13</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="F105" s="27">
-        <v>108</v>
-      </c>
-      <c r="G105" s="10"/>
+        <v>230</v>
+      </c>
+      <c r="F105" s="32">
+        <v>0</v>
+      </c>
+      <c r="G105" s="30"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>302</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="D106" s="28">
-        <v>6.3900000000000006</v>
+        <v>373</v>
+      </c>
+      <c r="D106" s="31">
+        <v>5.1100000000000003</v>
       </c>
       <c r="E106" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="F106" s="27">
-        <v>17</v>
-      </c>
-      <c r="G106" s="10"/>
+        <v>231</v>
+      </c>
+      <c r="F106" s="32">
+        <v>-7</v>
+      </c>
+      <c r="G106" s="30"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>302</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="D107" s="28">
-        <v>7.03</v>
+        <v>379</v>
+      </c>
+      <c r="D107" s="31">
+        <v>5.76</v>
       </c>
       <c r="E107" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="F107" s="27">
-        <v>47</v>
-      </c>
-      <c r="G107" s="10"/>
+        <v>232</v>
+      </c>
+      <c r="F107" s="32">
+        <v>100</v>
+      </c>
+      <c r="G107" s="30"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>302</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D108" s="28">
-        <v>7.68</v>
+        <v>389</v>
+      </c>
+      <c r="D108" s="31">
+        <v>6.3900000000000006</v>
       </c>
       <c r="E108" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="F108" s="27">
-        <v>100</v>
-      </c>
-      <c r="G108" s="10"/>
+        <v>233</v>
+      </c>
+      <c r="F108" s="32">
+        <v>13</v>
+      </c>
+      <c r="G108" s="30"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>302</v>
       </c>
       <c r="B109" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="D109" s="28">
-        <v>8.31</v>
+        <v>390</v>
+      </c>
+      <c r="D109" s="31">
+        <v>7.03</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="F109" s="27">
-        <v>169</v>
-      </c>
-      <c r="G109" s="10"/>
+        <v>234</v>
+      </c>
+      <c r="F109" s="32">
+        <v>31</v>
+      </c>
+      <c r="G109" s="30"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>302</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D110" s="28">
-        <v>8.9500000000000011</v>
+        <v>391</v>
+      </c>
+      <c r="D110" s="31">
+        <v>7.68</v>
       </c>
       <c r="E110" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="F110" s="27">
-        <v>23</v>
-      </c>
-      <c r="G110" s="10"/>
+        <v>235</v>
+      </c>
+      <c r="F110" s="32">
+        <v>95</v>
+      </c>
+      <c r="G110" s="30"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>302</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D111" s="28">
-        <v>9.61</v>
+        <v>392</v>
+      </c>
+      <c r="D111" s="31">
+        <v>8.31</v>
       </c>
       <c r="E111" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="F111" s="27">
-        <v>8</v>
-      </c>
-      <c r="G111" s="10"/>
+        <v>236</v>
+      </c>
+      <c r="F111" s="32">
+        <v>148</v>
+      </c>
+      <c r="G111" s="30"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="5"/>
-      <c r="B112" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="D112" s="28">
-        <v>4.2700000000000005</v>
+      <c r="A112" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B112" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D112" s="31">
+        <v>8.9500000000000011</v>
       </c>
       <c r="E112" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="F112" s="27">
-        <v>0</v>
-      </c>
-      <c r="G112" s="10"/>
+        <v>237</v>
+      </c>
+      <c r="F112" s="32">
+        <v>4</v>
+      </c>
+      <c r="G112" s="30"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="D113" s="28">
-        <v>10.220000000000001</v>
+        <v>394</v>
+      </c>
+      <c r="D113" s="31">
+        <v>9.61</v>
       </c>
       <c r="E113" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="F113" s="27">
-        <v>23</v>
-      </c>
-      <c r="G113" s="10"/>
+        <v>238</v>
+      </c>
+      <c r="F113" s="32">
+        <v>8</v>
+      </c>
+      <c r="G113" s="30"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="B114" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D114" s="28">
-        <v>11.5</v>
+      <c r="A114" s="5"/>
+      <c r="B114" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="D114" s="31">
+        <v>4.2700000000000005</v>
       </c>
       <c r="E114" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="F114" s="27">
-        <v>14</v>
-      </c>
-      <c r="G114" s="10"/>
+        <v>239</v>
+      </c>
+      <c r="F114" s="32">
+        <v>0</v>
+      </c>
+      <c r="G114" s="30"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="D115" s="28">
-        <v>12.780000000000001</v>
+        <v>380</v>
+      </c>
+      <c r="D115" s="31">
+        <v>10.220000000000001</v>
       </c>
       <c r="E115" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="F115" s="27">
-        <v>8</v>
-      </c>
-      <c r="G115" s="10"/>
+        <v>240</v>
+      </c>
+      <c r="F115" s="32">
+        <v>20</v>
+      </c>
+      <c r="G115" s="30"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="D116" s="28">
-        <v>14.07</v>
+        <v>381</v>
+      </c>
+      <c r="D116" s="31">
+        <v>11.5</v>
       </c>
       <c r="E116" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="F116" s="27">
-        <v>12</v>
-      </c>
-      <c r="G116" s="10"/>
+        <v>241</v>
+      </c>
+      <c r="F116" s="32">
+        <v>14</v>
+      </c>
+      <c r="G116" s="30"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="D117" s="28">
-        <v>15.34</v>
+        <v>382</v>
+      </c>
+      <c r="D117" s="31">
+        <v>12.780000000000001</v>
       </c>
       <c r="E117" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="F117" s="27">
-        <v>15</v>
-      </c>
-      <c r="G117" s="10"/>
+        <v>242</v>
+      </c>
+      <c r="F117" s="32">
+        <v>8</v>
+      </c>
+      <c r="G117" s="30"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D118" s="28">
-        <v>16.61</v>
+        <v>383</v>
+      </c>
+      <c r="D118" s="31">
+        <v>14.07</v>
       </c>
       <c r="E118" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="F118" s="27">
-        <v>32</v>
-      </c>
-      <c r="G118" s="10"/>
+        <v>243</v>
+      </c>
+      <c r="F118" s="32">
+        <v>12</v>
+      </c>
+      <c r="G118" s="30"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D119" s="28">
-        <v>17.88</v>
+        <v>384</v>
+      </c>
+      <c r="D119" s="31">
+        <v>15.34</v>
       </c>
       <c r="E119" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="F119" s="27">
-        <v>23</v>
-      </c>
-      <c r="G119" s="10"/>
+        <v>244</v>
+      </c>
+      <c r="F119" s="32">
+        <v>15</v>
+      </c>
+      <c r="G119" s="30"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D120" s="28">
-        <v>19.12</v>
+        <v>385</v>
+      </c>
+      <c r="D120" s="31">
+        <v>16.61</v>
       </c>
       <c r="E120" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="F120" s="27">
-        <v>11</v>
-      </c>
-      <c r="G120" s="10"/>
+        <v>245</v>
+      </c>
+      <c r="F120" s="32">
+        <v>32</v>
+      </c>
+      <c r="G120" s="30"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="5"/>
-      <c r="B121" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="D121" s="28">
-        <v>8.02</v>
+      <c r="A121" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B121" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D121" s="31">
+        <v>17.88</v>
       </c>
       <c r="E121" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="F121" s="27">
-        <v>0</v>
-      </c>
-      <c r="G121" s="10"/>
+        <v>246</v>
+      </c>
+      <c r="F121" s="32">
+        <v>21</v>
+      </c>
+      <c r="G121" s="30"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D122" s="28">
-        <v>18.100000000000001</v>
+        <v>387</v>
+      </c>
+      <c r="D122" s="31">
+        <v>19.12</v>
       </c>
       <c r="E122" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="F122" s="27">
-        <v>18</v>
-      </c>
-      <c r="G122" s="10"/>
+        <v>247</v>
+      </c>
+      <c r="F122" s="32">
+        <v>11</v>
+      </c>
+      <c r="G122" s="30"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="B123" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D123" s="28">
-        <v>22.64</v>
+      <c r="A123" s="5"/>
+      <c r="B123" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D123" s="31">
+        <v>8.02</v>
       </c>
       <c r="E123" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="F123" s="27">
-        <v>26</v>
-      </c>
-      <c r="G123" s="10"/>
+        <v>248</v>
+      </c>
+      <c r="F123" s="32">
+        <v>0</v>
+      </c>
+      <c r="G123" s="30"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D124" s="28">
-        <v>27.150000000000002</v>
+        <v>388</v>
+      </c>
+      <c r="D124" s="31">
+        <v>18.100000000000001</v>
       </c>
       <c r="E124" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="F124" s="27">
-        <v>23</v>
-      </c>
-      <c r="G124" s="10"/>
+        <v>249</v>
+      </c>
+      <c r="F124" s="32">
+        <v>13</v>
+      </c>
+      <c r="G124" s="30"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D125" s="28">
-        <v>31.69</v>
+        <v>395</v>
+      </c>
+      <c r="D125" s="31">
+        <v>22.64</v>
       </c>
       <c r="E125" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="F125" s="27">
-        <v>15</v>
-      </c>
-      <c r="G125" s="10"/>
+        <v>250</v>
+      </c>
+      <c r="F125" s="32">
+        <v>16</v>
+      </c>
+      <c r="G125" s="30"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="D126" s="28">
-        <v>33.94</v>
+        <v>396</v>
+      </c>
+      <c r="D126" s="31">
+        <v>27.150000000000002</v>
       </c>
       <c r="E126" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="F126" s="27">
-        <v>0</v>
-      </c>
-      <c r="G126" s="10"/>
+        <v>251</v>
+      </c>
+      <c r="F126" s="32">
+        <v>21</v>
+      </c>
+      <c r="G126" s="30"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B127" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D127" s="31">
+        <v>31.69</v>
+      </c>
+      <c r="E127" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="F127" s="32">
+        <v>15</v>
+      </c>
+      <c r="G127" s="30"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B128" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D128" s="31">
+        <v>33.94</v>
+      </c>
+      <c r="E128" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="F128" s="32">
+        <v>0</v>
+      </c>
+      <c r="G128" s="30"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B129" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="C127" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D127" s="28">
+      <c r="C129" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D129" s="31">
         <v>36.22</v>
       </c>
-      <c r="E127" s="19" t="s">
+      <c r="E129" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="F127" s="27">
+      <c r="F129" s="32">
         <v>0</v>
       </c>
-      <c r="G127" s="10"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="5"/>
-      <c r="B128" s="15" t="s">
+      <c r="G129" s="33"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="5"/>
+      <c r="B130" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="D128" s="11">
+      <c r="D130" s="34">
+        <v>2.15</v>
+      </c>
+      <c r="E130" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="F130" s="35">
         <v>0</v>
       </c>
-      <c r="E128" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="F128" s="12">
-        <v>0</v>
-      </c>
-      <c r="G128" s="10"/>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B129" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="D129" s="29">
-        <v>5.12</v>
-      </c>
-      <c r="E129" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="F129" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B130" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D130" s="29">
-        <v>3.93</v>
-      </c>
-      <c r="E130" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="F130" s="30">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G130" s="33"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="D131" s="29">
-        <v>4.53</v>
+        <v>400</v>
+      </c>
+      <c r="D131" s="34">
+        <v>5.12</v>
       </c>
       <c r="E131" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="F131" s="30">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+        <v>256</v>
+      </c>
+      <c r="F131" s="35">
+        <v>0</v>
+      </c>
+      <c r="G131" s="33"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D132" s="29">
-        <v>6.7</v>
+        <v>401</v>
+      </c>
+      <c r="D132" s="34">
+        <v>3.93</v>
       </c>
       <c r="E132" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="F132" s="30">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+        <v>257</v>
+      </c>
+      <c r="F132" s="35">
+        <v>369</v>
+      </c>
+      <c r="G132" s="33"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D133" s="29">
-        <v>8.31</v>
+        <v>402</v>
+      </c>
+      <c r="D133" s="34">
+        <v>4.53</v>
       </c>
       <c r="E133" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="F133" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+        <v>258</v>
+      </c>
+      <c r="F133" s="35">
+        <v>624</v>
+      </c>
+      <c r="G133" s="33"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D134" s="29">
-        <v>7.8900000000000006</v>
+        <v>403</v>
+      </c>
+      <c r="D134" s="34">
+        <v>6.7</v>
       </c>
       <c r="E134" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="F134" s="30">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+      <c r="F134" s="35">
+        <v>193</v>
+      </c>
+      <c r="G134" s="33"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="D135" s="29">
-        <v>9.61</v>
+        <v>404</v>
+      </c>
+      <c r="D135" s="34">
+        <v>8.31</v>
       </c>
       <c r="E135" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="F135" s="30">
+        <v>260</v>
+      </c>
+      <c r="F135" s="35">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="5"/>
-      <c r="B136" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="D136" s="29">
-        <v>3.5500000000000003</v>
+      <c r="G135" s="33"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B136" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D136" s="34">
+        <v>7.8900000000000006</v>
       </c>
       <c r="E136" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="F136" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+      <c r="F136" s="35">
+        <v>369</v>
+      </c>
+      <c r="G136" s="33"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="D137" s="29">
-        <v>6.22</v>
+        <v>406</v>
+      </c>
+      <c r="D137" s="34">
+        <v>9.61</v>
       </c>
       <c r="E137" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="F137" s="30">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B138" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="D138" s="29">
-        <v>6.7</v>
+        <v>262</v>
+      </c>
+      <c r="F137" s="35">
+        <v>0</v>
+      </c>
+      <c r="G137" s="33"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="5"/>
+      <c r="B138" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="D138" s="34">
+        <v>3.5500000000000003</v>
       </c>
       <c r="E138" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="F138" s="30">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+      <c r="F138" s="35">
+        <v>0</v>
+      </c>
+      <c r="G138" s="33"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="D139" s="29">
-        <v>10.91</v>
+        <v>407</v>
+      </c>
+      <c r="D139" s="34">
+        <v>6.22</v>
       </c>
       <c r="E139" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="F139" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+        <v>264</v>
+      </c>
+      <c r="F139" s="35">
+        <v>239</v>
+      </c>
+      <c r="G139" s="33"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D140" s="29">
-        <v>10.370000000000001</v>
+        <v>414</v>
+      </c>
+      <c r="D140" s="34">
+        <v>6.7</v>
       </c>
       <c r="E140" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="F140" s="30">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+      <c r="F140" s="35">
+        <v>375</v>
+      </c>
+      <c r="G140" s="33"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D141" s="29">
-        <v>6.76</v>
+        <v>415</v>
+      </c>
+      <c r="D141" s="34">
+        <v>10.91</v>
       </c>
       <c r="E141" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="F141" s="30">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+      <c r="F141" s="35">
+        <v>0</v>
+      </c>
+      <c r="G141" s="33"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D142" s="29">
-        <v>9.23</v>
+        <v>416</v>
+      </c>
+      <c r="D142" s="34">
+        <v>10.370000000000001</v>
       </c>
       <c r="E142" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="F142" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+      <c r="F142" s="35">
+        <v>201</v>
+      </c>
+      <c r="G142" s="33"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="D143" s="29">
-        <v>11.14</v>
+        <v>417</v>
+      </c>
+      <c r="D143" s="34">
+        <v>6.76</v>
       </c>
       <c r="E143" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="F143" s="30">
+        <v>268</v>
+      </c>
+      <c r="F143" s="35">
+        <v>132</v>
+      </c>
+      <c r="G143" s="33"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B144" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D144" s="34">
+        <v>9.23</v>
+      </c>
+      <c r="E144" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="F144" s="35">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="5"/>
-      <c r="B144" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="D144" s="29">
-        <v>3.17</v>
-      </c>
-      <c r="E144" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="F144" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G144" s="33"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="D145" s="29">
-        <v>7.2</v>
+        <v>419</v>
+      </c>
+      <c r="D145" s="34">
+        <v>11.14</v>
       </c>
       <c r="E145" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="F145" s="30">
+        <v>270</v>
+      </c>
+      <c r="F145" s="35">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B146" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="D146" s="29">
-        <v>18.11</v>
+      <c r="G145" s="33"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146" s="5"/>
+      <c r="B146" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D146" s="34">
+        <v>3.17</v>
       </c>
       <c r="E146" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="F146" s="30">
+        <v>271</v>
+      </c>
+      <c r="F146" s="35">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G146" s="33"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="D147" s="29">
-        <v>11.94</v>
+        <v>408</v>
+      </c>
+      <c r="D147" s="34">
+        <v>7.2</v>
       </c>
       <c r="E147" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="F147" s="30">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+      <c r="F147" s="35">
+        <v>0</v>
+      </c>
+      <c r="G147" s="33"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D148" s="29">
-        <v>15.16</v>
+        <v>409</v>
+      </c>
+      <c r="D148" s="34">
+        <v>18.11</v>
       </c>
       <c r="E148" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="F148" s="30">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+        <v>273</v>
+      </c>
+      <c r="F148" s="35">
+        <v>0</v>
+      </c>
+      <c r="G148" s="33"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="D149" s="29">
-        <v>13.52</v>
+        <v>410</v>
+      </c>
+      <c r="D149" s="34">
+        <v>11.94</v>
       </c>
       <c r="E149" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="F149" s="30">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+      <c r="F149" s="35">
+        <v>81</v>
+      </c>
+      <c r="G149" s="33"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B150" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D150" s="34">
+        <v>15.16</v>
+      </c>
+      <c r="E150" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="F150" s="35">
+        <v>45</v>
+      </c>
+      <c r="G150" s="33"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D151" s="34">
+        <v>13.52</v>
+      </c>
+      <c r="E151" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="F151" s="35">
+        <v>43</v>
+      </c>
+      <c r="G151" s="33"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B152" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C150" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D150" s="29">
+      <c r="C152" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D152" s="34">
         <v>24.89</v>
       </c>
-      <c r="E150" s="19" t="s">
+      <c r="E152" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="F150" s="30">
+      <c r="F152" s="35">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="5" t="s">
+      <c r="G152" s="33"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="B153" s="23" t="s">
+        <v>420</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="D153" s="12">
+        <v>7.8</v>
+      </c>
+      <c r="E153" s="19" t="s">
+        <v>460</v>
+      </c>
+      <c r="F153" s="22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="B154" s="24" t="s">
+        <v>421</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D154" s="11">
+        <v>18.150000000000002</v>
+      </c>
+      <c r="E154" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="F154" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="B155" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="D155" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="E155" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="F155" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="B156" s="24" t="s">
+        <v>426</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="D156" s="11">
+        <v>18.22</v>
+      </c>
+      <c r="E156" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="F156" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="B151" s="23" t="s">
-        <v>424</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="D151" s="12">
-        <v>7.8</v>
-      </c>
-      <c r="E151" s="19" t="s">
-        <v>464</v>
-      </c>
-      <c r="F151" s="22">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" s="5" t="s">
+      <c r="B157" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D157" s="11">
+        <v>9.82</v>
+      </c>
+      <c r="E157" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="F157" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="B158" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D158" s="11">
+        <v>9.82</v>
+      </c>
+      <c r="E158" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="F158" s="12">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="B152" s="24" t="s">
-        <v>425</v>
-      </c>
-      <c r="C152" s="2" t="s">
+      <c r="B159" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="C159" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="D152" s="11">
-        <v>18.150000000000002</v>
-      </c>
-      <c r="E152" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="F152" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="B153" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="D153" s="11">
-        <v>23.8</v>
-      </c>
-      <c r="E153" s="19" t="s">
-        <v>427</v>
-      </c>
-      <c r="F153" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="B154" s="24" t="s">
+      <c r="D159" s="11">
+        <v>9.82</v>
+      </c>
+      <c r="E159" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="F159" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B160" s="9" t="s">
         <v>430</v>
       </c>
-      <c r="C154" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="D154" s="11">
-        <v>18.22</v>
-      </c>
-      <c r="E154" s="19" t="s">
-        <v>429</v>
-      </c>
-      <c r="F154" s="12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="B155" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="D155" s="31">
+      <c r="C160" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D160" s="11">
         <v>9.82</v>
       </c>
-      <c r="E155" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="F155" s="32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="B156" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="D156" s="31">
-        <v>9.82</v>
-      </c>
-      <c r="E156" s="10" t="s">
-        <v>439</v>
-      </c>
-      <c r="F156" s="32">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="B157" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="D157" s="31">
-        <v>9.82</v>
-      </c>
-      <c r="E157" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="F157" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="B158" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="D158" s="31">
-        <v>9.82</v>
-      </c>
-      <c r="E158" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="F158" s="32">
+      <c r="E160" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="F160" s="12">
         <v>2</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="B159" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="D159" s="31">
-        <v>9.82</v>
-      </c>
-      <c r="E159" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="F159" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A160" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="B160" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="D160" s="31">
-        <v>9.82</v>
-      </c>
-      <c r="E160" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="F160" s="32">
-        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B161" s="9" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="D161" s="31">
+        <v>456</v>
+      </c>
+      <c r="D161" s="11">
+        <v>9.82</v>
+      </c>
+      <c r="E161" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="F161" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B162" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D162" s="11">
+        <v>9.82</v>
+      </c>
+      <c r="E162" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="F162" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="B163" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="D163" s="11">
         <v>6.3</v>
       </c>
-      <c r="E161" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="F161" s="32">
+      <c r="E163" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="F163" s="12">
         <v>3</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A162" s="5"/>
-      <c r="B162" s="5"/>
-      <c r="C162" s="5"/>
-      <c r="D162" s="5"/>
-      <c r="E162" s="19"/>
-      <c r="F162" s="5"/>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A163" s="5"/>
-      <c r="B163" s="5"/>
-      <c r="C163" s="5"/>
-      <c r="D163" s="5"/>
-      <c r="E163" s="19"/>
-      <c r="F163" s="5"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="5"/>
@@ -7354,14 +7492,30 @@
       <c r="E448" s="19"/>
       <c r="F448" s="5"/>
     </row>
-    <row r="449" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A449" s="2"/>
-    </row>
-    <row r="450" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A450" s="2"/>
-    </row>
-    <row r="451" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A449" s="5"/>
+      <c r="B449" s="5"/>
+      <c r="C449" s="5"/>
+      <c r="D449" s="5"/>
+      <c r="E449" s="19"/>
+      <c r="F449" s="5"/>
+    </row>
+    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A450" s="5"/>
+      <c r="B450" s="5"/>
+      <c r="C450" s="5"/>
+      <c r="D450" s="5"/>
+      <c r="E450" s="19"/>
+      <c r="F450" s="5"/>
+    </row>
+    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A451" s="2"/>
+    </row>
+    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A452" s="2"/>
+    </row>
+    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A453" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\bois\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FA628D-EB14-477E-BD77-AE4079CEFEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84DA782-E6E9-455D-BD8B-3B9CC28C588B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="471">
   <si>
     <t>path</t>
   </si>
@@ -1532,7 +1532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1602,37 +1602,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -2000,7 +1969,7 @@
       <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="26"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -2021,7 +1990,7 @@
       <c r="F2" s="12">
         <v>104.88500000000023</v>
       </c>
-      <c r="G2" s="26"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -2042,7 +2011,7 @@
       <c r="F3" s="12">
         <v>0</v>
       </c>
-      <c r="G3" s="26"/>
+      <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -2063,7 +2032,7 @@
       <c r="F4" s="12">
         <v>132.01899999999907</v>
       </c>
-      <c r="G4" s="26"/>
+      <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
@@ -2084,45 +2053,49 @@
       <c r="F5" s="12">
         <v>256.31999999999971</v>
       </c>
-      <c r="G5" s="26"/>
-    </row>
-    <row r="6" spans="1:7" s="25" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>307</v>
+      </c>
       <c r="B6" s="9" t="s">
         <v>463</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="11">
         <v>8.01</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="12">
         <v>374.22</v>
       </c>
-      <c r="G6" s="26"/>
-    </row>
-    <row r="7" spans="1:7" s="25" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>307</v>
+      </c>
       <c r="B7" s="9" t="s">
         <v>464</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="11">
         <v>11.33</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="12">
         <v>287.92</v>
       </c>
-      <c r="G7" s="26"/>
+      <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -2143,7 +2116,7 @@
       <c r="F8" s="12">
         <v>374.39999999999981</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -2164,7 +2137,7 @@
       <c r="F9" s="12">
         <v>83.518000000000654</v>
       </c>
-      <c r="G9" s="26"/>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
@@ -2180,7 +2153,7 @@
       <c r="F10" s="12">
         <v>30</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
@@ -2196,7 +2169,7 @@
       <c r="F11" s="12">
         <v>90</v>
       </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
@@ -2212,7 +2185,7 @@
       <c r="F12" s="12">
         <v>11.519999999999982</v>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
@@ -2228,7 +2201,7 @@
       <c r="F13" s="12">
         <v>0</v>
       </c>
-      <c r="G13" s="26"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
@@ -2244,7 +2217,7 @@
       <c r="F14" s="12">
         <v>0</v>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="10"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
@@ -2265,7 +2238,7 @@
       <c r="F15" s="12">
         <v>14.900000000000224</v>
       </c>
-      <c r="G15" s="26"/>
+      <c r="G15" s="10"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
@@ -2286,7 +2259,7 @@
       <c r="F16" s="12">
         <v>32.024999999999835</v>
       </c>
-      <c r="G16" s="26"/>
+      <c r="G16" s="10"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
@@ -2307,7 +2280,7 @@
       <c r="F17" s="12">
         <v>4.4750000000002101</v>
       </c>
-      <c r="G17" s="26"/>
+      <c r="G17" s="10"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
@@ -2328,7 +2301,7 @@
       <c r="F18" s="12">
         <v>0</v>
       </c>
-      <c r="G18" s="26"/>
+      <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
@@ -2349,7 +2322,7 @@
       <c r="F19" s="12">
         <v>4.9999999981578114E-3</v>
       </c>
-      <c r="G19" s="26"/>
+      <c r="G19" s="10"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -2370,7 +2343,7 @@
       <c r="F20" s="12">
         <v>0</v>
       </c>
-      <c r="G20" s="26"/>
+      <c r="G20" s="10"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
@@ -2391,7 +2364,7 @@
       <c r="F21" s="12">
         <v>120.08799999999336</v>
       </c>
-      <c r="G21" s="26"/>
+      <c r="G21" s="10"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
@@ -2412,7 +2385,7 @@
       <c r="F22" s="12">
         <v>167.15000000000467</v>
       </c>
-      <c r="G22" s="26"/>
+      <c r="G22" s="10"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -2433,7 +2406,7 @@
       <c r="F23" s="12">
         <v>144.26200000000185</v>
       </c>
-      <c r="G23" s="26"/>
+      <c r="G23" s="10"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
@@ -2454,7 +2427,7 @@
       <c r="F24" s="12">
         <v>-4.9999999999914557E-3</v>
       </c>
-      <c r="G24" s="26"/>
+      <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
@@ -2475,7 +2448,7 @@
       <c r="F25" s="12">
         <v>0</v>
       </c>
-      <c r="G25" s="26"/>
+      <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
@@ -2496,7 +2469,7 @@
       <c r="F26" s="12">
         <v>35.736999999999895</v>
       </c>
-      <c r="G26" s="26"/>
+      <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
@@ -2517,7 +2490,7 @@
       <c r="F27" s="12">
         <v>0</v>
       </c>
-      <c r="G27" s="26"/>
+      <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
@@ -2538,7 +2511,7 @@
       <c r="F28" s="12">
         <v>65.337999999999596</v>
       </c>
-      <c r="G28" s="26"/>
+      <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
@@ -2559,7 +2532,7 @@
       <c r="F29" s="12">
         <v>142.54700000000011</v>
       </c>
-      <c r="G29" s="26"/>
+      <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
@@ -2580,7 +2553,7 @@
       <c r="F30" s="12">
         <v>0</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="10"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
@@ -2601,7 +2574,7 @@
       <c r="F31" s="12">
         <v>176.0489999999939</v>
       </c>
-      <c r="G31" s="26"/>
+      <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
@@ -2622,7 +2595,7 @@
       <c r="F32" s="12">
         <v>0</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
@@ -2643,7 +2616,7 @@
       <c r="F33" s="12">
         <v>0</v>
       </c>
-      <c r="G33" s="26"/>
+      <c r="G33" s="10"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
@@ -2664,7 +2637,7 @@
       <c r="F34" s="12">
         <v>0</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="10"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
@@ -2685,7 +2658,7 @@
       <c r="F35" s="12">
         <v>152.56700000000018</v>
       </c>
-      <c r="G35" s="26"/>
+      <c r="G35" s="10"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
@@ -2706,7 +2679,7 @@
       <c r="F36" s="12">
         <v>152.87599999999372</v>
       </c>
-      <c r="G36" s="26"/>
+      <c r="G36" s="10"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
@@ -2727,7 +2700,7 @@
       <c r="F37" s="12">
         <v>0</v>
       </c>
-      <c r="G37" s="26"/>
+      <c r="G37" s="10"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
@@ -2748,7 +2721,7 @@
       <c r="F38" s="12">
         <v>0</v>
       </c>
-      <c r="G38" s="26"/>
+      <c r="G38" s="10"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
@@ -2769,7 +2742,7 @@
       <c r="F39" s="12">
         <v>0</v>
       </c>
-      <c r="G39" s="26"/>
+      <c r="G39" s="10"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
@@ -2790,7 +2763,7 @@
       <c r="F40" s="12">
         <v>0</v>
       </c>
-      <c r="G40" s="26"/>
+      <c r="G40" s="10"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
@@ -2811,7 +2784,7 @@
       <c r="F41" s="12">
         <v>87.61900000000422</v>
       </c>
-      <c r="G41" s="26"/>
+      <c r="G41" s="10"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
@@ -2827,7 +2800,7 @@
       <c r="F42" s="12">
         <v>0</v>
       </c>
-      <c r="G42" s="26"/>
+      <c r="G42" s="10"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
@@ -2843,7 +2816,7 @@
       <c r="F43" s="12">
         <v>0</v>
       </c>
-      <c r="G43" s="26"/>
+      <c r="G43" s="10"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
@@ -2859,7 +2832,7 @@
       <c r="F44" s="12">
         <v>2.34</v>
       </c>
-      <c r="G44" s="26"/>
+      <c r="G44" s="10"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
@@ -2875,7 +2848,7 @@
       <c r="F45" s="12">
         <v>4.3964831775156199E-14</v>
       </c>
-      <c r="G45" s="26"/>
+      <c r="G45" s="10"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
@@ -2891,7 +2864,7 @@
       <c r="F46" s="12">
         <v>0</v>
       </c>
-      <c r="G46" s="26"/>
+      <c r="G46" s="10"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
@@ -2907,7 +2880,7 @@
       <c r="F47" s="12">
         <v>0</v>
       </c>
-      <c r="G47" s="26"/>
+      <c r="G47" s="10"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
@@ -2923,7 +2896,7 @@
       <c r="F48" s="12">
         <v>0</v>
       </c>
-      <c r="G48" s="26"/>
+      <c r="G48" s="10"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
@@ -2939,7 +2912,7 @@
       <c r="F49" s="12">
         <v>0</v>
       </c>
-      <c r="G49" s="26"/>
+      <c r="G49" s="10"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
@@ -2955,7 +2928,7 @@
       <c r="F50" s="12">
         <v>0</v>
       </c>
-      <c r="G50" s="26"/>
+      <c r="G50" s="10"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
@@ -2971,7 +2944,7 @@
       <c r="F51" s="12">
         <v>0</v>
       </c>
-      <c r="G51" s="26"/>
+      <c r="G51" s="10"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
@@ -2992,7 +2965,7 @@
       <c r="F52" s="12">
         <v>4.6799999999999837</v>
       </c>
-      <c r="G52" s="26"/>
+      <c r="G52" s="10"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
@@ -3013,7 +2986,7 @@
       <c r="F53" s="12">
         <v>10.921000000000276</v>
       </c>
-      <c r="G53" s="26"/>
+      <c r="G53" s="10"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
@@ -3034,7 +3007,7 @@
       <c r="F54" s="12">
         <v>80.649999999997618</v>
       </c>
-      <c r="G54" s="26"/>
+      <c r="G54" s="10"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
@@ -3055,7 +3028,7 @@
       <c r="F55" s="12">
         <v>-3.3010000000018076</v>
       </c>
-      <c r="G55" s="26"/>
+      <c r="G55" s="10"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
@@ -3076,7 +3049,7 @@
       <c r="F56" s="12">
         <v>134.36999999999941</v>
       </c>
-      <c r="G56" s="26"/>
+      <c r="G56" s="10"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
@@ -3097,7 +3070,7 @@
       <c r="F57" s="12">
         <v>95.970000000011566</v>
       </c>
-      <c r="G57" s="26"/>
+      <c r="G57" s="10"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
@@ -3113,7 +3086,7 @@
       <c r="F58" s="12">
         <v>0</v>
       </c>
-      <c r="G58" s="26"/>
+      <c r="G58" s="10"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
@@ -3129,7 +3102,7 @@
       <c r="F59" s="12">
         <v>0</v>
       </c>
-      <c r="G59" s="26"/>
+      <c r="G59" s="10"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
@@ -3150,7 +3123,7 @@
       <c r="F60" s="12">
         <v>62.399999999999942</v>
       </c>
-      <c r="G60" s="26"/>
+      <c r="G60" s="10"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
@@ -3171,7 +3144,7 @@
       <c r="F61" s="12">
         <v>0</v>
       </c>
-      <c r="G61" s="26"/>
+      <c r="G61" s="10"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
@@ -3192,7 +3165,7 @@
       <c r="F62" s="12">
         <v>0</v>
       </c>
-      <c r="G62" s="26"/>
+      <c r="G62" s="10"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
@@ -3213,7 +3186,7 @@
       <c r="F63" s="12">
         <v>-4.9999999997818456E-3</v>
       </c>
-      <c r="G63" s="26"/>
+      <c r="G63" s="10"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
@@ -3234,7 +3207,7 @@
       <c r="F64" s="12">
         <v>0</v>
       </c>
-      <c r="G64" s="26"/>
+      <c r="G64" s="10"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
@@ -3250,7 +3223,7 @@
       <c r="F65" s="12">
         <v>0</v>
       </c>
-      <c r="G65" s="26"/>
+      <c r="G65" s="10"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
@@ -3271,7 +3244,7 @@
       <c r="F66" s="12">
         <v>12.200000000000017</v>
       </c>
-      <c r="G66" s="26"/>
+      <c r="G66" s="10"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
@@ -3292,7 +3265,7 @@
       <c r="F67" s="12">
         <v>0</v>
       </c>
-      <c r="G67" s="26"/>
+      <c r="G67" s="10"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
@@ -3308,7 +3281,7 @@
       <c r="F68" s="12">
         <v>0</v>
       </c>
-      <c r="G68" s="26"/>
+      <c r="G68" s="10"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
@@ -3324,7 +3297,7 @@
       <c r="F69" s="12">
         <v>0</v>
       </c>
-      <c r="G69" s="26"/>
+      <c r="G69" s="10"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
@@ -3340,7 +3313,7 @@
       <c r="F70" s="12">
         <v>0</v>
       </c>
-      <c r="G70" s="26"/>
+      <c r="G70" s="10"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
@@ -3356,7 +3329,7 @@
       <c r="F71" s="12">
         <v>0</v>
       </c>
-      <c r="G71" s="26"/>
+      <c r="G71" s="10"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
@@ -3372,7 +3345,7 @@
       <c r="F72" s="12">
         <v>0</v>
       </c>
-      <c r="G72" s="30"/>
+      <c r="G72" s="10"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
@@ -3382,80 +3355,80 @@
       <c r="C73" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="D73" s="31">
+      <c r="D73" s="11">
         <v>0.69000000000000006</v>
       </c>
       <c r="E73" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="F73" s="32">
+      <c r="F73" s="12">
         <v>550.80000000000132</v>
       </c>
-      <c r="G73" s="30"/>
+      <c r="G73" s="10"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D74" s="31">
+      <c r="D74" s="11">
         <v>0.54</v>
       </c>
       <c r="E74" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="F74" s="32">
+      <c r="F74" s="12">
         <v>0</v>
       </c>
-      <c r="G74" s="30"/>
+      <c r="G74" s="10"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="D75" s="31">
+      <c r="D75" s="11">
         <v>0.35000000000000003</v>
       </c>
       <c r="E75" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="F75" s="32">
+      <c r="F75" s="12">
         <v>0</v>
       </c>
-      <c r="G75" s="30"/>
+      <c r="G75" s="10"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D76" s="31">
+      <c r="D76" s="11">
         <v>0.28000000000000003</v>
       </c>
       <c r="E76" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="F76" s="32">
+      <c r="F76" s="12">
         <v>0</v>
       </c>
-      <c r="G76" s="30"/>
+      <c r="G76" s="10"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D77" s="31">
+      <c r="D77" s="11">
         <v>0.64</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="F77" s="32">
+      <c r="F77" s="12">
         <v>0</v>
       </c>
-      <c r="G77" s="30"/>
+      <c r="G77" s="10"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
@@ -3467,16 +3440,16 @@
       <c r="C78" s="17" t="s">
         <v>354</v>
       </c>
-      <c r="D78" s="31">
+      <c r="D78" s="11">
         <v>1.33</v>
       </c>
       <c r="E78" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="F78" s="32">
+      <c r="F78" s="12">
         <v>16</v>
       </c>
-      <c r="G78" s="30"/>
+      <c r="G78" s="10"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
@@ -3488,16 +3461,16 @@
       <c r="C79" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="D79" s="31">
+      <c r="D79" s="11">
         <v>1.49</v>
       </c>
       <c r="E79" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="F79" s="32">
+      <c r="F79" s="12">
         <v>62</v>
       </c>
-      <c r="G79" s="30"/>
+      <c r="G79" s="10"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
@@ -3509,16 +3482,16 @@
       <c r="C80" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="D80" s="31">
+      <c r="D80" s="11">
         <v>1.6300000000000001</v>
       </c>
       <c r="E80" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="F80" s="32">
+      <c r="F80" s="12">
         <v>239</v>
       </c>
-      <c r="G80" s="30"/>
+      <c r="G80" s="10"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
@@ -3530,16 +3503,16 @@
       <c r="C81" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D81" s="31">
+      <c r="D81" s="11">
         <v>1.82</v>
       </c>
       <c r="E81" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="F81" s="32">
+      <c r="F81" s="12">
         <v>0</v>
       </c>
-      <c r="G81" s="30"/>
+      <c r="G81" s="10"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
@@ -3551,16 +3524,16 @@
       <c r="C82" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="D82" s="31">
+      <c r="D82" s="11">
         <v>1.96</v>
       </c>
       <c r="E82" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="F82" s="32">
+      <c r="F82" s="12">
         <v>13</v>
       </c>
-      <c r="G82" s="30"/>
+      <c r="G82" s="10"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
@@ -3572,16 +3545,16 @@
       <c r="C83" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="D83" s="31">
+      <c r="D83" s="11">
         <v>2.13</v>
       </c>
       <c r="E83" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="F83" s="32">
+      <c r="F83" s="12">
         <v>125</v>
       </c>
-      <c r="G83" s="30"/>
+      <c r="G83" s="10"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
@@ -3593,16 +3566,16 @@
       <c r="C84" s="17" t="s">
         <v>370</v>
       </c>
-      <c r="D84" s="31">
+      <c r="D84" s="11">
         <v>2.29</v>
       </c>
       <c r="E84" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="F84" s="32">
+      <c r="F84" s="12">
         <v>65</v>
       </c>
-      <c r="G84" s="30"/>
+      <c r="G84" s="10"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
@@ -3614,16 +3587,16 @@
       <c r="C85" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D85" s="31">
+      <c r="D85" s="11">
         <v>2.4700000000000002</v>
       </c>
       <c r="E85" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="F85" s="32">
+      <c r="F85" s="12">
         <v>2</v>
       </c>
-      <c r="G85" s="30"/>
+      <c r="G85" s="10"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
@@ -3635,16 +3608,16 @@
       <c r="C86" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="D86" s="31">
+      <c r="D86" s="11">
         <v>2.61</v>
       </c>
       <c r="E86" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="F86" s="32">
+      <c r="F86" s="12">
         <v>0</v>
       </c>
-      <c r="G86" s="30"/>
+      <c r="G86" s="10"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
@@ -3656,16 +3629,16 @@
       <c r="C87" s="17" t="s">
         <v>458</v>
       </c>
-      <c r="D87" s="31">
+      <c r="D87" s="11">
         <v>1.59</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="F87" s="32">
+      <c r="F87" s="12">
         <v>82</v>
       </c>
-      <c r="G87" s="30"/>
+      <c r="G87" s="10"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
@@ -3677,16 +3650,16 @@
       <c r="C88" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="D88" s="31">
+      <c r="D88" s="11">
         <v>1.98</v>
       </c>
       <c r="E88" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="F88" s="32">
+      <c r="F88" s="12">
         <v>-3</v>
       </c>
-      <c r="G88" s="30"/>
+      <c r="G88" s="10"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
@@ -3698,16 +3671,16 @@
       <c r="C89" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="D89" s="31">
+      <c r="D89" s="11">
         <v>2.38</v>
       </c>
       <c r="E89" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="F89" s="32">
+      <c r="F89" s="12">
         <v>0</v>
       </c>
-      <c r="G89" s="30"/>
+      <c r="G89" s="10"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
@@ -3719,32 +3692,32 @@
       <c r="C90" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="D90" s="31">
+      <c r="D90" s="11">
         <v>2.7600000000000002</v>
       </c>
       <c r="E90" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="F90" s="32">
+      <c r="F90" s="12">
         <v>-40</v>
       </c>
-      <c r="G90" s="30"/>
+      <c r="G90" s="10"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="5"/>
       <c r="B91" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="D91" s="31">
+      <c r="D91" s="11">
         <v>1.31</v>
       </c>
       <c r="E91" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="F91" s="32">
+      <c r="F91" s="12">
         <v>0</v>
       </c>
-      <c r="G91" s="30"/>
+      <c r="G91" s="10"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
@@ -3756,16 +3729,16 @@
       <c r="C92" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D92" s="31">
+      <c r="D92" s="11">
         <v>3.12</v>
       </c>
       <c r="E92" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="F92" s="32">
+      <c r="F92" s="12">
         <v>-5</v>
       </c>
-      <c r="G92" s="30"/>
+      <c r="G92" s="10"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
@@ -3777,16 +3750,16 @@
       <c r="C93" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="D93" s="31">
+      <c r="D93" s="11">
         <v>3.5100000000000002</v>
       </c>
       <c r="E93" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="F93" s="32">
+      <c r="F93" s="12">
         <v>34</v>
       </c>
-      <c r="G93" s="30"/>
+      <c r="G93" s="10"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
@@ -3798,16 +3771,16 @@
       <c r="C94" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D94" s="31">
+      <c r="D94" s="11">
         <v>3.91</v>
       </c>
       <c r="E94" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="F94" s="32">
+      <c r="F94" s="12">
         <v>82</v>
       </c>
-      <c r="G94" s="30"/>
+      <c r="G94" s="10"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
@@ -3819,16 +3792,16 @@
       <c r="C95" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D95" s="31">
+      <c r="D95" s="11">
         <v>4.3100000000000005</v>
       </c>
       <c r="E95" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="F95" s="32">
+      <c r="F95" s="12">
         <v>64</v>
       </c>
-      <c r="G95" s="30"/>
+      <c r="G95" s="10"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
@@ -3840,16 +3813,16 @@
       <c r="C96" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D96" s="31">
+      <c r="D96" s="11">
         <v>4.68</v>
       </c>
       <c r="E96" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="F96" s="32">
+      <c r="F96" s="12">
         <v>61</v>
       </c>
-      <c r="G96" s="30"/>
+      <c r="G96" s="10"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
@@ -3861,16 +3834,16 @@
       <c r="C97" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="D97" s="31">
+      <c r="D97" s="11">
         <v>5.07</v>
       </c>
       <c r="E97" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="F97" s="32">
+      <c r="F97" s="12">
         <v>66</v>
       </c>
-      <c r="G97" s="30"/>
+      <c r="G97" s="10"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
@@ -3882,16 +3855,16 @@
       <c r="C98" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="D98" s="31">
+      <c r="D98" s="11">
         <v>5.47</v>
       </c>
       <c r="E98" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="F98" s="32">
+      <c r="F98" s="12">
         <v>113</v>
       </c>
-      <c r="G98" s="30"/>
+      <c r="G98" s="10"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
@@ -3903,32 +3876,32 @@
       <c r="C99" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="D99" s="31">
+      <c r="D99" s="11">
         <v>5.87</v>
       </c>
       <c r="E99" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="F99" s="32">
+      <c r="F99" s="12">
         <v>28</v>
       </c>
-      <c r="G99" s="30"/>
+      <c r="G99" s="10"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="5"/>
       <c r="B100" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="D100" s="31">
+      <c r="D100" s="11">
         <v>1.69</v>
       </c>
       <c r="E100" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="F100" s="32">
+      <c r="F100" s="12">
         <v>91</v>
       </c>
-      <c r="G100" s="30"/>
+      <c r="G100" s="10"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
@@ -3940,16 +3913,16 @@
       <c r="C101" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="D101" s="31">
+      <c r="D101" s="11">
         <v>3.98</v>
       </c>
       <c r="E101" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="F101" s="32">
+      <c r="F101" s="12">
         <v>55</v>
       </c>
-      <c r="G101" s="30"/>
+      <c r="G101" s="10"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
@@ -3961,16 +3934,16 @@
       <c r="C102" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="D102" s="31">
+      <c r="D102" s="11">
         <v>5.12</v>
       </c>
       <c r="E102" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="F102" s="32">
+      <c r="F102" s="12">
         <v>45</v>
       </c>
-      <c r="G102" s="30"/>
+      <c r="G102" s="10"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
@@ -3982,16 +3955,16 @@
       <c r="C103" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="D103" s="31">
+      <c r="D103" s="11">
         <v>5.94</v>
       </c>
       <c r="E103" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="F103" s="32">
+      <c r="F103" s="12">
         <v>52</v>
       </c>
-      <c r="G103" s="30"/>
+      <c r="G103" s="10"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
@@ -4003,32 +3976,32 @@
       <c r="C104" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="D104" s="31">
+      <c r="D104" s="11">
         <v>6.92</v>
       </c>
       <c r="E104" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="F104" s="32">
+      <c r="F104" s="12">
         <v>41</v>
       </c>
-      <c r="G104" s="30"/>
+      <c r="G104" s="10"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="5"/>
       <c r="B105" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="D105" s="31">
+      <c r="D105" s="11">
         <v>2.13</v>
       </c>
       <c r="E105" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="F105" s="32">
+      <c r="F105" s="12">
         <v>0</v>
       </c>
-      <c r="G105" s="30"/>
+      <c r="G105" s="10"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
@@ -4040,16 +4013,16 @@
       <c r="C106" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="D106" s="31">
+      <c r="D106" s="11">
         <v>5.1100000000000003</v>
       </c>
       <c r="E106" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="F106" s="32">
+      <c r="F106" s="12">
         <v>-7</v>
       </c>
-      <c r="G106" s="30"/>
+      <c r="G106" s="10"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
@@ -4061,16 +4034,16 @@
       <c r="C107" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="D107" s="31">
+      <c r="D107" s="11">
         <v>5.76</v>
       </c>
       <c r="E107" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="F107" s="32">
+      <c r="F107" s="12">
         <v>100</v>
       </c>
-      <c r="G107" s="30"/>
+      <c r="G107" s="10"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
@@ -4082,16 +4055,16 @@
       <c r="C108" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="D108" s="31">
+      <c r="D108" s="11">
         <v>6.3900000000000006</v>
       </c>
       <c r="E108" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="F108" s="32">
+      <c r="F108" s="12">
         <v>13</v>
       </c>
-      <c r="G108" s="30"/>
+      <c r="G108" s="10"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
@@ -4103,16 +4076,16 @@
       <c r="C109" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D109" s="31">
+      <c r="D109" s="11">
         <v>7.03</v>
       </c>
       <c r="E109" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="F109" s="32">
+      <c r="F109" s="12">
         <v>31</v>
       </c>
-      <c r="G109" s="30"/>
+      <c r="G109" s="10"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
@@ -4124,16 +4097,16 @@
       <c r="C110" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="D110" s="31">
+      <c r="D110" s="11">
         <v>7.68</v>
       </c>
       <c r="E110" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="F110" s="32">
+      <c r="F110" s="12">
         <v>95</v>
       </c>
-      <c r="G110" s="30"/>
+      <c r="G110" s="10"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
@@ -4145,16 +4118,16 @@
       <c r="C111" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D111" s="31">
+      <c r="D111" s="11">
         <v>8.31</v>
       </c>
       <c r="E111" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="F111" s="32">
+      <c r="F111" s="12">
         <v>148</v>
       </c>
-      <c r="G111" s="30"/>
+      <c r="G111" s="10"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
@@ -4166,16 +4139,16 @@
       <c r="C112" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="D112" s="31">
+      <c r="D112" s="11">
         <v>8.9500000000000011</v>
       </c>
       <c r="E112" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="F112" s="32">
+      <c r="F112" s="12">
         <v>4</v>
       </c>
-      <c r="G112" s="30"/>
+      <c r="G112" s="10"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
@@ -4187,32 +4160,32 @@
       <c r="C113" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="D113" s="31">
+      <c r="D113" s="11">
         <v>9.61</v>
       </c>
       <c r="E113" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="F113" s="32">
+      <c r="F113" s="12">
         <v>8</v>
       </c>
-      <c r="G113" s="30"/>
+      <c r="G113" s="10"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="5"/>
       <c r="B114" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D114" s="31">
+      <c r="D114" s="11">
         <v>4.2700000000000005</v>
       </c>
       <c r="E114" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="F114" s="32">
+      <c r="F114" s="12">
         <v>0</v>
       </c>
-      <c r="G114" s="30"/>
+      <c r="G114" s="10"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
@@ -4224,16 +4197,16 @@
       <c r="C115" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="D115" s="31">
+      <c r="D115" s="11">
         <v>10.220000000000001</v>
       </c>
       <c r="E115" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="F115" s="32">
+      <c r="F115" s="12">
         <v>20</v>
       </c>
-      <c r="G115" s="30"/>
+      <c r="G115" s="10"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
@@ -4245,16 +4218,16 @@
       <c r="C116" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="D116" s="31">
+      <c r="D116" s="11">
         <v>11.5</v>
       </c>
       <c r="E116" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="F116" s="32">
+      <c r="F116" s="12">
         <v>14</v>
       </c>
-      <c r="G116" s="30"/>
+      <c r="G116" s="10"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
@@ -4266,16 +4239,16 @@
       <c r="C117" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D117" s="31">
+      <c r="D117" s="11">
         <v>12.780000000000001</v>
       </c>
       <c r="E117" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="F117" s="32">
+      <c r="F117" s="12">
         <v>8</v>
       </c>
-      <c r="G117" s="30"/>
+      <c r="G117" s="10"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
@@ -4287,16 +4260,16 @@
       <c r="C118" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="D118" s="31">
+      <c r="D118" s="11">
         <v>14.07</v>
       </c>
       <c r="E118" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="F118" s="32">
+      <c r="F118" s="12">
         <v>12</v>
       </c>
-      <c r="G118" s="30"/>
+      <c r="G118" s="10"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
@@ -4308,16 +4281,16 @@
       <c r="C119" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="D119" s="31">
+      <c r="D119" s="11">
         <v>15.34</v>
       </c>
       <c r="E119" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F119" s="32">
+      <c r="F119" s="12">
         <v>15</v>
       </c>
-      <c r="G119" s="30"/>
+      <c r="G119" s="10"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
@@ -4329,16 +4302,16 @@
       <c r="C120" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D120" s="31">
+      <c r="D120" s="11">
         <v>16.61</v>
       </c>
       <c r="E120" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="F120" s="32">
+      <c r="F120" s="12">
         <v>32</v>
       </c>
-      <c r="G120" s="30"/>
+      <c r="G120" s="10"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
@@ -4350,16 +4323,16 @@
       <c r="C121" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D121" s="31">
+      <c r="D121" s="11">
         <v>17.88</v>
       </c>
       <c r="E121" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="F121" s="32">
+      <c r="F121" s="12">
         <v>21</v>
       </c>
-      <c r="G121" s="30"/>
+      <c r="G121" s="10"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
@@ -4371,32 +4344,32 @@
       <c r="C122" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="D122" s="31">
+      <c r="D122" s="11">
         <v>19.12</v>
       </c>
       <c r="E122" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="F122" s="32">
+      <c r="F122" s="12">
         <v>11</v>
       </c>
-      <c r="G122" s="30"/>
+      <c r="G122" s="10"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="5"/>
       <c r="B123" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="D123" s="31">
+      <c r="D123" s="11">
         <v>8.02</v>
       </c>
       <c r="E123" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="F123" s="32">
+      <c r="F123" s="12">
         <v>0</v>
       </c>
-      <c r="G123" s="30"/>
+      <c r="G123" s="10"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
@@ -4408,16 +4381,16 @@
       <c r="C124" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="D124" s="31">
+      <c r="D124" s="11">
         <v>18.100000000000001</v>
       </c>
       <c r="E124" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="F124" s="32">
+      <c r="F124" s="12">
         <v>13</v>
       </c>
-      <c r="G124" s="30"/>
+      <c r="G124" s="10"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
@@ -4429,16 +4402,16 @@
       <c r="C125" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="D125" s="31">
+      <c r="D125" s="11">
         <v>22.64</v>
       </c>
       <c r="E125" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="F125" s="32">
+      <c r="F125" s="12">
         <v>16</v>
       </c>
-      <c r="G125" s="30"/>
+      <c r="G125" s="10"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
@@ -4450,16 +4423,16 @@
       <c r="C126" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="D126" s="31">
+      <c r="D126" s="11">
         <v>27.150000000000002</v>
       </c>
       <c r="E126" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="F126" s="32">
+      <c r="F126" s="12">
         <v>21</v>
       </c>
-      <c r="G126" s="30"/>
+      <c r="G126" s="10"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
@@ -4471,16 +4444,16 @@
       <c r="C127" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="D127" s="31">
+      <c r="D127" s="11">
         <v>31.69</v>
       </c>
       <c r="E127" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="F127" s="32">
+      <c r="F127" s="12">
         <v>15</v>
       </c>
-      <c r="G127" s="30"/>
+      <c r="G127" s="10"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
@@ -4492,16 +4465,16 @@
       <c r="C128" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D128" s="31">
+      <c r="D128" s="11">
         <v>33.94</v>
       </c>
       <c r="E128" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="F128" s="32">
+      <c r="F128" s="12">
         <v>0</v>
       </c>
-      <c r="G128" s="30"/>
+      <c r="G128" s="10"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
@@ -4513,32 +4486,32 @@
       <c r="C129" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="D129" s="31">
+      <c r="D129" s="11">
         <v>36.22</v>
       </c>
       <c r="E129" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="F129" s="32">
+      <c r="F129" s="12">
         <v>0</v>
       </c>
-      <c r="G129" s="33"/>
+      <c r="G129" s="10"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="5"/>
       <c r="B130" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="D130" s="34">
+      <c r="D130" s="11">
         <v>2.15</v>
       </c>
       <c r="E130" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="F130" s="35">
+      <c r="F130" s="12">
         <v>0</v>
       </c>
-      <c r="G130" s="33"/>
+      <c r="G130" s="10"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
@@ -4550,16 +4523,16 @@
       <c r="C131" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="D131" s="34">
+      <c r="D131" s="11">
         <v>5.12</v>
       </c>
       <c r="E131" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="F131" s="35">
+      <c r="F131" s="12">
         <v>0</v>
       </c>
-      <c r="G131" s="33"/>
+      <c r="G131" s="10"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
@@ -4571,16 +4544,16 @@
       <c r="C132" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="D132" s="34">
+      <c r="D132" s="11">
         <v>3.93</v>
       </c>
       <c r="E132" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="F132" s="35">
+      <c r="F132" s="12">
         <v>369</v>
       </c>
-      <c r="G132" s="33"/>
+      <c r="G132" s="10"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
@@ -4592,16 +4565,16 @@
       <c r="C133" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D133" s="34">
+      <c r="D133" s="11">
         <v>4.53</v>
       </c>
       <c r="E133" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="F133" s="35">
+      <c r="F133" s="12">
         <v>624</v>
       </c>
-      <c r="G133" s="33"/>
+      <c r="G133" s="10"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
@@ -4613,16 +4586,16 @@
       <c r="C134" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="D134" s="34">
+      <c r="D134" s="11">
         <v>6.7</v>
       </c>
       <c r="E134" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="F134" s="35">
+      <c r="F134" s="12">
         <v>193</v>
       </c>
-      <c r="G134" s="33"/>
+      <c r="G134" s="10"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
@@ -4634,16 +4607,16 @@
       <c r="C135" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="D135" s="34">
+      <c r="D135" s="11">
         <v>8.31</v>
       </c>
       <c r="E135" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="F135" s="35">
+      <c r="F135" s="12">
         <v>0</v>
       </c>
-      <c r="G135" s="33"/>
+      <c r="G135" s="10"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
@@ -4655,16 +4628,16 @@
       <c r="C136" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="D136" s="34">
+      <c r="D136" s="11">
         <v>7.8900000000000006</v>
       </c>
       <c r="E136" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="F136" s="35">
+      <c r="F136" s="12">
         <v>369</v>
       </c>
-      <c r="G136" s="33"/>
+      <c r="G136" s="10"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
@@ -4676,32 +4649,32 @@
       <c r="C137" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="D137" s="34">
+      <c r="D137" s="11">
         <v>9.61</v>
       </c>
       <c r="E137" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="F137" s="35">
+      <c r="F137" s="12">
         <v>0</v>
       </c>
-      <c r="G137" s="33"/>
+      <c r="G137" s="10"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
       <c r="B138" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="D138" s="34">
+      <c r="D138" s="11">
         <v>3.5500000000000003</v>
       </c>
       <c r="E138" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="F138" s="35">
+      <c r="F138" s="12">
         <v>0</v>
       </c>
-      <c r="G138" s="33"/>
+      <c r="G138" s="10"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
@@ -4713,16 +4686,16 @@
       <c r="C139" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D139" s="34">
+      <c r="D139" s="11">
         <v>6.22</v>
       </c>
       <c r="E139" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="F139" s="35">
+      <c r="F139" s="12">
         <v>239</v>
       </c>
-      <c r="G139" s="33"/>
+      <c r="G139" s="10"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
@@ -4734,16 +4707,16 @@
       <c r="C140" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D140" s="34">
+      <c r="D140" s="11">
         <v>6.7</v>
       </c>
       <c r="E140" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="F140" s="35">
+      <c r="F140" s="12">
         <v>375</v>
       </c>
-      <c r="G140" s="33"/>
+      <c r="G140" s="10"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
@@ -4755,16 +4728,16 @@
       <c r="C141" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="D141" s="34">
+      <c r="D141" s="11">
         <v>10.91</v>
       </c>
       <c r="E141" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="F141" s="35">
+      <c r="F141" s="12">
         <v>0</v>
       </c>
-      <c r="G141" s="33"/>
+      <c r="G141" s="10"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
@@ -4776,16 +4749,16 @@
       <c r="C142" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D142" s="34">
+      <c r="D142" s="11">
         <v>10.370000000000001</v>
       </c>
       <c r="E142" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="F142" s="35">
+      <c r="F142" s="12">
         <v>201</v>
       </c>
-      <c r="G142" s="33"/>
+      <c r="G142" s="10"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
@@ -4797,16 +4770,16 @@
       <c r="C143" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="D143" s="34">
+      <c r="D143" s="11">
         <v>6.76</v>
       </c>
       <c r="E143" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="F143" s="35">
+      <c r="F143" s="12">
         <v>132</v>
       </c>
-      <c r="G143" s="33"/>
+      <c r="G143" s="10"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
@@ -4818,16 +4791,16 @@
       <c r="C144" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D144" s="34">
+      <c r="D144" s="11">
         <v>9.23</v>
       </c>
       <c r="E144" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="F144" s="35">
+      <c r="F144" s="12">
         <v>0</v>
       </c>
-      <c r="G144" s="33"/>
+      <c r="G144" s="10"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
@@ -4839,32 +4812,32 @@
       <c r="C145" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D145" s="34">
+      <c r="D145" s="11">
         <v>11.14</v>
       </c>
       <c r="E145" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="F145" s="35">
+      <c r="F145" s="12">
         <v>0</v>
       </c>
-      <c r="G145" s="33"/>
+      <c r="G145" s="10"/>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
       <c r="B146" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="D146" s="34">
+      <c r="D146" s="11">
         <v>3.17</v>
       </c>
       <c r="E146" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="F146" s="35">
+      <c r="F146" s="12">
         <v>0</v>
       </c>
-      <c r="G146" s="33"/>
+      <c r="G146" s="10"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
@@ -4876,16 +4849,16 @@
       <c r="C147" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D147" s="34">
+      <c r="D147" s="11">
         <v>7.2</v>
       </c>
       <c r="E147" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="F147" s="35">
+      <c r="F147" s="12">
         <v>0</v>
       </c>
-      <c r="G147" s="33"/>
+      <c r="G147" s="10"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
@@ -4897,16 +4870,16 @@
       <c r="C148" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="D148" s="34">
+      <c r="D148" s="11">
         <v>18.11</v>
       </c>
       <c r="E148" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="F148" s="35">
+      <c r="F148" s="12">
         <v>0</v>
       </c>
-      <c r="G148" s="33"/>
+      <c r="G148" s="10"/>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
@@ -4918,16 +4891,16 @@
       <c r="C149" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="D149" s="34">
+      <c r="D149" s="11">
         <v>11.94</v>
       </c>
       <c r="E149" s="19" t="s">
         <v>274</v>
       </c>
-      <c r="F149" s="35">
+      <c r="F149" s="12">
         <v>81</v>
       </c>
-      <c r="G149" s="33"/>
+      <c r="G149" s="10"/>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
@@ -4939,16 +4912,16 @@
       <c r="C150" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="D150" s="34">
+      <c r="D150" s="11">
         <v>15.16</v>
       </c>
       <c r="E150" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="F150" s="35">
+      <c r="F150" s="12">
         <v>45</v>
       </c>
-      <c r="G150" s="33"/>
+      <c r="G150" s="10"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
@@ -4960,16 +4933,16 @@
       <c r="C151" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="D151" s="34">
+      <c r="D151" s="11">
         <v>13.52</v>
       </c>
       <c r="E151" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="F151" s="35">
+      <c r="F151" s="12">
         <v>43</v>
       </c>
-      <c r="G151" s="33"/>
+      <c r="G151" s="10"/>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
@@ -4981,16 +4954,16 @@
       <c r="C152" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="D152" s="34">
+      <c r="D152" s="11">
         <v>24.89</v>
       </c>
       <c r="E152" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="F152" s="35">
+      <c r="F152" s="12">
         <v>0</v>
       </c>
-      <c r="G152" s="33"/>
+      <c r="G152" s="10"/>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
